--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
@@ -1169,14 +1169,14 @@
       <c r="V2" t="str">
         <v/>
       </c>
-      <c r="W2" t="str">
-        <v/>
+      <c r="W2" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X2" t="str">
         <v/>
       </c>
-      <c r="Y2" t="str">
-        <v/>
+      <c r="Y2" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z2" t="str">
         <v>淡水路亚</v>
@@ -1205,8 +1205,8 @@
       <c r="AH2" t="str">
         <v/>
       </c>
-      <c r="AI2" t="str">
-        <v>淡水路亚</v>
+      <c r="AI2" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
@@ -1345,14 +1345,14 @@
       <c r="V3" t="str">
         <v/>
       </c>
-      <c r="W3" t="str">
-        <v/>
+      <c r="W3" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X3" t="str">
         <v/>
       </c>
-      <c r="Y3" t="str">
-        <v/>
+      <c r="Y3" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z3" t="str">
         <v>淡水路亚</v>
@@ -1381,8 +1381,8 @@
       <c r="AH3" t="str">
         <v/>
       </c>
-      <c r="AI3" t="str">
-        <v>淡水路亚</v>
+      <c r="AI3" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
@@ -1521,14 +1521,14 @@
       <c r="V4" t="str">
         <v/>
       </c>
-      <c r="W4" t="str">
-        <v/>
+      <c r="W4" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X4" t="str">
         <v/>
       </c>
-      <c r="Y4" t="str">
-        <v/>
+      <c r="Y4" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z4" t="str">
         <v>淡水路亚</v>
@@ -1557,8 +1557,8 @@
       <c r="AH4" t="str">
         <v/>
       </c>
-      <c r="AI4" t="str">
-        <v>淡水路亚</v>
+      <c r="AI4" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
@@ -1697,14 +1697,14 @@
       <c r="V5" t="str">
         <v/>
       </c>
-      <c r="W5" t="str">
-        <v/>
+      <c r="W5" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X5" t="str">
         <v/>
       </c>
-      <c r="Y5" t="str">
-        <v/>
+      <c r="Y5" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z5" t="str">
         <v>淡水路亚</v>
@@ -1733,8 +1733,8 @@
       <c r="AH5" t="str">
         <v/>
       </c>
-      <c r="AI5" t="str">
-        <v>淡水路亚</v>
+      <c r="AI5" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
@@ -1873,14 +1873,14 @@
       <c r="V6" t="str">
         <v/>
       </c>
-      <c r="W6" t="str">
-        <v/>
+      <c r="W6" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X6" t="str">
         <v/>
       </c>
-      <c r="Y6" t="str">
-        <v/>
+      <c r="Y6" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z6" t="str">
         <v>淡水路亚</v>
@@ -1909,8 +1909,8 @@
       <c r="AH6" t="str">
         <v/>
       </c>
-      <c r="AI6" t="str">
-        <v>淡水路亚</v>
+      <c r="AI6" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
@@ -2049,14 +2049,14 @@
       <c r="V7" t="str">
         <v/>
       </c>
-      <c r="W7" t="str">
-        <v/>
+      <c r="W7" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X7" t="str">
         <v/>
       </c>
-      <c r="Y7" t="str">
-        <v/>
+      <c r="Y7" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z7" t="str">
         <v>淡水路亚</v>
@@ -2085,8 +2085,8 @@
       <c r="AH7" t="str">
         <v/>
       </c>
-      <c r="AI7" t="str">
-        <v>淡水路亚</v>
+      <c r="AI7" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -2225,14 +2225,14 @@
       <c r="V8" t="str">
         <v/>
       </c>
-      <c r="W8" t="str">
-        <v/>
+      <c r="W8" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X8" t="str">
         <v/>
       </c>
-      <c r="Y8" t="str">
-        <v/>
+      <c r="Y8" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z8" t="str">
         <v>淡水路亚</v>
@@ -2261,8 +2261,8 @@
       <c r="AH8" t="str">
         <v/>
       </c>
-      <c r="AI8" t="str">
-        <v>淡水路亚</v>
+      <c r="AI8" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ8" t="str">
         <v/>
@@ -2401,14 +2401,14 @@
       <c r="V9" t="str">
         <v/>
       </c>
-      <c r="W9" t="str">
-        <v/>
+      <c r="W9" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X9" t="str">
         <v/>
       </c>
-      <c r="Y9" t="str">
-        <v/>
+      <c r="Y9" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z9" t="str">
         <v>淡水路亚</v>
@@ -2437,8 +2437,8 @@
       <c r="AH9" t="str">
         <v/>
       </c>
-      <c r="AI9" t="str">
-        <v>淡水路亚</v>
+      <c r="AI9" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ9" t="str">
         <v/>
@@ -2577,14 +2577,14 @@
       <c r="V10" t="str">
         <v/>
       </c>
-      <c r="W10" t="str">
-        <v/>
+      <c r="W10" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X10" t="str">
         <v/>
       </c>
-      <c r="Y10" t="str">
-        <v/>
+      <c r="Y10" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z10" t="str">
         <v>淡水路亚</v>
@@ -2613,8 +2613,8 @@
       <c r="AH10" t="str">
         <v/>
       </c>
-      <c r="AI10" t="str">
-        <v>淡水路亚</v>
+      <c r="AI10" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ10" t="str">
         <v/>
@@ -2753,14 +2753,14 @@
       <c r="V11" t="str">
         <v/>
       </c>
-      <c r="W11" t="str">
-        <v/>
+      <c r="W11" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X11" t="str">
         <v/>
       </c>
-      <c r="Y11" t="str">
-        <v/>
+      <c r="Y11" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z11" t="str">
         <v>淡水路亚</v>
@@ -2789,8 +2789,8 @@
       <c r="AH11" t="str">
         <v/>
       </c>
-      <c r="AI11" t="str">
-        <v>淡水路亚</v>
+      <c r="AI11" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ11" t="str">
         <v/>
@@ -2929,14 +2929,14 @@
       <c r="V12" t="str">
         <v/>
       </c>
-      <c r="W12" t="str">
-        <v/>
+      <c r="W12" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X12" t="str">
         <v/>
       </c>
-      <c r="Y12" t="str">
-        <v/>
+      <c r="Y12" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z12" t="str">
         <v>淡水路亚</v>
@@ -2965,8 +2965,8 @@
       <c r="AH12" t="str">
         <v/>
       </c>
-      <c r="AI12" t="str">
-        <v>淡水路亚</v>
+      <c r="AI12" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ12" t="str">
         <v/>
@@ -3105,14 +3105,14 @@
       <c r="V13" t="str">
         <v/>
       </c>
-      <c r="W13" t="str">
-        <v/>
+      <c r="W13" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X13" t="str">
         <v/>
       </c>
-      <c r="Y13" t="str">
-        <v/>
+      <c r="Y13" t="str" s="1">
+        <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z13" t="str">
         <v>淡水路亚</v>
@@ -3141,8 +3141,8 @@
       <c r="AH13" t="str">
         <v/>
       </c>
-      <c r="AI13" t="str">
-        <v>淡水路亚</v>
+      <c r="AI13" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ13" t="str">
         <v/>
@@ -3281,14 +3281,14 @@
       <c r="V14" t="str">
         <v/>
       </c>
-      <c r="W14" t="str">
-        <v/>
-      </c>
-      <c r="X14" t="str">
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <v/>
+      <c r="W14" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X14" t="str" s="1">
+        <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
+      </c>
+      <c r="Y14" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z14" t="str">
         <v>淡水路亚</v>
@@ -3317,8 +3317,8 @@
       <c r="AH14" t="str">
         <v/>
       </c>
-      <c r="AI14" t="str">
-        <v>淡水路亚</v>
+      <c r="AI14" t="str" s="1">
+        <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ14" t="str">
         <v/>
@@ -3457,14 +3457,14 @@
       <c r="V15" t="str">
         <v/>
       </c>
-      <c r="W15" t="str">
-        <v/>
-      </c>
-      <c r="X15" t="str">
-        <v/>
-      </c>
-      <c r="Y15" t="str">
-        <v/>
+      <c r="W15" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X15" t="str" s="1">
+        <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
+      </c>
+      <c r="Y15" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z15" t="str">
         <v>淡水路亚</v>
@@ -3493,8 +3493,8 @@
       <c r="AH15" t="str">
         <v/>
       </c>
-      <c r="AI15" t="str">
-        <v>淡水路亚</v>
+      <c r="AI15" t="str" s="1">
+        <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ15" t="str">
         <v/>
@@ -3633,14 +3633,14 @@
       <c r="V16" t="str">
         <v/>
       </c>
-      <c r="W16" t="str">
-        <v/>
-      </c>
-      <c r="X16" t="str">
-        <v/>
-      </c>
-      <c r="Y16" t="str">
-        <v/>
+      <c r="W16" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X16" t="str" s="1">
+        <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
+      </c>
+      <c r="Y16" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z16" t="str">
         <v>淡水路亚</v>
@@ -3669,8 +3669,8 @@
       <c r="AH16" t="str">
         <v/>
       </c>
-      <c r="AI16" t="str">
-        <v>淡水路亚</v>
+      <c r="AI16" t="str" s="1">
+        <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ16" t="str">
         <v/>
@@ -3809,14 +3809,14 @@
       <c r="V17" t="str">
         <v/>
       </c>
-      <c r="W17" t="str">
-        <v/>
-      </c>
-      <c r="X17" t="str">
-        <v/>
-      </c>
-      <c r="Y17" t="str">
-        <v/>
+      <c r="W17" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X17" t="str" s="1">
+        <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
+      </c>
+      <c r="Y17" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z17" t="str">
         <v>淡水路亚</v>
@@ -3845,8 +3845,8 @@
       <c r="AH17" t="str">
         <v/>
       </c>
-      <c r="AI17" t="str">
-        <v>淡水路亚</v>
+      <c r="AI17" t="str" s="1">
+        <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ17" t="str">
         <v/>
@@ -3985,14 +3985,14 @@
       <c r="V18" t="str">
         <v/>
       </c>
-      <c r="W18" t="str">
-        <v/>
-      </c>
-      <c r="X18" t="str">
-        <v/>
-      </c>
-      <c r="Y18" t="str">
-        <v/>
+      <c r="W18" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X18" t="str" s="1">
+        <v>Genuine Spool 18 ALDEBARAN MGL</v>
+      </c>
+      <c r="Y18" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z18" t="str">
         <v>淡水路亚</v>
@@ -4021,8 +4021,8 @@
       <c r="AH18" t="str">
         <v/>
       </c>
-      <c r="AI18" t="str">
-        <v>淡水路亚</v>
+      <c r="AI18" t="str" s="1">
+        <v>淡水技巧</v>
       </c>
       <c r="AJ18" t="str">
         <v/>
@@ -4161,14 +4161,14 @@
       <c r="V19" t="str">
         <v/>
       </c>
-      <c r="W19" t="str">
-        <v/>
-      </c>
-      <c r="X19" t="str">
-        <v/>
-      </c>
-      <c r="Y19" t="str">
-        <v/>
+      <c r="W19" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X19" t="str" s="1">
+        <v>Genuine Spool 18 ALDEBARAN MGL</v>
+      </c>
+      <c r="Y19" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z19" t="str">
         <v>淡水路亚</v>
@@ -4197,8 +4197,8 @@
       <c r="AH19" t="str">
         <v/>
       </c>
-      <c r="AI19" t="str">
-        <v>淡水路亚</v>
+      <c r="AI19" t="str" s="1">
+        <v>淡水技巧</v>
       </c>
       <c r="AJ19" t="str">
         <v/>
@@ -4337,14 +4337,14 @@
       <c r="V20" t="str">
         <v/>
       </c>
-      <c r="W20" t="str">
-        <v/>
-      </c>
-      <c r="X20" t="str">
-        <v/>
-      </c>
-      <c r="Y20" t="str">
-        <v/>
+      <c r="W20" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X20" t="str" s="1">
+        <v>Genuine Spool 18 ALDEBARAN MGL</v>
+      </c>
+      <c r="Y20" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z20" t="str">
         <v>淡水路亚</v>
@@ -4373,8 +4373,8 @@
       <c r="AH20" t="str">
         <v/>
       </c>
-      <c r="AI20" t="str">
-        <v>淡水路亚</v>
+      <c r="AI20" t="str" s="1">
+        <v>淡水技巧</v>
       </c>
       <c r="AJ20" t="str">
         <v/>
@@ -4513,14 +4513,14 @@
       <c r="V21" t="str">
         <v/>
       </c>
-      <c r="W21" t="str">
-        <v/>
-      </c>
-      <c r="X21" t="str">
-        <v/>
-      </c>
-      <c r="Y21" t="str">
-        <v/>
+      <c r="W21" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X21" t="str" s="1">
+        <v>Genuine Spool 18 ALDEBARAN MGL</v>
+      </c>
+      <c r="Y21" t="str" s="1">
+        <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z21" t="str">
         <v>淡水路亚</v>
@@ -4549,8 +4549,8 @@
       <c r="AH21" t="str">
         <v/>
       </c>
-      <c r="AI21" t="str">
-        <v>淡水路亚</v>
+      <c r="AI21" t="str" s="1">
+        <v>淡水技巧</v>
       </c>
       <c r="AJ21" t="str">
         <v/>
@@ -4689,14 +4689,14 @@
       <c r="V22" t="str">
         <v/>
       </c>
-      <c r="W22" t="str">
-        <v/>
-      </c>
-      <c r="X22" t="str">
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <v/>
+      <c r="W22" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X22" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y22" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z22" t="str">
         <v>淡水路亚</v>
@@ -4725,8 +4725,8 @@
       <c r="AH22" t="str">
         <v/>
       </c>
-      <c r="AI22" t="str">
-        <v>淡水路亚</v>
+      <c r="AI22" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ22" t="str">
         <v/>
@@ -4865,14 +4865,14 @@
       <c r="V23" t="str">
         <v/>
       </c>
-      <c r="W23" t="str">
-        <v/>
-      </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <v/>
+      <c r="W23" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X23" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y23" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z23" t="str">
         <v>淡水路亚</v>
@@ -4901,8 +4901,8 @@
       <c r="AH23" t="str">
         <v/>
       </c>
-      <c r="AI23" t="str">
-        <v>淡水路亚</v>
+      <c r="AI23" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ23" t="str">
         <v/>
@@ -5041,14 +5041,14 @@
       <c r="V24" t="str">
         <v/>
       </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <v/>
+      <c r="W24" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X24" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y24" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z24" t="str">
         <v>淡水路亚</v>
@@ -5077,8 +5077,8 @@
       <c r="AH24" t="str">
         <v/>
       </c>
-      <c r="AI24" t="str">
-        <v>淡水路亚</v>
+      <c r="AI24" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ24" t="str">
         <v/>
@@ -5217,14 +5217,14 @@
       <c r="V25" t="str">
         <v/>
       </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <v/>
+      <c r="W25" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X25" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y25" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z25" t="str">
         <v>淡水路亚</v>
@@ -5253,8 +5253,8 @@
       <c r="AH25" t="str">
         <v/>
       </c>
-      <c r="AI25" t="str">
-        <v>淡水路亚</v>
+      <c r="AI25" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ25" t="str">
         <v/>
@@ -5393,14 +5393,14 @@
       <c r="V26" t="str">
         <v/>
       </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
+      <c r="W26" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X26" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y26" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z26" t="str">
         <v>淡水路亚</v>
@@ -5429,8 +5429,8 @@
       <c r="AH26" t="str">
         <v/>
       </c>
-      <c r="AI26" t="str">
-        <v>淡水路亚</v>
+      <c r="AI26" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ26" t="str">
         <v/>
@@ -5569,14 +5569,14 @@
       <c r="V27" t="str">
         <v/>
       </c>
-      <c r="W27" t="str">
-        <v/>
-      </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <v/>
+      <c r="W27" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X27" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y27" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z27" t="str">
         <v>淡水路亚</v>
@@ -5605,8 +5605,8 @@
       <c r="AH27" t="str">
         <v/>
       </c>
-      <c r="AI27" t="str">
-        <v>淡水路亚</v>
+      <c r="AI27" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ27" t="str">
         <v/>
@@ -5745,14 +5745,14 @@
       <c r="V28" t="str">
         <v/>
       </c>
-      <c r="W28" t="str">
-        <v/>
-      </c>
-      <c r="X28" t="str">
-        <v/>
-      </c>
-      <c r="Y28" t="str">
-        <v/>
+      <c r="W28" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X28" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y28" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z28" t="str">
         <v>淡水路亚</v>
@@ -5781,8 +5781,8 @@
       <c r="AH28" t="str">
         <v/>
       </c>
-      <c r="AI28" t="str">
-        <v>淡水路亚</v>
+      <c r="AI28" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ28" t="str">
         <v/>
@@ -5921,14 +5921,14 @@
       <c r="V29" t="str">
         <v/>
       </c>
-      <c r="W29" t="str">
-        <v/>
-      </c>
-      <c r="X29" t="str">
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <v/>
+      <c r="W29" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X29" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y29" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z29" t="str">
         <v>淡水路亚</v>
@@ -5957,8 +5957,8 @@
       <c r="AH29" t="str">
         <v/>
       </c>
-      <c r="AI29" t="str">
-        <v>淡水路亚</v>
+      <c r="AI29" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ29" t="str">
         <v/>
@@ -6097,14 +6097,14 @@
       <c r="V30" t="str">
         <v/>
       </c>
-      <c r="W30" t="str">
-        <v/>
-      </c>
-      <c r="X30" t="str">
-        <v/>
-      </c>
-      <c r="Y30" t="str">
-        <v/>
+      <c r="W30" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X30" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y30" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z30" t="str">
         <v>淡水路亚</v>
@@ -6133,8 +6133,8 @@
       <c r="AH30" t="str">
         <v/>
       </c>
-      <c r="AI30" t="str">
-        <v>淡水路亚</v>
+      <c r="AI30" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ30" t="str">
         <v/>
@@ -6273,14 +6273,14 @@
       <c r="V31" t="str">
         <v/>
       </c>
-      <c r="W31" t="str">
-        <v/>
-      </c>
-      <c r="X31" t="str">
-        <v/>
-      </c>
-      <c r="Y31" t="str">
-        <v/>
+      <c r="W31" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X31" t="str" s="1">
+        <v>Genuine Spool 22 CURADO DC</v>
+      </c>
+      <c r="Y31" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z31" t="str">
         <v>淡水路亚</v>
@@ -6309,8 +6309,8 @@
       <c r="AH31" t="str">
         <v/>
       </c>
-      <c r="AI31" t="str">
-        <v>淡水路亚</v>
+      <c r="AI31" t="str" s="1">
+        <v>淡水重饵</v>
       </c>
       <c r="AJ31" t="str">
         <v/>
@@ -6449,14 +6449,14 @@
       <c r="V32" t="str">
         <v/>
       </c>
-      <c r="W32" t="str">
-        <v/>
-      </c>
-      <c r="X32" t="str">
-        <v/>
-      </c>
-      <c r="Y32" t="str">
-        <v/>
+      <c r="W32" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X32" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y32" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z32" t="str">
         <v>淡水路亚</v>
@@ -6485,8 +6485,8 @@
       <c r="AH32" t="str">
         <v/>
       </c>
-      <c r="AI32" t="str">
-        <v>淡水路亚</v>
+      <c r="AI32" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ32" t="str">
         <v/>
@@ -6625,14 +6625,14 @@
       <c r="V33" t="str">
         <v/>
       </c>
-      <c r="W33" t="str">
-        <v/>
-      </c>
-      <c r="X33" t="str">
-        <v/>
-      </c>
-      <c r="Y33" t="str">
-        <v/>
+      <c r="W33" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X33" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y33" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z33" t="str">
         <v>淡水路亚</v>
@@ -6661,8 +6661,8 @@
       <c r="AH33" t="str">
         <v/>
       </c>
-      <c r="AI33" t="str">
-        <v>淡水路亚</v>
+      <c r="AI33" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ33" t="str">
         <v/>
@@ -6801,14 +6801,14 @@
       <c r="V34" t="str">
         <v/>
       </c>
-      <c r="W34" t="str">
-        <v/>
-      </c>
-      <c r="X34" t="str">
-        <v/>
-      </c>
-      <c r="Y34" t="str">
-        <v/>
+      <c r="W34" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X34" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y34" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z34" t="str">
         <v>淡水路亚</v>
@@ -6837,8 +6837,8 @@
       <c r="AH34" t="str">
         <v/>
       </c>
-      <c r="AI34" t="str">
-        <v>淡水路亚</v>
+      <c r="AI34" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ34" t="str">
         <v/>
@@ -6977,14 +6977,14 @@
       <c r="V35" t="str">
         <v/>
       </c>
-      <c r="W35" t="str">
-        <v/>
-      </c>
-      <c r="X35" t="str">
-        <v/>
-      </c>
-      <c r="Y35" t="str">
-        <v/>
+      <c r="W35" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X35" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y35" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z35" t="str">
         <v>淡水路亚</v>
@@ -7013,8 +7013,8 @@
       <c r="AH35" t="str">
         <v/>
       </c>
-      <c r="AI35" t="str">
-        <v>淡水路亚</v>
+      <c r="AI35" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ35" t="str">
         <v/>
@@ -7153,14 +7153,14 @@
       <c r="V36" t="str">
         <v/>
       </c>
-      <c r="W36" t="str">
-        <v/>
-      </c>
-      <c r="X36" t="str">
-        <v/>
-      </c>
-      <c r="Y36" t="str">
-        <v/>
+      <c r="W36" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X36" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y36" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z36" t="str">
         <v>淡水路亚</v>
@@ -7189,8 +7189,8 @@
       <c r="AH36" t="str">
         <v/>
       </c>
-      <c r="AI36" t="str">
-        <v>淡水路亚</v>
+      <c r="AI36" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ36" t="str">
         <v/>
@@ -7329,14 +7329,14 @@
       <c r="V37" t="str">
         <v/>
       </c>
-      <c r="W37" t="str">
-        <v/>
-      </c>
-      <c r="X37" t="str">
-        <v/>
-      </c>
-      <c r="Y37" t="str">
-        <v/>
+      <c r="W37" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X37" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y37" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z37" t="str">
         <v>淡水路亚</v>
@@ -7365,8 +7365,8 @@
       <c r="AH37" t="str">
         <v/>
       </c>
-      <c r="AI37" t="str">
-        <v>淡水路亚</v>
+      <c r="AI37" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ37" t="str">
         <v/>
@@ -7505,14 +7505,14 @@
       <c r="V38" t="str">
         <v/>
       </c>
-      <c r="W38" t="str">
-        <v/>
-      </c>
-      <c r="X38" t="str">
-        <v/>
-      </c>
-      <c r="Y38" t="str">
-        <v/>
+      <c r="W38" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X38" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y38" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z38" t="str">
         <v>淡水路亚</v>
@@ -7541,8 +7541,8 @@
       <c r="AH38" t="str">
         <v/>
       </c>
-      <c r="AI38" t="str">
-        <v>淡水路亚</v>
+      <c r="AI38" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ38" t="str">
         <v/>
@@ -7681,14 +7681,14 @@
       <c r="V39" t="str">
         <v/>
       </c>
-      <c r="W39" t="str">
-        <v/>
-      </c>
-      <c r="X39" t="str">
-        <v/>
-      </c>
-      <c r="Y39" t="str">
-        <v/>
+      <c r="W39" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X39" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y39" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z39" t="str">
         <v>淡水路亚</v>
@@ -7717,8 +7717,8 @@
       <c r="AH39" t="str">
         <v/>
       </c>
-      <c r="AI39" t="str">
-        <v>淡水路亚</v>
+      <c r="AI39" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ39" t="str">
         <v/>
@@ -7857,14 +7857,14 @@
       <c r="V40" t="str">
         <v/>
       </c>
-      <c r="W40" t="str">
-        <v/>
-      </c>
-      <c r="X40" t="str">
-        <v/>
-      </c>
-      <c r="Y40" t="str">
-        <v/>
+      <c r="W40" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X40" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y40" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z40" t="str">
         <v>淡水路亚</v>
@@ -7893,8 +7893,8 @@
       <c r="AH40" t="str">
         <v/>
       </c>
-      <c r="AI40" t="str">
-        <v>淡水路亚</v>
+      <c r="AI40" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ40" t="str">
         <v/>
@@ -8033,14 +8033,14 @@
       <c r="V41" t="str">
         <v/>
       </c>
-      <c r="W41" t="str">
-        <v/>
-      </c>
-      <c r="X41" t="str">
-        <v/>
-      </c>
-      <c r="Y41" t="str">
-        <v/>
+      <c r="W41" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X41" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y41" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z41" t="str">
         <v>淡水路亚</v>
@@ -8069,8 +8069,8 @@
       <c r="AH41" t="str">
         <v/>
       </c>
-      <c r="AI41" t="str">
-        <v>淡水路亚</v>
+      <c r="AI41" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ41" t="str">
         <v/>
@@ -8209,14 +8209,14 @@
       <c r="V42" t="str">
         <v/>
       </c>
-      <c r="W42" t="str">
-        <v/>
-      </c>
-      <c r="X42" t="str">
-        <v/>
-      </c>
-      <c r="Y42" t="str">
-        <v/>
+      <c r="W42" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X42" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y42" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z42" t="str">
         <v>淡水路亚</v>
@@ -8245,8 +8245,8 @@
       <c r="AH42" t="str">
         <v/>
       </c>
-      <c r="AI42" t="str">
-        <v>淡水路亚</v>
+      <c r="AI42" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ42" t="str">
         <v/>
@@ -8385,14 +8385,14 @@
       <c r="V43" t="str">
         <v/>
       </c>
-      <c r="W43" t="str">
-        <v/>
-      </c>
-      <c r="X43" t="str">
-        <v/>
-      </c>
-      <c r="Y43" t="str">
-        <v/>
+      <c r="W43" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X43" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y43" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z43" t="str">
         <v>淡水路亚</v>
@@ -8421,8 +8421,8 @@
       <c r="AH43" t="str">
         <v/>
       </c>
-      <c r="AI43" t="str">
-        <v>淡水路亚</v>
+      <c r="AI43" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ43" t="str">
         <v/>
@@ -8561,14 +8561,14 @@
       <c r="V44" t="str">
         <v/>
       </c>
-      <c r="W44" t="str">
-        <v/>
-      </c>
-      <c r="X44" t="str">
-        <v/>
-      </c>
-      <c r="Y44" t="str">
-        <v/>
+      <c r="W44" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X44" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y44" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z44" t="str">
         <v>淡水路亚</v>
@@ -8597,8 +8597,8 @@
       <c r="AH44" t="str">
         <v/>
       </c>
-      <c r="AI44" t="str">
-        <v>淡水路亚</v>
+      <c r="AI44" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ44" t="str">
         <v/>
@@ -8737,14 +8737,14 @@
       <c r="V45" t="str">
         <v/>
       </c>
-      <c r="W45" t="str">
-        <v/>
-      </c>
-      <c r="X45" t="str">
-        <v/>
-      </c>
-      <c r="Y45" t="str">
-        <v/>
+      <c r="W45" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X45" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y45" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z45" t="str">
         <v>淡水路亚</v>
@@ -8773,8 +8773,8 @@
       <c r="AH45" t="str">
         <v/>
       </c>
-      <c r="AI45" t="str">
-        <v>淡水路亚</v>
+      <c r="AI45" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ45" t="str">
         <v/>
@@ -8913,14 +8913,14 @@
       <c r="V46" t="str">
         <v/>
       </c>
-      <c r="W46" t="str">
-        <v/>
-      </c>
-      <c r="X46" t="str">
-        <v/>
-      </c>
-      <c r="Y46" t="str">
-        <v/>
+      <c r="W46" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X46" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y46" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z46" t="str">
         <v>淡水路亚</v>
@@ -8949,8 +8949,8 @@
       <c r="AH46" t="str">
         <v/>
       </c>
-      <c r="AI46" t="str">
-        <v>淡水路亚</v>
+      <c r="AI46" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ46" t="str">
         <v/>
@@ -9089,14 +9089,14 @@
       <c r="V47" t="str">
         <v/>
       </c>
-      <c r="W47" t="str">
-        <v/>
-      </c>
-      <c r="X47" t="str">
-        <v/>
-      </c>
-      <c r="Y47" t="str">
-        <v/>
+      <c r="W47" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X47" t="str" s="1">
+        <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
+      </c>
+      <c r="Y47" t="str" s="1">
+        <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z47" t="str">
         <v>淡水路亚</v>
@@ -9125,8 +9125,8 @@
       <c r="AH47" t="str">
         <v/>
       </c>
-      <c r="AI47" t="str">
-        <v>淡水路亚</v>
+      <c r="AI47" t="str" s="1">
+        <v>淡水泛用</v>
       </c>
       <c r="AJ47" t="str">
         <v/>
@@ -9265,14 +9265,14 @@
       <c r="V48" t="str">
         <v/>
       </c>
-      <c r="W48" t="str">
-        <v/>
-      </c>
-      <c r="X48" t="str">
-        <v/>
-      </c>
-      <c r="Y48" t="str">
-        <v/>
+      <c r="W48" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X48" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y48" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z48" t="str">
         <v>淡水路亚</v>
@@ -9301,8 +9301,8 @@
       <c r="AH48" t="str">
         <v/>
       </c>
-      <c r="AI48" t="str">
-        <v>淡水路亚</v>
+      <c r="AI48" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ48" t="str">
         <v/>
@@ -9441,14 +9441,14 @@
       <c r="V49" t="str">
         <v/>
       </c>
-      <c r="W49" t="str">
-        <v/>
-      </c>
-      <c r="X49" t="str">
-        <v/>
-      </c>
-      <c r="Y49" t="str">
-        <v/>
+      <c r="W49" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X49" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y49" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z49" t="str">
         <v>淡水路亚</v>
@@ -9477,8 +9477,8 @@
       <c r="AH49" t="str">
         <v/>
       </c>
-      <c r="AI49" t="str">
-        <v>淡水路亚</v>
+      <c r="AI49" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ49" t="str">
         <v/>
@@ -9617,14 +9617,14 @@
       <c r="V50" t="str">
         <v/>
       </c>
-      <c r="W50" t="str">
-        <v/>
-      </c>
-      <c r="X50" t="str">
-        <v/>
-      </c>
-      <c r="Y50" t="str">
-        <v/>
+      <c r="W50" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X50" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y50" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z50" t="str">
         <v>淡水路亚</v>
@@ -9653,8 +9653,8 @@
       <c r="AH50" t="str">
         <v/>
       </c>
-      <c r="AI50" t="str">
-        <v>淡水路亚</v>
+      <c r="AI50" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ50" t="str">
         <v/>
@@ -9793,14 +9793,14 @@
       <c r="V51" t="str">
         <v/>
       </c>
-      <c r="W51" t="str">
-        <v/>
-      </c>
-      <c r="X51" t="str">
-        <v/>
-      </c>
-      <c r="Y51" t="str">
-        <v/>
+      <c r="W51" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X51" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y51" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z51" t="str">
         <v>淡水路亚</v>
@@ -9829,8 +9829,8 @@
       <c r="AH51" t="str">
         <v/>
       </c>
-      <c r="AI51" t="str">
-        <v>淡水路亚</v>
+      <c r="AI51" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ51" t="str">
         <v/>
@@ -9969,14 +9969,14 @@
       <c r="V52" t="str">
         <v/>
       </c>
-      <c r="W52" t="str">
-        <v/>
-      </c>
-      <c r="X52" t="str">
-        <v/>
-      </c>
-      <c r="Y52" t="str">
-        <v/>
+      <c r="W52" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X52" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y52" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z52" t="str">
         <v>淡水路亚</v>
@@ -10005,8 +10005,8 @@
       <c r="AH52" t="str">
         <v/>
       </c>
-      <c r="AI52" t="str">
-        <v>淡水路亚</v>
+      <c r="AI52" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ52" t="str">
         <v/>
@@ -10145,14 +10145,14 @@
       <c r="V53" t="str">
         <v/>
       </c>
-      <c r="W53" t="str">
-        <v/>
-      </c>
-      <c r="X53" t="str">
-        <v/>
-      </c>
-      <c r="Y53" t="str">
-        <v/>
+      <c r="W53" t="str" s="1">
+        <v>SHG-740ZZ / HRCB-740ZHi</v>
+      </c>
+      <c r="X53" t="str" s="1">
+        <v>Genuine Spool 22 Bantam</v>
+      </c>
+      <c r="Y53" t="str" s="1">
+        <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z53" t="str">
         <v>淡水路亚</v>
@@ -10181,8 +10181,8 @@
       <c r="AH53" t="str">
         <v/>
       </c>
-      <c r="AI53" t="str">
-        <v>淡水路亚</v>
+      <c r="AI53" t="str" s="1">
+        <v>淡水强力泛用</v>
       </c>
       <c r="AJ53" t="str">
         <v/>
@@ -10321,11 +10321,11 @@
       <c r="V54" t="str">
         <v/>
       </c>
-      <c r="W54" t="str">
-        <v/>
-      </c>
-      <c r="X54" t="str">
-        <v/>
+      <c r="W54" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X54" t="str" s="1">
+        <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y54" t="str">
         <v/>
@@ -10357,8 +10357,8 @@
       <c r="AH54" t="str">
         <v/>
       </c>
-      <c r="AI54" t="str">
-        <v>淡水路亚</v>
+      <c r="AI54" t="str" s="1">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ54" t="str">
         <v/>
@@ -10497,11 +10497,11 @@
       <c r="V55" t="str">
         <v/>
       </c>
-      <c r="W55" t="str">
-        <v/>
-      </c>
-      <c r="X55" t="str">
-        <v/>
+      <c r="W55" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X55" t="str" s="1">
+        <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y55" t="str">
         <v/>
@@ -10533,8 +10533,8 @@
       <c r="AH55" t="str">
         <v/>
       </c>
-      <c r="AI55" t="str">
-        <v>淡水路亚</v>
+      <c r="AI55" t="str" s="1">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ55" t="str">
         <v/>
@@ -10673,11 +10673,11 @@
       <c r="V56" t="str">
         <v/>
       </c>
-      <c r="W56" t="str">
-        <v/>
-      </c>
-      <c r="X56" t="str">
-        <v/>
+      <c r="W56" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X56" t="str" s="1">
+        <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y56" t="str">
         <v/>
@@ -10709,8 +10709,8 @@
       <c r="AH56" t="str">
         <v/>
       </c>
-      <c r="AI56" t="str">
-        <v>淡水路亚</v>
+      <c r="AI56" t="str" s="1">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ56" t="str">
         <v/>
@@ -10849,11 +10849,11 @@
       <c r="V57" t="str">
         <v/>
       </c>
-      <c r="W57" t="str">
-        <v/>
-      </c>
-      <c r="X57" t="str">
-        <v/>
+      <c r="W57" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X57" t="str" s="1">
+        <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y57" t="str">
         <v/>
@@ -10885,8 +10885,8 @@
       <c r="AH57" t="str">
         <v/>
       </c>
-      <c r="AI57" t="str">
-        <v>淡水路亚</v>
+      <c r="AI57" t="str" s="1">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ57" t="str">
         <v/>
@@ -11025,17 +11025,17 @@
       <c r="V58" t="str">
         <v/>
       </c>
-      <c r="W58" t="str">
-        <v/>
-      </c>
-      <c r="X58" t="str">
-        <v/>
+      <c r="W58" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X58" t="str" s="1">
+        <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y58" t="str">
         <v/>
       </c>
       <c r="Z58" t="str">
-        <v>淡水路亚</v>
+        <v>海水路亚</v>
       </c>
       <c r="AA58" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
@@ -11061,8 +11061,8 @@
       <c r="AH58" t="str">
         <v/>
       </c>
-      <c r="AI58" t="str">
-        <v>淡水路亚</v>
+      <c r="AI58" t="str" s="1">
+        <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ58" t="str">
         <v/>
@@ -11086,7 +11086,7 @@
         <v>DC</v>
       </c>
       <c r="AQ58" t="str">
-        <v>淡水泛用 / 远投 / 快收方向</v>
+        <v>海水近岸 / 远投 / 快收方向</v>
       </c>
       <c r="AR58" t="str">
         <v/>
@@ -11104,7 +11104,7 @@
         <v>baitcasting</v>
       </c>
       <c r="AW58" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="AX58" t="str">
         <v/>
@@ -11201,17 +11201,17 @@
       <c r="V59" t="str">
         <v/>
       </c>
-      <c r="W59" t="str">
-        <v/>
-      </c>
-      <c r="X59" t="str">
-        <v/>
+      <c r="W59" t="str" s="1">
+        <v>4x7x2.5（stock）</v>
+      </c>
+      <c r="X59" t="str" s="1">
+        <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y59" t="str">
         <v/>
       </c>
       <c r="Z59" t="str">
-        <v>淡水路亚</v>
+        <v>海水路亚</v>
       </c>
       <c r="AA59" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
@@ -11237,8 +11237,8 @@
       <c r="AH59" t="str">
         <v/>
       </c>
-      <c r="AI59" t="str">
-        <v>淡水路亚</v>
+      <c r="AI59" t="str" s="1">
+        <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ59" t="str">
         <v/>
@@ -11262,7 +11262,7 @@
         <v>DC</v>
       </c>
       <c r="AQ59" t="str">
-        <v>淡水泛用 / 远投 / 快收方向</v>
+        <v>海水近岸 / 远投 / 快收方向</v>
       </c>
       <c r="AR59" t="str">
         <v/>
@@ -11280,7 +11280,7 @@
         <v>baitcasting</v>
       </c>
       <c r="AW59" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="AX59" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:T9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,6 +466,12 @@
       <c r="R1" t="str">
         <v>market_reference_price</v>
       </c>
+      <c r="S1" t="str">
+        <v>player_positioning</v>
+      </c>
+      <c r="T1" t="str">
+        <v>player_selling_points</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -522,6 +528,12 @@
       <c r="R2" t="str">
         <v/>
       </c>
+      <c r="S2" t="str" s="1">
+        <v>泛用入门水滴轮</v>
+      </c>
+      <c r="T2" t="str" s="1">
+        <v>性价比高 / MGL III / 泛用覆盖</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -536,8 +548,8 @@
       <c r="D3" t="str">
         <v>ALDEBARAN BFS</v>
       </c>
-      <c r="E3" t="str">
-        <v/>
+      <c r="E3" t="str" s="1">
+        <v>阿德巴兰 BFS</v>
       </c>
       <c r="F3" t="str" s="1">
         <v>2022</v>
@@ -577,6 +589,12 @@
       </c>
       <c r="R3" t="str" s="1">
         <v>49900JPY</v>
+      </c>
+      <c r="S3" t="str" s="1">
+        <v>BFS轻饵特化旗舰</v>
+      </c>
+      <c r="T3" t="str" s="1">
+        <v>超轻线杯 / FTB / 轻饵上限高</v>
       </c>
     </row>
     <row r="4">
@@ -592,8 +610,8 @@
       <c r="D4" t="str">
         <v>ALDEBARAN MGL</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
+      <c r="E4" t="str" s="1">
+        <v>阿德巴兰 MGL</v>
       </c>
       <c r="F4" t="str" s="1">
         <v>2018</v>
@@ -633,6 +651,12 @@
       </c>
       <c r="R4" t="str" s="1">
         <v>49500JPY</v>
+      </c>
+      <c r="S4" t="str" s="1">
+        <v>轻量技巧泛用</v>
+      </c>
+      <c r="T4" t="str" s="1">
+        <v>低姿态轻量 / MGL线杯 / 技巧泛用</v>
       </c>
     </row>
     <row r="5">
@@ -648,8 +672,8 @@
       <c r="D5" t="str">
         <v>CURADO</v>
       </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="E5" t="str" s="1">
+        <v>库拉多 DC</v>
       </c>
       <c r="F5" t="str" s="1">
         <v>2022</v>
@@ -689,6 +713,12 @@
       </c>
       <c r="R5" t="str" s="1">
         <v>33300JPY</v>
+      </c>
+      <c r="S5" t="str" s="1">
+        <v>DC重饵泛用</v>
+      </c>
+      <c r="T5" t="str" s="1">
+        <v>DC刹车 / 200尺寸 / 重饵覆盖</v>
       </c>
     </row>
     <row r="6">
@@ -746,6 +776,12 @@
       <c r="R6" t="str" s="1">
         <v>48200JPY</v>
       </c>
+      <c r="S6" t="str" s="1">
+        <v>轻量泛用旗舰</v>
+      </c>
+      <c r="T6" t="str" s="1">
+        <v>CORESOLID / 轻量机身 / 泛用上限高</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -760,8 +796,8 @@
       <c r="D7" t="str">
         <v>Bantam</v>
       </c>
-      <c r="E7" t="str">
-        <v/>
+      <c r="E7" t="str" s="1">
+        <v>班塔姆</v>
       </c>
       <c r="F7" t="str" s="1">
         <v>2022</v>
@@ -801,6 +837,12 @@
       </c>
       <c r="R7" t="str" s="1">
         <v>42600JPY</v>
+      </c>
+      <c r="S7" t="str" s="1">
+        <v>刚性强力泛用</v>
+      </c>
+      <c r="T7" t="str" s="1">
+        <v>高刚性机身 / 黄铜主齿 / 卷感扎实</v>
       </c>
     </row>
     <row r="8">
@@ -816,8 +858,8 @@
       <c r="D8" t="str">
         <v>ANTARES DC MD</v>
       </c>
-      <c r="E8" t="str">
-        <v/>
+      <c r="E8" t="str" s="1">
+        <v>安塔列斯 DC MD</v>
       </c>
       <c r="F8" t="str" s="1">
         <v>2023</v>
@@ -857,6 +899,12 @@
       </c>
       <c r="R8" t="str" s="1">
         <v>62000JPY</v>
+      </c>
+      <c r="S8" t="str" s="1">
+        <v>巨物远投旗舰</v>
+      </c>
+      <c r="T8" t="str" s="1">
+        <v>4x8 DC MD Tune / 巨物向 / 宽线杯</v>
       </c>
     </row>
     <row r="9">
@@ -914,10 +962,16 @@
       <c r="R9" t="str" s="1">
         <v>83400JPY</v>
       </c>
+      <c r="S9" t="str" s="1">
+        <v>海鲈DC远投特化</v>
+      </c>
+      <c r="T9" t="str" s="1">
+        <v>海鲈PE适配 / DC调校 / 远投性能</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1238,8 +1292,8 @@
       <c r="AS2" t="str">
         <v/>
       </c>
-      <c r="AT2" t="str">
-        <v/>
+      <c r="AT2" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU2" t="str">
         <v/>
@@ -1259,8 +1313,8 @@
       <c r="AZ2" t="str">
         <v/>
       </c>
-      <c r="BA2" t="str">
-        <v/>
+      <c r="BA2" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB2" t="str">
         <v/>
@@ -1414,8 +1468,8 @@
       <c r="AS3" t="str">
         <v/>
       </c>
-      <c r="AT3" t="str">
-        <v/>
+      <c r="AT3" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU3" t="str">
         <v/>
@@ -1435,8 +1489,8 @@
       <c r="AZ3" t="str">
         <v/>
       </c>
-      <c r="BA3" t="str">
-        <v/>
+      <c r="BA3" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB3" t="str">
         <v/>
@@ -1590,8 +1644,8 @@
       <c r="AS4" t="str">
         <v/>
       </c>
-      <c r="AT4" t="str">
-        <v/>
+      <c r="AT4" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU4" t="str">
         <v/>
@@ -1611,8 +1665,8 @@
       <c r="AZ4" t="str">
         <v/>
       </c>
-      <c r="BA4" t="str">
-        <v/>
+      <c r="BA4" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB4" t="str">
         <v/>
@@ -1766,8 +1820,8 @@
       <c r="AS5" t="str">
         <v/>
       </c>
-      <c r="AT5" t="str">
-        <v/>
+      <c r="AT5" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU5" t="str">
         <v/>
@@ -1787,8 +1841,8 @@
       <c r="AZ5" t="str">
         <v/>
       </c>
-      <c r="BA5" t="str">
-        <v/>
+      <c r="BA5" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB5" t="str">
         <v/>
@@ -1942,8 +1996,8 @@
       <c r="AS6" t="str">
         <v/>
       </c>
-      <c r="AT6" t="str">
-        <v/>
+      <c r="AT6" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU6" t="str">
         <v/>
@@ -1963,8 +2017,8 @@
       <c r="AZ6" t="str">
         <v/>
       </c>
-      <c r="BA6" t="str">
-        <v/>
+      <c r="BA6" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB6" t="str">
         <v/>
@@ -2118,8 +2172,8 @@
       <c r="AS7" t="str">
         <v/>
       </c>
-      <c r="AT7" t="str">
-        <v/>
+      <c r="AT7" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU7" t="str">
         <v/>
@@ -2139,8 +2193,8 @@
       <c r="AZ7" t="str">
         <v/>
       </c>
-      <c r="BA7" t="str">
-        <v/>
+      <c r="BA7" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB7" t="str">
         <v/>
@@ -2294,8 +2348,8 @@
       <c r="AS8" t="str">
         <v/>
       </c>
-      <c r="AT8" t="str">
-        <v/>
+      <c r="AT8" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU8" t="str">
         <v/>
@@ -2315,8 +2369,8 @@
       <c r="AZ8" t="str">
         <v/>
       </c>
-      <c r="BA8" t="str">
-        <v/>
+      <c r="BA8" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB8" t="str">
         <v/>
@@ -2470,8 +2524,8 @@
       <c r="AS9" t="str">
         <v/>
       </c>
-      <c r="AT9" t="str">
-        <v/>
+      <c r="AT9" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU9" t="str">
         <v/>
@@ -2491,8 +2545,8 @@
       <c r="AZ9" t="str">
         <v/>
       </c>
-      <c r="BA9" t="str">
-        <v/>
+      <c r="BA9" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB9" t="str">
         <v/>
@@ -2646,8 +2700,8 @@
       <c r="AS10" t="str">
         <v/>
       </c>
-      <c r="AT10" t="str">
-        <v/>
+      <c r="AT10" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU10" t="str">
         <v/>
@@ -2667,8 +2721,8 @@
       <c r="AZ10" t="str">
         <v/>
       </c>
-      <c r="BA10" t="str">
-        <v/>
+      <c r="BA10" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB10" t="str">
         <v/>
@@ -2822,8 +2876,8 @@
       <c r="AS11" t="str">
         <v/>
       </c>
-      <c r="AT11" t="str">
-        <v/>
+      <c r="AT11" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU11" t="str">
         <v/>
@@ -2843,8 +2897,8 @@
       <c r="AZ11" t="str">
         <v/>
       </c>
-      <c r="BA11" t="str">
-        <v/>
+      <c r="BA11" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB11" t="str">
         <v/>
@@ -2998,8 +3052,8 @@
       <c r="AS12" t="str">
         <v/>
       </c>
-      <c r="AT12" t="str">
-        <v/>
+      <c r="AT12" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU12" t="str">
         <v/>
@@ -3019,8 +3073,8 @@
       <c r="AZ12" t="str">
         <v/>
       </c>
-      <c r="BA12" t="str">
-        <v/>
+      <c r="BA12" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB12" t="str">
         <v/>
@@ -3174,8 +3228,8 @@
       <c r="AS13" t="str">
         <v/>
       </c>
-      <c r="AT13" t="str">
-        <v/>
+      <c r="AT13" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU13" t="str">
         <v/>
@@ -3195,8 +3249,8 @@
       <c r="AZ13" t="str">
         <v/>
       </c>
-      <c r="BA13" t="str">
-        <v/>
+      <c r="BA13" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB13" t="str">
         <v/>
@@ -3278,8 +3332,8 @@
       <c r="U14" t="str">
         <v/>
       </c>
-      <c r="V14" t="str">
-        <v/>
+      <c r="V14" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W14" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -3296,11 +3350,11 @@
       <c r="AA14" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB14" t="str">
-        <v/>
-      </c>
-      <c r="AC14" t="str">
-        <v/>
+      <c r="AB14" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC14" t="str" s="1">
+        <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
       <c r="AD14" t="str" s="1">
         <v>Magnesium</v>
@@ -3350,8 +3404,8 @@
       <c r="AS14" t="str">
         <v/>
       </c>
-      <c r="AT14" t="str">
-        <v/>
+      <c r="AT14" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU14" t="str">
         <v/>
@@ -3371,8 +3425,8 @@
       <c r="AZ14" t="str">
         <v/>
       </c>
-      <c r="BA14" t="str">
-        <v/>
+      <c r="BA14" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB14" t="str">
         <v/>
@@ -3454,8 +3508,8 @@
       <c r="U15" t="str">
         <v/>
       </c>
-      <c r="V15" t="str">
-        <v/>
+      <c r="V15" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W15" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -3472,11 +3526,11 @@
       <c r="AA15" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB15" t="str">
-        <v/>
-      </c>
-      <c r="AC15" t="str">
-        <v/>
+      <c r="AB15" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC15" t="str" s="1">
+        <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
       <c r="AD15" t="str" s="1">
         <v>Magnesium</v>
@@ -3526,8 +3580,8 @@
       <c r="AS15" t="str">
         <v/>
       </c>
-      <c r="AT15" t="str">
-        <v/>
+      <c r="AT15" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU15" t="str">
         <v/>
@@ -3547,8 +3601,8 @@
       <c r="AZ15" t="str">
         <v/>
       </c>
-      <c r="BA15" t="str">
-        <v/>
+      <c r="BA15" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB15" t="str">
         <v/>
@@ -3630,8 +3684,8 @@
       <c r="U16" t="str">
         <v/>
       </c>
-      <c r="V16" t="str">
-        <v/>
+      <c r="V16" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W16" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -3648,11 +3702,11 @@
       <c r="AA16" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB16" t="str">
-        <v/>
-      </c>
-      <c r="AC16" t="str">
-        <v/>
+      <c r="AB16" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC16" t="str" s="1">
+        <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
       <c r="AD16" t="str" s="1">
         <v>Magnesium</v>
@@ -3702,8 +3756,8 @@
       <c r="AS16" t="str">
         <v/>
       </c>
-      <c r="AT16" t="str">
-        <v/>
+      <c r="AT16" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU16" t="str">
         <v/>
@@ -3723,8 +3777,8 @@
       <c r="AZ16" t="str">
         <v/>
       </c>
-      <c r="BA16" t="str">
-        <v/>
+      <c r="BA16" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB16" t="str">
         <v/>
@@ -3806,8 +3860,8 @@
       <c r="U17" t="str">
         <v/>
       </c>
-      <c r="V17" t="str">
-        <v/>
+      <c r="V17" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W17" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -3824,11 +3878,11 @@
       <c r="AA17" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB17" t="str">
-        <v/>
-      </c>
-      <c r="AC17" t="str">
-        <v/>
+      <c r="AB17" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC17" t="str" s="1">
+        <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
       <c r="AD17" t="str" s="1">
         <v>Magnesium</v>
@@ -3878,8 +3932,8 @@
       <c r="AS17" t="str">
         <v/>
       </c>
-      <c r="AT17" t="str">
-        <v/>
+      <c r="AT17" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU17" t="str">
         <v/>
@@ -3899,8 +3953,8 @@
       <c r="AZ17" t="str">
         <v/>
       </c>
-      <c r="BA17" t="str">
-        <v/>
+      <c r="BA17" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB17" t="str">
         <v/>
@@ -3982,8 +4036,8 @@
       <c r="U18" t="str">
         <v/>
       </c>
-      <c r="V18" t="str">
-        <v/>
+      <c r="V18" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W18" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -4000,11 +4054,11 @@
       <c r="AA18" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB18" t="str">
-        <v/>
-      </c>
-      <c r="AC18" t="str">
-        <v/>
+      <c r="AB18" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC18" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="AD18" t="str" s="1">
         <v>Magnesium</v>
@@ -4054,8 +4108,8 @@
       <c r="AS18" t="str">
         <v/>
       </c>
-      <c r="AT18" t="str">
-        <v/>
+      <c r="AT18" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU18" t="str">
         <v/>
@@ -4075,8 +4129,8 @@
       <c r="AZ18" t="str">
         <v/>
       </c>
-      <c r="BA18" t="str">
-        <v/>
+      <c r="BA18" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB18" t="str">
         <v/>
@@ -4158,8 +4212,8 @@
       <c r="U19" t="str">
         <v/>
       </c>
-      <c r="V19" t="str">
-        <v/>
+      <c r="V19" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W19" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -4176,11 +4230,11 @@
       <c r="AA19" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB19" t="str">
-        <v/>
-      </c>
-      <c r="AC19" t="str">
-        <v/>
+      <c r="AB19" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC19" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="AD19" t="str" s="1">
         <v>Magnesium</v>
@@ -4230,8 +4284,8 @@
       <c r="AS19" t="str">
         <v/>
       </c>
-      <c r="AT19" t="str">
-        <v/>
+      <c r="AT19" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU19" t="str">
         <v/>
@@ -4251,8 +4305,8 @@
       <c r="AZ19" t="str">
         <v/>
       </c>
-      <c r="BA19" t="str">
-        <v/>
+      <c r="BA19" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB19" t="str">
         <v/>
@@ -4334,8 +4388,8 @@
       <c r="U20" t="str">
         <v/>
       </c>
-      <c r="V20" t="str">
-        <v/>
+      <c r="V20" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W20" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -4352,11 +4406,11 @@
       <c r="AA20" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB20" t="str">
-        <v/>
-      </c>
-      <c r="AC20" t="str">
-        <v/>
+      <c r="AB20" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC20" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="AD20" t="str" s="1">
         <v>Magnesium</v>
@@ -4406,8 +4460,8 @@
       <c r="AS20" t="str">
         <v/>
       </c>
-      <c r="AT20" t="str">
-        <v/>
+      <c r="AT20" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU20" t="str">
         <v/>
@@ -4427,8 +4481,8 @@
       <c r="AZ20" t="str">
         <v/>
       </c>
-      <c r="BA20" t="str">
-        <v/>
+      <c r="BA20" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB20" t="str">
         <v/>
@@ -4510,8 +4564,8 @@
       <c r="U21" t="str">
         <v/>
       </c>
-      <c r="V21" t="str">
-        <v/>
+      <c r="V21" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="W21" t="str" s="1">
         <v>4x7x2.5（stock）</v>
@@ -4528,11 +4582,11 @@
       <c r="AA21" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB21" t="str">
-        <v/>
-      </c>
-      <c r="AC21" t="str">
-        <v/>
+      <c r="AB21" t="str" s="1">
+        <v>lightweight slim knob</v>
+      </c>
+      <c r="AC21" t="str" s="1">
+        <v>S size / lightweight slim knob</v>
       </c>
       <c r="AD21" t="str" s="1">
         <v>Magnesium</v>
@@ -4582,8 +4636,8 @@
       <c r="AS21" t="str">
         <v/>
       </c>
-      <c r="AT21" t="str">
-        <v/>
+      <c r="AT21" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU21" t="str">
         <v/>
@@ -4603,8 +4657,8 @@
       <c r="AZ21" t="str">
         <v/>
       </c>
-      <c r="BA21" t="str">
-        <v/>
+      <c r="BA21" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB21" t="str">
         <v/>
@@ -4758,8 +4812,8 @@
       <c r="AS22" t="str">
         <v/>
       </c>
-      <c r="AT22" t="str">
-        <v/>
+      <c r="AT22" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU22" t="str">
         <v/>
@@ -4779,8 +4833,8 @@
       <c r="AZ22" t="str">
         <v/>
       </c>
-      <c r="BA22" t="str">
-        <v/>
+      <c r="BA22" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB22" t="str" s="1">
         <v>Brass</v>
@@ -4934,8 +4988,8 @@
       <c r="AS23" t="str">
         <v/>
       </c>
-      <c r="AT23" t="str">
-        <v/>
+      <c r="AT23" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU23" t="str">
         <v/>
@@ -4955,8 +5009,8 @@
       <c r="AZ23" t="str">
         <v/>
       </c>
-      <c r="BA23" t="str">
-        <v/>
+      <c r="BA23" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB23" t="str" s="1">
         <v>Brass</v>
@@ -5110,8 +5164,8 @@
       <c r="AS24" t="str">
         <v/>
       </c>
-      <c r="AT24" t="str">
-        <v/>
+      <c r="AT24" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU24" t="str">
         <v/>
@@ -5131,8 +5185,8 @@
       <c r="AZ24" t="str">
         <v/>
       </c>
-      <c r="BA24" t="str">
-        <v/>
+      <c r="BA24" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB24" t="str" s="1">
         <v>Brass</v>
@@ -5286,8 +5340,8 @@
       <c r="AS25" t="str">
         <v/>
       </c>
-      <c r="AT25" t="str">
-        <v/>
+      <c r="AT25" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU25" t="str">
         <v/>
@@ -5307,8 +5361,8 @@
       <c r="AZ25" t="str">
         <v/>
       </c>
-      <c r="BA25" t="str">
-        <v/>
+      <c r="BA25" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB25" t="str" s="1">
         <v>Brass</v>
@@ -5462,8 +5516,8 @@
       <c r="AS26" t="str">
         <v/>
       </c>
-      <c r="AT26" t="str">
-        <v/>
+      <c r="AT26" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU26" t="str">
         <v/>
@@ -5483,8 +5537,8 @@
       <c r="AZ26" t="str">
         <v/>
       </c>
-      <c r="BA26" t="str">
-        <v/>
+      <c r="BA26" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB26" t="str" s="1">
         <v>Brass</v>
@@ -5638,8 +5692,8 @@
       <c r="AS27" t="str">
         <v/>
       </c>
-      <c r="AT27" t="str">
-        <v/>
+      <c r="AT27" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU27" t="str">
         <v/>
@@ -5659,8 +5713,8 @@
       <c r="AZ27" t="str">
         <v/>
       </c>
-      <c r="BA27" t="str">
-        <v/>
+      <c r="BA27" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB27" t="str" s="1">
         <v>Brass</v>
@@ -5814,8 +5868,8 @@
       <c r="AS28" t="str">
         <v/>
       </c>
-      <c r="AT28" t="str">
-        <v/>
+      <c r="AT28" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU28" t="str">
         <v/>
@@ -5835,8 +5889,8 @@
       <c r="AZ28" t="str">
         <v/>
       </c>
-      <c r="BA28" t="str">
-        <v/>
+      <c r="BA28" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB28" t="str" s="1">
         <v>Brass</v>
@@ -5990,8 +6044,8 @@
       <c r="AS29" t="str">
         <v/>
       </c>
-      <c r="AT29" t="str">
-        <v/>
+      <c r="AT29" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU29" t="str">
         <v/>
@@ -6011,8 +6065,8 @@
       <c r="AZ29" t="str">
         <v/>
       </c>
-      <c r="BA29" t="str">
-        <v/>
+      <c r="BA29" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB29" t="str" s="1">
         <v>Brass</v>
@@ -6166,8 +6220,8 @@
       <c r="AS30" t="str">
         <v/>
       </c>
-      <c r="AT30" t="str">
-        <v/>
+      <c r="AT30" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU30" t="str">
         <v/>
@@ -6187,8 +6241,8 @@
       <c r="AZ30" t="str">
         <v/>
       </c>
-      <c r="BA30" t="str">
-        <v/>
+      <c r="BA30" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB30" t="str" s="1">
         <v>Brass</v>
@@ -6342,8 +6396,8 @@
       <c r="AS31" t="str">
         <v/>
       </c>
-      <c r="AT31" t="str">
-        <v/>
+      <c r="AT31" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU31" t="str">
         <v/>
@@ -6363,8 +6417,8 @@
       <c r="AZ31" t="str">
         <v/>
       </c>
-      <c r="BA31" t="str">
-        <v/>
+      <c r="BA31" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB31" t="str" s="1">
         <v>Brass</v>
@@ -6467,8 +6521,8 @@
       <c r="AB32" t="str">
         <v/>
       </c>
-      <c r="AC32" t="str">
-        <v/>
+      <c r="AC32" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD32" t="str" s="1">
         <v>Magnesium</v>
@@ -6518,8 +6572,8 @@
       <c r="AS32" t="str">
         <v/>
       </c>
-      <c r="AT32" t="str">
-        <v/>
+      <c r="AT32" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU32" t="str">
         <v/>
@@ -6539,8 +6593,8 @@
       <c r="AZ32" t="str">
         <v/>
       </c>
-      <c r="BA32" t="str">
-        <v/>
+      <c r="BA32" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB32" t="str">
         <v>Brass</v>
@@ -6643,8 +6697,8 @@
       <c r="AB33" t="str">
         <v/>
       </c>
-      <c r="AC33" t="str">
-        <v/>
+      <c r="AC33" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD33" t="str" s="1">
         <v>Magnesium</v>
@@ -6694,8 +6748,8 @@
       <c r="AS33" t="str">
         <v/>
       </c>
-      <c r="AT33" t="str">
-        <v/>
+      <c r="AT33" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU33" t="str">
         <v/>
@@ -6715,8 +6769,8 @@
       <c r="AZ33" t="str">
         <v/>
       </c>
-      <c r="BA33" t="str">
-        <v/>
+      <c r="BA33" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB33" t="str">
         <v>Brass</v>
@@ -6819,8 +6873,8 @@
       <c r="AB34" t="str">
         <v/>
       </c>
-      <c r="AC34" t="str">
-        <v/>
+      <c r="AC34" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD34" t="str" s="1">
         <v>Magnesium</v>
@@ -6870,8 +6924,8 @@
       <c r="AS34" t="str">
         <v/>
       </c>
-      <c r="AT34" t="str">
-        <v/>
+      <c r="AT34" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU34" t="str">
         <v/>
@@ -6891,8 +6945,8 @@
       <c r="AZ34" t="str">
         <v/>
       </c>
-      <c r="BA34" t="str">
-        <v/>
+      <c r="BA34" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB34" t="str">
         <v>Brass</v>
@@ -6995,8 +7049,8 @@
       <c r="AB35" t="str">
         <v/>
       </c>
-      <c r="AC35" t="str">
-        <v/>
+      <c r="AC35" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD35" t="str" s="1">
         <v>Magnesium</v>
@@ -7046,8 +7100,8 @@
       <c r="AS35" t="str">
         <v/>
       </c>
-      <c r="AT35" t="str">
-        <v/>
+      <c r="AT35" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU35" t="str">
         <v/>
@@ -7067,8 +7121,8 @@
       <c r="AZ35" t="str">
         <v/>
       </c>
-      <c r="BA35" t="str">
-        <v/>
+      <c r="BA35" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB35" t="str">
         <v>Brass</v>
@@ -7171,8 +7225,8 @@
       <c r="AB36" t="str">
         <v/>
       </c>
-      <c r="AC36" t="str">
-        <v/>
+      <c r="AC36" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD36" t="str" s="1">
         <v>Magnesium</v>
@@ -7222,8 +7276,8 @@
       <c r="AS36" t="str">
         <v/>
       </c>
-      <c r="AT36" t="str">
-        <v/>
+      <c r="AT36" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU36" t="str">
         <v/>
@@ -7243,8 +7297,8 @@
       <c r="AZ36" t="str">
         <v/>
       </c>
-      <c r="BA36" t="str">
-        <v/>
+      <c r="BA36" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB36" t="str">
         <v>Brass</v>
@@ -7347,8 +7401,8 @@
       <c r="AB37" t="str">
         <v/>
       </c>
-      <c r="AC37" t="str">
-        <v/>
+      <c r="AC37" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD37" t="str" s="1">
         <v>Magnesium</v>
@@ -7398,8 +7452,8 @@
       <c r="AS37" t="str">
         <v/>
       </c>
-      <c r="AT37" t="str">
-        <v/>
+      <c r="AT37" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU37" t="str">
         <v/>
@@ -7419,8 +7473,8 @@
       <c r="AZ37" t="str">
         <v/>
       </c>
-      <c r="BA37" t="str">
-        <v/>
+      <c r="BA37" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB37" t="str">
         <v>Brass</v>
@@ -7523,8 +7577,8 @@
       <c r="AB38" t="str">
         <v/>
       </c>
-      <c r="AC38" t="str">
-        <v/>
+      <c r="AC38" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD38" t="str" s="1">
         <v>Magnesium</v>
@@ -7574,8 +7628,8 @@
       <c r="AS38" t="str">
         <v/>
       </c>
-      <c r="AT38" t="str">
-        <v/>
+      <c r="AT38" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU38" t="str">
         <v/>
@@ -7595,8 +7649,8 @@
       <c r="AZ38" t="str">
         <v/>
       </c>
-      <c r="BA38" t="str">
-        <v/>
+      <c r="BA38" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB38" t="str">
         <v>Brass</v>
@@ -7699,8 +7753,8 @@
       <c r="AB39" t="str">
         <v/>
       </c>
-      <c r="AC39" t="str">
-        <v/>
+      <c r="AC39" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD39" t="str" s="1">
         <v>Magnesium</v>
@@ -7750,8 +7804,8 @@
       <c r="AS39" t="str">
         <v/>
       </c>
-      <c r="AT39" t="str">
-        <v/>
+      <c r="AT39" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU39" t="str">
         <v/>
@@ -7771,8 +7825,8 @@
       <c r="AZ39" t="str">
         <v/>
       </c>
-      <c r="BA39" t="str">
-        <v/>
+      <c r="BA39" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB39" t="str">
         <v>Brass</v>
@@ -7875,8 +7929,8 @@
       <c r="AB40" t="str">
         <v/>
       </c>
-      <c r="AC40" t="str">
-        <v/>
+      <c r="AC40" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD40" t="str" s="1">
         <v>Magnesium</v>
@@ -7926,8 +7980,8 @@
       <c r="AS40" t="str">
         <v/>
       </c>
-      <c r="AT40" t="str">
-        <v/>
+      <c r="AT40" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU40" t="str">
         <v/>
@@ -7947,8 +8001,8 @@
       <c r="AZ40" t="str">
         <v/>
       </c>
-      <c r="BA40" t="str">
-        <v/>
+      <c r="BA40" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB40" t="str">
         <v>Brass</v>
@@ -8051,8 +8105,8 @@
       <c r="AB41" t="str">
         <v/>
       </c>
-      <c r="AC41" t="str">
-        <v/>
+      <c r="AC41" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD41" t="str" s="1">
         <v>Magnesium</v>
@@ -8102,8 +8156,8 @@
       <c r="AS41" t="str">
         <v/>
       </c>
-      <c r="AT41" t="str">
-        <v/>
+      <c r="AT41" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU41" t="str">
         <v/>
@@ -8123,8 +8177,8 @@
       <c r="AZ41" t="str">
         <v/>
       </c>
-      <c r="BA41" t="str">
-        <v/>
+      <c r="BA41" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB41" t="str">
         <v>Brass</v>
@@ -8227,8 +8281,8 @@
       <c r="AB42" t="str">
         <v/>
       </c>
-      <c r="AC42" t="str">
-        <v/>
+      <c r="AC42" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD42" t="str" s="1">
         <v>Magnesium</v>
@@ -8278,8 +8332,8 @@
       <c r="AS42" t="str">
         <v/>
       </c>
-      <c r="AT42" t="str">
-        <v/>
+      <c r="AT42" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU42" t="str">
         <v/>
@@ -8299,8 +8353,8 @@
       <c r="AZ42" t="str">
         <v/>
       </c>
-      <c r="BA42" t="str">
-        <v/>
+      <c r="BA42" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB42" t="str">
         <v>Brass</v>
@@ -8403,8 +8457,8 @@
       <c r="AB43" t="str">
         <v/>
       </c>
-      <c r="AC43" t="str">
-        <v/>
+      <c r="AC43" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD43" t="str" s="1">
         <v>Magnesium</v>
@@ -8454,8 +8508,8 @@
       <c r="AS43" t="str">
         <v/>
       </c>
-      <c r="AT43" t="str">
-        <v/>
+      <c r="AT43" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU43" t="str">
         <v/>
@@ -8475,8 +8529,8 @@
       <c r="AZ43" t="str">
         <v/>
       </c>
-      <c r="BA43" t="str">
-        <v/>
+      <c r="BA43" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB43" t="str">
         <v>Brass</v>
@@ -8579,8 +8633,8 @@
       <c r="AB44" t="str">
         <v/>
       </c>
-      <c r="AC44" t="str">
-        <v/>
+      <c r="AC44" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD44" t="str" s="1">
         <v>Magnesium</v>
@@ -8630,8 +8684,8 @@
       <c r="AS44" t="str">
         <v/>
       </c>
-      <c r="AT44" t="str">
-        <v/>
+      <c r="AT44" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU44" t="str">
         <v/>
@@ -8651,8 +8705,8 @@
       <c r="AZ44" t="str">
         <v/>
       </c>
-      <c r="BA44" t="str">
-        <v/>
+      <c r="BA44" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB44" t="str">
         <v>Brass</v>
@@ -8755,8 +8809,8 @@
       <c r="AB45" t="str">
         <v/>
       </c>
-      <c r="AC45" t="str">
-        <v/>
+      <c r="AC45" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD45" t="str" s="1">
         <v>Magnesium</v>
@@ -8806,8 +8860,8 @@
       <c r="AS45" t="str">
         <v/>
       </c>
-      <c r="AT45" t="str">
-        <v/>
+      <c r="AT45" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU45" t="str">
         <v/>
@@ -8827,8 +8881,8 @@
       <c r="AZ45" t="str">
         <v/>
       </c>
-      <c r="BA45" t="str">
-        <v/>
+      <c r="BA45" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB45" t="str">
         <v>Brass</v>
@@ -8931,8 +8985,8 @@
       <c r="AB46" t="str">
         <v/>
       </c>
-      <c r="AC46" t="str">
-        <v/>
+      <c r="AC46" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD46" t="str" s="1">
         <v>Magnesium</v>
@@ -8982,8 +9036,8 @@
       <c r="AS46" t="str">
         <v/>
       </c>
-      <c r="AT46" t="str">
-        <v/>
+      <c r="AT46" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU46" t="str">
         <v/>
@@ -9003,8 +9057,8 @@
       <c r="AZ46" t="str">
         <v/>
       </c>
-      <c r="BA46" t="str">
-        <v/>
+      <c r="BA46" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB46" t="str">
         <v>Brass</v>
@@ -9107,8 +9161,8 @@
       <c r="AB47" t="str">
         <v/>
       </c>
-      <c r="AC47" t="str">
-        <v/>
+      <c r="AC47" t="str" s="1">
+        <v>HKC-20MT</v>
       </c>
       <c r="AD47" t="str" s="1">
         <v>Magnesium</v>
@@ -9158,8 +9212,8 @@
       <c r="AS47" t="str">
         <v/>
       </c>
-      <c r="AT47" t="str">
-        <v/>
+      <c r="AT47" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU47" t="str">
         <v/>
@@ -9179,8 +9233,8 @@
       <c r="AZ47" t="str">
         <v/>
       </c>
-      <c r="BA47" t="str">
-        <v/>
+      <c r="BA47" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB47" t="str">
         <v>Brass</v>
@@ -9334,8 +9388,8 @@
       <c r="AS48" t="str">
         <v>是</v>
       </c>
-      <c r="AT48" t="str">
-        <v/>
+      <c r="AT48" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU48" t="str">
         <v/>
@@ -9355,8 +9409,8 @@
       <c r="AZ48" t="str">
         <v/>
       </c>
-      <c r="BA48" t="str">
-        <v/>
+      <c r="BA48" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB48" t="str" s="1">
         <v>Brass</v>
@@ -9510,8 +9564,8 @@
       <c r="AS49" t="str">
         <v>是</v>
       </c>
-      <c r="AT49" t="str">
-        <v/>
+      <c r="AT49" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU49" t="str">
         <v/>
@@ -9531,8 +9585,8 @@
       <c r="AZ49" t="str">
         <v/>
       </c>
-      <c r="BA49" t="str">
-        <v/>
+      <c r="BA49" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB49" t="str" s="1">
         <v>Brass</v>
@@ -9686,8 +9740,8 @@
       <c r="AS50" t="str">
         <v>是</v>
       </c>
-      <c r="AT50" t="str">
-        <v/>
+      <c r="AT50" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU50" t="str">
         <v/>
@@ -9707,8 +9761,8 @@
       <c r="AZ50" t="str">
         <v/>
       </c>
-      <c r="BA50" t="str">
-        <v/>
+      <c r="BA50" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB50" t="str" s="1">
         <v>Brass</v>
@@ -9862,8 +9916,8 @@
       <c r="AS51" t="str">
         <v>是</v>
       </c>
-      <c r="AT51" t="str">
-        <v/>
+      <c r="AT51" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU51" t="str">
         <v/>
@@ -9883,8 +9937,8 @@
       <c r="AZ51" t="str">
         <v/>
       </c>
-      <c r="BA51" t="str">
-        <v/>
+      <c r="BA51" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB51" t="str" s="1">
         <v>Brass</v>
@@ -10038,8 +10092,8 @@
       <c r="AS52" t="str">
         <v>是</v>
       </c>
-      <c r="AT52" t="str">
-        <v/>
+      <c r="AT52" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU52" t="str">
         <v/>
@@ -10059,8 +10113,8 @@
       <c r="AZ52" t="str">
         <v/>
       </c>
-      <c r="BA52" t="str">
-        <v/>
+      <c r="BA52" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB52" t="str" s="1">
         <v>Brass</v>
@@ -10214,8 +10268,8 @@
       <c r="AS53" t="str">
         <v>是</v>
       </c>
-      <c r="AT53" t="str">
-        <v/>
+      <c r="AT53" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU53" t="str">
         <v/>
@@ -10235,8 +10289,8 @@
       <c r="AZ53" t="str">
         <v/>
       </c>
-      <c r="BA53" t="str">
-        <v/>
+      <c r="BA53" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB53" t="str" s="1">
         <v>Brass</v>
@@ -10390,8 +10444,8 @@
       <c r="AS54" t="str">
         <v/>
       </c>
-      <c r="AT54" t="str">
-        <v/>
+      <c r="AT54" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU54" t="str">
         <v/>
@@ -10411,8 +10465,8 @@
       <c r="AZ54" t="str">
         <v/>
       </c>
-      <c r="BA54" t="str">
-        <v/>
+      <c r="BA54" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB54" t="str" s="1">
         <v>Brass</v>
@@ -10566,8 +10620,8 @@
       <c r="AS55" t="str">
         <v/>
       </c>
-      <c r="AT55" t="str">
-        <v/>
+      <c r="AT55" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU55" t="str">
         <v/>
@@ -10587,8 +10641,8 @@
       <c r="AZ55" t="str">
         <v/>
       </c>
-      <c r="BA55" t="str">
-        <v/>
+      <c r="BA55" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB55" t="str" s="1">
         <v>Brass</v>
@@ -10742,8 +10796,8 @@
       <c r="AS56" t="str">
         <v/>
       </c>
-      <c r="AT56" t="str">
-        <v/>
+      <c r="AT56" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU56" t="str">
         <v/>
@@ -10763,8 +10817,8 @@
       <c r="AZ56" t="str">
         <v/>
       </c>
-      <c r="BA56" t="str">
-        <v/>
+      <c r="BA56" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB56" t="str" s="1">
         <v>Brass</v>
@@ -10918,8 +10972,8 @@
       <c r="AS57" t="str">
         <v/>
       </c>
-      <c r="AT57" t="str">
-        <v/>
+      <c r="AT57" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU57" t="str">
         <v/>
@@ -10939,8 +10993,8 @@
       <c r="AZ57" t="str">
         <v/>
       </c>
-      <c r="BA57" t="str">
-        <v/>
+      <c r="BA57" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB57" t="str" s="1">
         <v>Brass</v>
@@ -11094,8 +11148,8 @@
       <c r="AS58" t="str">
         <v/>
       </c>
-      <c r="AT58" t="str">
-        <v/>
+      <c r="AT58" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU58" t="str">
         <v/>
@@ -11115,8 +11169,8 @@
       <c r="AZ58" t="str" s="1">
         <v>EVA</v>
       </c>
-      <c r="BA58" t="str">
-        <v/>
+      <c r="BA58" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB58" t="str">
         <v/>
@@ -11270,8 +11324,8 @@
       <c r="AS59" t="str">
         <v/>
       </c>
-      <c r="AT59" t="str">
-        <v/>
+      <c r="AT59" t="str" s="1">
+        <v>单摇臂</v>
       </c>
       <c r="AU59" t="str">
         <v/>
@@ -11291,8 +11345,8 @@
       <c r="AZ59" t="str" s="1">
         <v>EVA</v>
       </c>
-      <c r="BA59" t="str">
-        <v/>
+      <c r="BA59" t="str" s="1">
+        <v>M7</v>
       </c>
       <c r="BB59" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -49,18 +49,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF59D"/>
-        <bgColor rgb="FFF59D"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -75,9 +69,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,8 +401,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,7 +468,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -489,10 +482,10 @@
       <c r="E2" t="str">
         <v/>
       </c>
-      <c r="F2" t="str" s="1">
+      <c r="F2" t="str">
         <v>2024</v>
       </c>
-      <c r="G2" t="str" s="1">
+      <c r="G2" t="str">
         <v>24 SLX 70</v>
       </c>
       <c r="H2" t="str">
@@ -502,7 +495,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J2" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX_main.jpg</v>
+        <v>https://dassets2.shimano.com/content/dam/Shimanofish/Common/Productsrelated/cg2SHIFGlobalREEL/cg3SHIFGlobalREELBaitReel/SICPlanningProducts/Product/PRD_a075F000042PnchQAC_main.jpg/jcr:content/renditions/cq5dam.web.481.481.jpeg</v>
       </c>
       <c r="K2" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -510,10 +503,10 @@
       <c r="L2" t="str">
         <v>2026-04-15 02:14:15</v>
       </c>
-      <c r="M2" t="str" s="1">
+      <c r="M2" t="str">
         <v>泛用入门</v>
       </c>
-      <c r="N2" t="str" s="1">
+      <c r="N2" t="str">
         <v>MGL III / 紧凑机身 / 入门泛用</v>
       </c>
       <c r="O2" t="str">
@@ -528,16 +521,16 @@
       <c r="R2" t="str">
         <v/>
       </c>
-      <c r="S2" t="str" s="1">
+      <c r="S2" t="str">
         <v>泛用入门水滴轮</v>
       </c>
-      <c r="T2" t="str" s="1">
+      <c r="T2" t="str">
         <v>性价比高 / MGL III / 泛用覆盖</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SRE5025</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -546,16 +539,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="str">
-        <v>ALDEBARAN BFS</v>
-      </c>
-      <c r="E3" t="str" s="1">
-        <v>阿德巴兰 BFS</v>
-      </c>
-      <c r="F3" t="str" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G3" t="str" s="1">
-        <v>22 Aldebaran BFS</v>
+        <v>SLX XT</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>2024</v>
+      </c>
+      <c r="G3" t="str">
+        <v>24 SLX XT 150</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -564,42 +557,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J3" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpg</v>
+        <v>https://dassets2.shimano.com/content/dam/Shimanofish/Common/Productsrelated/cg2SHIFGlobalREEL/cg3SHIFGlobalREELBaitReel/SICPlanningProducts/Product/PRD_a075F00003c623mQAA_main.jpg/jcr:content/renditions/cq5dam.web.481.481.jpeg</v>
       </c>
       <c r="K3" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-04-15 02:13:31</v>
-      </c>
-      <c r="M3" t="str" s="1">
-        <v>极致BFS</v>
-      </c>
-      <c r="N3" t="str" s="1">
-        <v>FTB / 超轻量线杯 / 轻饵特化</v>
+        <v>2026-04-15 02:14:15</v>
+      </c>
+      <c r="M3" t="str">
+        <v>泛用入门</v>
+      </c>
+      <c r="N3" t="str">
+        <v>HAGANE机身 / SILENTTUNE / 高性价比</v>
       </c>
       <c r="O3" t="str">
-        <v>¥2,604</v>
+        <v>¥697 - ¥1,181</v>
       </c>
       <c r="P3" t="str">
         <v>在售</v>
       </c>
       <c r="Q3" t="str">
-        <v>ALDEBARAN BFS搭载了第一次在SHIMANO BFS渔轮上运用的MGLⅢ技术。专门为BFS设计的低惯性线杯将在轻钓组的世界里掀起一场风暴。采用不易炸线的FTB磁刹系统。不在线杯上配置刹车单位配件，使其低惯性化，相比过去刹车单位配件行程拉长，使刹车更易调节。此外，新配置的磁环在最小刹车力时能够吸收磁力的影响，即使抖动抛投假饵弹道也不易上浮，彷如在水面上爬行般达到结构钓点的深处。此外，其重量仅130g，满载了MICROMODULE GEAR和EXCITING DRAG SOUND等先进技术。于是高性价比的ALDEBARAN诞生了。</v>
-      </c>
-      <c r="R3" t="str" s="1">
-        <v>49900JPY</v>
-      </c>
-      <c r="S3" t="str" s="1">
-        <v>BFS轻饵特化旗舰</v>
-      </c>
-      <c r="T3" t="str" s="1">
-        <v>超轻线杯 / FTB / 轻饵上限高</v>
+        <v>SLX搭载SILENTTUNE后升级，更顺滑的收线手感，HAGANE机身则确保了机身强度，非常高性价比的一款产品。</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v>泛用入门水滴轮</v>
+      </c>
+      <c r="T3" t="str">
+        <v>入门友好 / 更强容线量 / 泛用覆盖</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SRE5026</v>
+        <v>SRE5025</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -608,16 +601,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>ALDEBARAN MGL</v>
-      </c>
-      <c r="E4" t="str" s="1">
-        <v>阿德巴兰 MGL</v>
-      </c>
-      <c r="F4" t="str" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G4" t="str" s="1">
-        <v>18 Aldebaran MGL</v>
+        <v>ALDEBARAN BFS</v>
+      </c>
+      <c r="E4" t="str">
+        <v>阿德巴兰 BFS</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G4" t="str">
+        <v>22 Aldebaran BFS</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -626,42 +619,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J4" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpg</v>
       </c>
       <c r="K4" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-04-15 02:13:33</v>
-      </c>
-      <c r="M4" t="str" s="1">
-        <v>轻量泛用技巧</v>
-      </c>
-      <c r="N4" t="str" s="1">
-        <v>浅溝轻量线杯 / 轻饵泛用 / 低姿态机身</v>
+        <v>2026-04-15 02:13:31</v>
+      </c>
+      <c r="M4" t="str">
+        <v>极致BFS</v>
+      </c>
+      <c r="N4" t="str">
+        <v>FTB / 超轻量线杯 / 轻饵特化</v>
       </c>
       <c r="O4" t="str">
-        <v>¥2,562</v>
+        <v>¥2,604</v>
       </c>
       <c r="P4" t="str">
         <v>在售</v>
       </c>
       <c r="Q4" t="str">
-        <v>轻假饵专用的ALDEBARAN，浅杯化并搭载新设计的MagnumLITE线杯。通过在线杯侧面打孔减轻了惯性及重量，这样减少了需要控制的刹车力。轻量假饵的适应性进一步提升，提升了远投性能。轻量假饵那轻微的重量能够瞬间加速，提升抛投的距离，覆盖至微物钓的领域。</v>
-      </c>
-      <c r="R4" t="str" s="1">
-        <v>49500JPY</v>
-      </c>
-      <c r="S4" t="str" s="1">
-        <v>轻量技巧泛用</v>
-      </c>
-      <c r="T4" t="str" s="1">
-        <v>低姿态轻量 / MGL线杯 / 技巧泛用</v>
+        <v>ALDEBARAN BFS搭载了第一次在SHIMANO BFS渔轮上运用的MGLⅢ技术。专门为BFS设计的低惯性线杯将在轻钓组的世界里掀起一场风暴。采用不易炸线的FTB磁刹系统。不在线杯上配置刹车单位配件，使其低惯性化，相比过去刹车单位配件行程拉长，使刹车更易调节。此外，新配置的磁环在最小刹车力时能够吸收磁力的影响，即使抖动抛投假饵弹道也不易上浮，彷如在水面上爬行般达到结构钓点的深处。此外，其重量仅130g，满载了MICROMODULE GEAR和EXCITING DRAG SOUND等先进技术。于是高性价比的ALDEBARAN诞生了。</v>
+      </c>
+      <c r="R4" t="str">
+        <v>49900JPY</v>
+      </c>
+      <c r="S4" t="str">
+        <v>BFS轻饵特化旗舰</v>
+      </c>
+      <c r="T4" t="str">
+        <v>超轻线杯 / FTB / 轻饵上限高</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SRE5054</v>
+        <v>SRE5026</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -670,16 +663,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>CURADO</v>
-      </c>
-      <c r="E5" t="str" s="1">
-        <v>库拉多 DC</v>
-      </c>
-      <c r="F5" t="str" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G5" t="str" s="1">
-        <v>22 Curado DC</v>
+        <v>ALDEBARAN MGL</v>
+      </c>
+      <c r="E5" t="str">
+        <v>阿德巴兰 MGL</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2018</v>
+      </c>
+      <c r="G5" t="str">
+        <v>18 Aldebaran MGL</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -688,42 +681,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J5" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpg</v>
       </c>
       <c r="K5" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-04-15 02:14:08</v>
-      </c>
-      <c r="M5" t="str" s="1">
-        <v>重饵泛用</v>
-      </c>
-      <c r="N5" t="str" s="1">
-        <v>DC刹车 / 200尺寸 / 宽线杯</v>
+        <v>2026-04-15 02:13:33</v>
+      </c>
+      <c r="M5" t="str">
+        <v>轻量泛用技巧</v>
+      </c>
+      <c r="N5" t="str">
+        <v>浅溝轻量线杯 / 轻饵泛用 / 低姿态机身</v>
       </c>
       <c r="O5" t="str">
-        <v>¥1,254 - ¥1,307</v>
+        <v>¥2,562</v>
       </c>
       <c r="P5" t="str">
         <v>在售</v>
       </c>
       <c r="Q5" t="str">
-        <v>搭载第三代MGL线杯后，CURADO朝着更远的抛投距离前进，加持MICROMODULE GEAR和SILENTTUNE技术后，手感也有所提升，适合大饵的200型也是你攻略巨物的好伙伴。</v>
-      </c>
-      <c r="R5" t="str" s="1">
-        <v>33300JPY</v>
-      </c>
-      <c r="S5" t="str" s="1">
-        <v>DC重饵泛用</v>
-      </c>
-      <c r="T5" t="str" s="1">
-        <v>DC刹车 / 200尺寸 / 重饵覆盖</v>
+        <v>轻假饵专用的ALDEBARAN，浅杯化并搭载新设计的MagnumLITE线杯。通过在线杯侧面打孔减轻了惯性及重量，这样减少了需要控制的刹车力。轻量假饵的适应性进一步提升，提升了远投性能。轻量假饵那轻微的重量能够瞬间加速，提升抛投的距离，覆盖至微物钓的领域。</v>
+      </c>
+      <c r="R5" t="str">
+        <v>49500JPY</v>
+      </c>
+      <c r="S5" t="str">
+        <v>轻量技巧泛用</v>
+      </c>
+      <c r="T5" t="str">
+        <v>低姿态轻量 / MGL线杯 / 技巧泛用</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SRE5028</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -732,16 +725,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>Metanium</v>
+        <v>CURADO</v>
       </c>
       <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G6" t="str" s="1">
-        <v>20 Metanium</v>
+        <v>库拉多</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G6" t="str">
+        <v>22 CURADO 200</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -750,42 +743,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J6" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpg</v>
+        <v>https://dassets2.shimano.com/content/dam/Shimanofish/Common/Productsrelated/cg2SHIFGlobalREEL/cg3SHIFGlobalREELBaitReel/SICPlanningProducts/Product/PRD_a075F00003rGoSwQAK_main.jpg/jcr:content/renditions/cq5dam.web.481.481.jpeg</v>
       </c>
       <c r="K6" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-04-15 02:13:35</v>
-      </c>
-      <c r="M6" t="str" s="1">
-        <v>泛用技巧</v>
-      </c>
-      <c r="N6" t="str" s="1">
-        <v>CORESOLID / MGL III / 轻量泛用</v>
+        <v>2026-04-15 02:14:08</v>
+      </c>
+      <c r="M6" t="str">
+        <v>重饵泛用</v>
+      </c>
+      <c r="N6" t="str">
+        <v>MGL III线杯 / MICROMODULE GEAR / SILENTTUNE</v>
       </c>
       <c r="O6" t="str">
-        <v>¥2,457</v>
+        <v>¥1,254 - ¥1,307</v>
       </c>
       <c r="P6" t="str">
         <v>在售</v>
       </c>
       <c r="Q6" t="str">
-        <v>覆盖范围广泛的技巧款泛用规格，操作性优秀且轻量，采用镁金属一体成型的CORESOLID机身并搭载了第三代MGL线杯。轻快的操作性和坚韧的适应力，经过提升后，都能更技巧地收线打点和操控轻量假饵。另外在保证轻量的同时，采用超高强度黄铜素材的驱动齿轮，让渔轮更耐用。</v>
-      </c>
-      <c r="R6" t="str" s="1">
-        <v>48200JPY</v>
-      </c>
-      <c r="S6" t="str" s="1">
-        <v>轻量泛用旗舰</v>
-      </c>
-      <c r="T6" t="str" s="1">
-        <v>CORESOLID / 轻量机身 / 泛用上限高</v>
+        <v>搭载第三代MGL线杯后，CURADO朝着更远的抛投距离前进，加持MICROMODULE GEAR和SILENTTUNE技术后，手感也有所提升，适合大饵的200型也是你攻略巨物的好伙伴。</v>
+      </c>
+      <c r="R6" t="str">
+        <v>33300JPY</v>
+      </c>
+      <c r="S6" t="str">
+        <v>重饵泛用</v>
+      </c>
+      <c r="T6" t="str">
+        <v>200尺寸 / 卷感顺滑 / 重饵覆盖</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SRE5033</v>
+        <v>SRE5054_300</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -794,16 +787,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>Bantam</v>
-      </c>
-      <c r="E7" t="str" s="1">
-        <v>班塔姆</v>
-      </c>
-      <c r="F7" t="str" s="1">
+        <v>CURADO</v>
+      </c>
+      <c r="E7" t="str">
+        <v>库拉多</v>
+      </c>
+      <c r="F7" t="str">
         <v>2022</v>
       </c>
-      <c r="G7" t="str" s="1">
-        <v>22 Bantam</v>
+      <c r="G7" t="str">
+        <v>22 CURADO 300</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -812,42 +805,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J7" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpg</v>
+        <v>https://dassets2.shimano.com/content/dam/Shimanofish/Common/Productsrelated/cg2SHIFGlobalREEL/cg3SHIFGlobalREELBaitReel/SICPlanningProducts/Product/PRD_a075F00003HW4bGQAT_main.jpg/jcr:content/renditions/cq5dam.web.481.481.jpeg</v>
       </c>
       <c r="K7" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-04-15 02:13:42</v>
-      </c>
-      <c r="M7" t="str" s="1">
-        <v>强力泛用</v>
-      </c>
-      <c r="N7" t="str" s="1">
-        <v>35mm线杯 / CORESOLID / 黄铜齿轮</v>
+        <v>2026-04-15 02:14:08</v>
+      </c>
+      <c r="M7" t="str">
+        <v>巨物泛用</v>
+      </c>
+      <c r="N7" t="str">
+        <v>300尺寸 / 巨物覆盖 / 高端技术下放</v>
       </c>
       <c r="O7" t="str">
-        <v>¥2,184</v>
+        <v>¥1,254 - ¥1,307</v>
       </c>
       <c r="P7" t="str">
         <v>在售</v>
       </c>
       <c r="Q7" t="str">
-        <v>开拓了强力泛用轮的新世界的Bantam再次进化。新Bantam搭载了150号尺寸MGLⅢ线杯。抛竿时的轻便和舒适感彷如19 ANTARES。兼具高刚性和紧凑握感的CORE SOLID机身中，蕴藏SHIMANO第一次在水滴轮上运用的INFINITYDRIVE。减少转动阻力使其可以在全力状态下收线。将强力泛用轮带向新台阶的一款渔轮。</v>
-      </c>
-      <c r="R7" t="str" s="1">
-        <v>42600JPY</v>
-      </c>
-      <c r="S7" t="str" s="1">
-        <v>刚性强力泛用</v>
-      </c>
-      <c r="T7" t="str" s="1">
-        <v>高刚性机身 / 黄铜主齿 / 卷感扎实</v>
+        <v>汇聚SHIMANO高端技术的CURADO推出300规格。</v>
+      </c>
+      <c r="R7" t="str">
+        <v>33300JPY</v>
+      </c>
+      <c r="S7" t="str">
+        <v>重饵巨物泛用</v>
+      </c>
+      <c r="T7" t="str">
+        <v>300尺寸 / 巨物覆盖 / 容线量更大</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SRE5004</v>
+        <v>SRE5028</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -856,16 +849,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>ANTARES DC MD</v>
-      </c>
-      <c r="E8" t="str" s="1">
-        <v>安塔列斯 DC MD</v>
-      </c>
-      <c r="F8" t="str" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G8" t="str" s="1">
-        <v>23 Antares DC MD</v>
+        <v>Metanium</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>2020</v>
+      </c>
+      <c r="G8" t="str">
+        <v>20 Metanium</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -874,42 +867,42 @@
         <v>baitcasting</v>
       </c>
       <c r="J8" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="K8" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-04-15 02:13:04</v>
-      </c>
-      <c r="M8" t="str" s="1">
-        <v>巨物旗舰</v>
-      </c>
-      <c r="N8" t="str" s="1">
-        <v>MGL III / 4x8 DC MD Tune / 巨物强化</v>
+        <v>2026-04-15 02:13:35</v>
+      </c>
+      <c r="M8" t="str">
+        <v>泛用技巧</v>
+      </c>
+      <c r="N8" t="str">
+        <v>CORESOLID / MGL III / 轻量泛用</v>
       </c>
       <c r="O8" t="str">
-        <v>¥4,253</v>
+        <v>¥2,457</v>
       </c>
       <c r="P8" t="str">
         <v>在售</v>
       </c>
       <c r="Q8" t="str">
-        <v>SHIMANO FREESTYLE的巅峰，ANTARES DC MD，作为奋斗在世界舞台的旗舰产品，搭载了MGL SPOOL Ⅲ和新4X8DC MD TUNE刹车系统后，进化成了更具战斗力的规格。第三代MGL线杯带来了抛投时更轻量的手感和更优秀的抛投距离，新4X8DC MD TUNE则在刹车介入时有着更好的精度，和以往抛投时相比抛投得更远且更不易发生缠线问题。另外，搭载精密齿轮后也带来了顺滑的转动性能，在驱动齿轮轴增加支撑培林让构造更强大坚固，转动手把时也能有效降低卡顿问题，带来更顺滑的收线手感。流线美丽的机身传达出的跃动感和信赖感，不断积累厚重的历史步伐，带着更高目标并带着钓手向着高处进发，SHIMANO FREESTYLE的顶点。</v>
-      </c>
-      <c r="R8" t="str" s="1">
-        <v>62000JPY</v>
-      </c>
-      <c r="S8" t="str" s="1">
-        <v>巨物远投旗舰</v>
-      </c>
-      <c r="T8" t="str" s="1">
-        <v>4x8 DC MD Tune / 巨物向 / 宽线杯</v>
+        <v>覆盖范围广泛的技巧款泛用规格，操作性优秀且轻量，采用镁金属一体成型的CORESOLID机身并搭载了第三代MGL线杯。轻快的操作性和坚韧的适应力，经过提升后，都能更技巧地收线打点和操控轻量假饵。另外在保证轻量的同时，采用超高强度黄铜素材的驱动齿轮，让渔轮更耐用。</v>
+      </c>
+      <c r="R8" t="str">
+        <v>48200JPY</v>
+      </c>
+      <c r="S8" t="str">
+        <v>轻量泛用旗舰</v>
+      </c>
+      <c r="T8" t="str">
+        <v>CORESOLID / 轻量机身 / 泛用上限高</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SRE5002</v>
+        <v>SRE5033</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -918,16 +911,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>EXSENCE DC</v>
+        <v>Bantam</v>
       </c>
       <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str" s="1">
+        <v>班塔姆</v>
+      </c>
+      <c r="F9" t="str">
         <v>2022</v>
       </c>
-      <c r="G9" t="str" s="1">
-        <v>22 Exsence DC</v>
+      <c r="G9" t="str">
+        <v>22 Bantam</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -936,49 +929,173 @@
         <v>baitcasting</v>
       </c>
       <c r="J9" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="K9" t="str">
         <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-04-15 02:13:02</v>
-      </c>
-      <c r="M9" t="str" s="1">
-        <v>海鲈远投特化</v>
-      </c>
-      <c r="N9" t="str" s="1">
-        <v>4x8 DC Exsence Tune / 海鲈远投 / PE 线路亚</v>
+        <v>2026-04-15 02:13:42</v>
+      </c>
+      <c r="M9" t="str">
+        <v>强力泛用</v>
+      </c>
+      <c r="N9" t="str">
+        <v>35mm线杯 / CORESOLID / 黄铜齿轮</v>
       </c>
       <c r="O9" t="str">
-        <v>¥4,284</v>
+        <v>¥2,184</v>
       </c>
       <c r="P9" t="str">
         <v>在售</v>
       </c>
       <c r="Q9" t="str">
+        <v>开拓了强力泛用轮的新世界的Bantam再次进化。新Bantam搭载了150号尺寸MGLⅢ线杯。抛竿时的轻便和舒适感彷如19 ANTARES。兼具高刚性和紧凑握感的CORE SOLID机身中，蕴藏SHIMANO第一次在水滴轮上运用的INFINITYDRIVE。减少转动阻力使其可以在全力状态下收线。将强力泛用轮带向新台阶的一款渔轮。</v>
+      </c>
+      <c r="R9" t="str">
+        <v>42600JPY</v>
+      </c>
+      <c r="S9" t="str">
+        <v>刚性强力泛用</v>
+      </c>
+      <c r="T9" t="str">
+        <v>高刚性机身 / 黄铜主齿 / 卷感扎实</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SRE5004</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ANTARES DC MD</v>
+      </c>
+      <c r="E10" t="str">
+        <v>安塔列斯 DC MD</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2023</v>
+      </c>
+      <c r="G10" t="str">
+        <v>23 Antares DC MD</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J10" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-04-10 00:51:20</v>
+      </c>
+      <c r="L10" t="str">
+        <v>2026-04-15 02:13:04</v>
+      </c>
+      <c r="M10" t="str">
+        <v>巨物旗舰</v>
+      </c>
+      <c r="N10" t="str">
+        <v>MGL III / 4x8 DC MD Tune / 巨物强化</v>
+      </c>
+      <c r="O10" t="str">
+        <v>¥4,253</v>
+      </c>
+      <c r="P10" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>SHIMANO FREESTYLE的巅峰，ANTARES DC MD，作为奋斗在世界舞台的旗舰产品，搭载了MGL SPOOL Ⅲ和新4X8DC MD TUNE刹车系统后，进化成了更具战斗力的规格。第三代MGL线杯带来了抛投时更轻量的手感和更优秀的抛投距离，新4X8DC MD TUNE则在刹车介入时有着更好的精度，和以往抛投时相比抛投得更远且更不易发生缠线问题。另外，搭载精密齿轮后也带来了顺滑的转动性能，在驱动齿轮轴增加支撑培林让构造更强大坚固，转动手把时也能有效降低卡顿问题，带来更顺滑的收线手感。流线美丽的机身传达出的跃动感和信赖感，不断积累厚重的历史步伐，带着更高目标并带着钓手向着高处进发，SHIMANO FREESTYLE的顶点。</v>
+      </c>
+      <c r="R10" t="str">
+        <v>62000JPY</v>
+      </c>
+      <c r="S10" t="str">
+        <v>巨物远投旗舰</v>
+      </c>
+      <c r="T10" t="str">
+        <v>4x8 DC MD Tune / 巨物向 / 宽线杯</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SRE5002</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>EXSENCE DC</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>2022</v>
+      </c>
+      <c r="G11" t="str">
+        <v>22 Exsence DC</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>baitcasting</v>
+      </c>
+      <c r="J11" t="str">
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-04-10 00:51:20</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-04-15 02:13:02</v>
+      </c>
+      <c r="M11" t="str">
+        <v>海鲈远投特化</v>
+      </c>
+      <c r="N11" t="str">
+        <v>4x8 DC Exsence Tune / 海鲈远投 / PE 线路亚</v>
+      </c>
+      <c r="O11" t="str">
+        <v>¥4,284</v>
+      </c>
+      <c r="P11" t="str">
+        <v>在售</v>
+      </c>
+      <c r="Q11" t="str">
         <v>技术进化而重生的NEW 4x8 DC EXSENCE TUNE，实现了SHIMANO至今未有的精密刹车力。MGL SPOOLⅢ，SILENTUNE，S3D线杯效果相辅相成，使得抛投距离大幅进化。特别是解决了使用PE线时的缠线问题，瞬间的刹车控制能力大幅减少了切线的可能性。另外增加了最大卸力和收线量，使其泛用性更强。具备可以和海水鱼对抗潜力的两轴轮诞生。</v>
       </c>
-      <c r="R9" t="str" s="1">
+      <c r="R11" t="str">
         <v>83400JPY</v>
       </c>
-      <c r="S9" t="str" s="1">
+      <c r="S11" t="str">
         <v>海鲈DC远投特化</v>
       </c>
-      <c r="T9" t="str" s="1">
+      <c r="T11" t="str">
         <v>海鲈PE适配 / DC调校 / 远投性能</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BF59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BH59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1135,24 +1252,30 @@
         <v>Description</v>
       </c>
       <c r="AZ1" t="str">
+        <v>EV_link</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>Specs_link</v>
+      </c>
+      <c r="BB1" t="str">
         <v>handle_knob_material</v>
       </c>
-      <c r="BA1" t="str">
+      <c r="BC1" t="str">
         <v>handle_hole_spec</v>
       </c>
-      <c r="BB1" t="str">
+      <c r="BD1" t="str">
         <v>main_gear_material</v>
       </c>
-      <c r="BC1" t="str">
+      <c r="BE1" t="str">
         <v>main_gear_size</v>
       </c>
-      <c r="BD1" t="str">
+      <c r="BF1" t="str">
         <v>minor_gear_material</v>
       </c>
-      <c r="BE1" t="str">
+      <c r="BG1" t="str">
         <v>player_environment</v>
       </c>
-      <c r="BF1" t="str">
+      <c r="BH1" t="str">
         <v>is_handle_double</v>
       </c>
     </row>
@@ -1161,7 +1284,7 @@
         <v>SRED50332</v>
       </c>
       <c r="B2" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C2" t="str">
         <v>SLX 70</v>
@@ -1223,13 +1346,13 @@
       <c r="V2" t="str">
         <v/>
       </c>
-      <c r="W2" t="str" s="1">
+      <c r="W2" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X2" t="str">
         <v/>
       </c>
-      <c r="Y2" t="str" s="1">
+      <c r="Y2" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z2" t="str">
@@ -1259,7 +1382,7 @@
       <c r="AH2" t="str">
         <v/>
       </c>
-      <c r="AI2" t="str" s="1">
+      <c r="AI2" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ2" t="str">
@@ -1292,7 +1415,7 @@
       <c r="AS2" t="str">
         <v/>
       </c>
-      <c r="AT2" t="str" s="1">
+      <c r="AT2" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU2" t="str">
@@ -1311,24 +1434,30 @@
         <v/>
       </c>
       <c r="AZ2" t="str">
-        <v/>
-      </c>
-      <c r="BA2" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA2" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB2" t="str">
+        <v/>
+      </c>
+      <c r="BC2" t="str">
         <v>M7</v>
       </c>
-      <c r="BB2" t="str">
-        <v/>
-      </c>
-      <c r="BC2" t="str">
-        <v/>
-      </c>
       <c r="BD2" t="str">
         <v/>
       </c>
-      <c r="BE2" t="str" s="1">
+      <c r="BE2" t="str">
+        <v/>
+      </c>
+      <c r="BF2" t="str">
+        <v/>
+      </c>
+      <c r="BG2" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF2" t="str">
+      <c r="BH2" t="str">
         <v/>
       </c>
     </row>
@@ -1337,7 +1466,7 @@
         <v>SRED50333</v>
       </c>
       <c r="B3" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C3" t="str">
         <v>SLX 71</v>
@@ -1399,13 +1528,13 @@
       <c r="V3" t="str">
         <v/>
       </c>
-      <c r="W3" t="str" s="1">
+      <c r="W3" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X3" t="str">
         <v/>
       </c>
-      <c r="Y3" t="str" s="1">
+      <c r="Y3" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z3" t="str">
@@ -1435,7 +1564,7 @@
       <c r="AH3" t="str">
         <v/>
       </c>
-      <c r="AI3" t="str" s="1">
+      <c r="AI3" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ3" t="str">
@@ -1468,7 +1597,7 @@
       <c r="AS3" t="str">
         <v/>
       </c>
-      <c r="AT3" t="str" s="1">
+      <c r="AT3" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU3" t="str">
@@ -1487,24 +1616,30 @@
         <v/>
       </c>
       <c r="AZ3" t="str">
-        <v/>
-      </c>
-      <c r="BA3" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046963</v>
+      </c>
+      <c r="BA3" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB3" t="str">
+        <v/>
+      </c>
+      <c r="BC3" t="str">
         <v>M7</v>
       </c>
-      <c r="BB3" t="str">
-        <v/>
-      </c>
-      <c r="BC3" t="str">
-        <v/>
-      </c>
       <c r="BD3" t="str">
         <v/>
       </c>
-      <c r="BE3" t="str" s="1">
+      <c r="BE3" t="str">
+        <v/>
+      </c>
+      <c r="BF3" t="str">
+        <v/>
+      </c>
+      <c r="BG3" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF3" t="str">
+      <c r="BH3" t="str">
         <v/>
       </c>
     </row>
@@ -1513,7 +1648,7 @@
         <v>SRED50334</v>
       </c>
       <c r="B4" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C4" t="str">
         <v>SLX 70HG</v>
@@ -1575,13 +1710,13 @@
       <c r="V4" t="str">
         <v/>
       </c>
-      <c r="W4" t="str" s="1">
+      <c r="W4" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X4" t="str">
         <v/>
       </c>
-      <c r="Y4" t="str" s="1">
+      <c r="Y4" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z4" t="str">
@@ -1611,7 +1746,7 @@
       <c r="AH4" t="str">
         <v/>
       </c>
-      <c r="AI4" t="str" s="1">
+      <c r="AI4" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ4" t="str">
@@ -1644,7 +1779,7 @@
       <c r="AS4" t="str">
         <v/>
       </c>
-      <c r="AT4" t="str" s="1">
+      <c r="AT4" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU4" t="str">
@@ -1663,24 +1798,30 @@
         <v/>
       </c>
       <c r="AZ4" t="str">
-        <v/>
-      </c>
-      <c r="BA4" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046970</v>
+      </c>
+      <c r="BA4" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB4" t="str">
+        <v/>
+      </c>
+      <c r="BC4" t="str">
         <v>M7</v>
       </c>
-      <c r="BB4" t="str">
-        <v/>
-      </c>
-      <c r="BC4" t="str">
-        <v/>
-      </c>
       <c r="BD4" t="str">
         <v/>
       </c>
-      <c r="BE4" t="str" s="1">
+      <c r="BE4" t="str">
+        <v/>
+      </c>
+      <c r="BF4" t="str">
+        <v/>
+      </c>
+      <c r="BG4" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF4" t="str">
+      <c r="BH4" t="str">
         <v/>
       </c>
     </row>
@@ -1689,7 +1830,7 @@
         <v>SRED50335</v>
       </c>
       <c r="B5" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C5" t="str">
         <v>SLX 71HG</v>
@@ -1751,13 +1892,13 @@
       <c r="V5" t="str">
         <v/>
       </c>
-      <c r="W5" t="str" s="1">
+      <c r="W5" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X5" t="str">
         <v/>
       </c>
-      <c r="Y5" t="str" s="1">
+      <c r="Y5" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z5" t="str">
@@ -1787,7 +1928,7 @@
       <c r="AH5" t="str">
         <v/>
       </c>
-      <c r="AI5" t="str" s="1">
+      <c r="AI5" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ5" t="str">
@@ -1820,7 +1961,7 @@
       <c r="AS5" t="str">
         <v/>
       </c>
-      <c r="AT5" t="str" s="1">
+      <c r="AT5" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU5" t="str">
@@ -1839,24 +1980,30 @@
         <v/>
       </c>
       <c r="AZ5" t="str">
-        <v/>
-      </c>
-      <c r="BA5" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046987</v>
+      </c>
+      <c r="BA5" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB5" t="str">
+        <v/>
+      </c>
+      <c r="BC5" t="str">
         <v>M7</v>
       </c>
-      <c r="BB5" t="str">
-        <v/>
-      </c>
-      <c r="BC5" t="str">
-        <v/>
-      </c>
       <c r="BD5" t="str">
         <v/>
       </c>
-      <c r="BE5" t="str" s="1">
+      <c r="BE5" t="str">
+        <v/>
+      </c>
+      <c r="BF5" t="str">
+        <v/>
+      </c>
+      <c r="BG5" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF5" t="str">
+      <c r="BH5" t="str">
         <v/>
       </c>
     </row>
@@ -1865,7 +2012,7 @@
         <v>SRED50336</v>
       </c>
       <c r="B6" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C6" t="str">
         <v>SLX 70XG</v>
@@ -1927,13 +2074,13 @@
       <c r="V6" t="str">
         <v/>
       </c>
-      <c r="W6" t="str" s="1">
+      <c r="W6" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X6" t="str">
         <v/>
       </c>
-      <c r="Y6" t="str" s="1">
+      <c r="Y6" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z6" t="str">
@@ -1963,7 +2110,7 @@
       <c r="AH6" t="str">
         <v/>
       </c>
-      <c r="AI6" t="str" s="1">
+      <c r="AI6" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ6" t="str">
@@ -1996,7 +2143,7 @@
       <c r="AS6" t="str">
         <v/>
       </c>
-      <c r="AT6" t="str" s="1">
+      <c r="AT6" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU6" t="str">
@@ -2015,24 +2162,30 @@
         <v/>
       </c>
       <c r="AZ6" t="str">
-        <v/>
-      </c>
-      <c r="BA6" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046994</v>
+      </c>
+      <c r="BA6" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB6" t="str">
+        <v/>
+      </c>
+      <c r="BC6" t="str">
         <v>M7</v>
       </c>
-      <c r="BB6" t="str">
-        <v/>
-      </c>
-      <c r="BC6" t="str">
-        <v/>
-      </c>
       <c r="BD6" t="str">
         <v/>
       </c>
-      <c r="BE6" t="str" s="1">
+      <c r="BE6" t="str">
+        <v/>
+      </c>
+      <c r="BF6" t="str">
+        <v/>
+      </c>
+      <c r="BG6" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF6" t="str">
+      <c r="BH6" t="str">
         <v/>
       </c>
     </row>
@@ -2041,7 +2194,7 @@
         <v>SRED50337</v>
       </c>
       <c r="B7" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_70</v>
       </c>
       <c r="C7" t="str">
         <v>SLX 71XG</v>
@@ -2103,13 +2256,13 @@
       <c r="V7" t="str">
         <v/>
       </c>
-      <c r="W7" t="str" s="1">
+      <c r="W7" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X7" t="str">
         <v/>
       </c>
-      <c r="Y7" t="str" s="1">
+      <c r="Y7" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z7" t="str">
@@ -2139,7 +2292,7 @@
       <c r="AH7" t="str">
         <v/>
       </c>
-      <c r="AI7" t="str" s="1">
+      <c r="AI7" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ7" t="str">
@@ -2172,7 +2325,7 @@
       <c r="AS7" t="str">
         <v/>
       </c>
-      <c r="AT7" t="str" s="1">
+      <c r="AT7" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU7" t="str">
@@ -2191,24 +2344,30 @@
         <v/>
       </c>
       <c r="AZ7" t="str">
-        <v/>
-      </c>
-      <c r="BA7" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047007</v>
+      </c>
+      <c r="BA7" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB7" t="str">
+        <v/>
+      </c>
+      <c r="BC7" t="str">
         <v>M7</v>
       </c>
-      <c r="BB7" t="str">
-        <v/>
-      </c>
-      <c r="BC7" t="str">
-        <v/>
-      </c>
       <c r="BD7" t="str">
         <v/>
       </c>
-      <c r="BE7" t="str" s="1">
+      <c r="BE7" t="str">
+        <v/>
+      </c>
+      <c r="BF7" t="str">
+        <v/>
+      </c>
+      <c r="BG7" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF7" t="str">
+      <c r="BH7" t="str">
         <v/>
       </c>
     </row>
@@ -2217,10 +2376,10 @@
         <v>SRED50370</v>
       </c>
       <c r="B8" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C8" t="str">
-        <v>SLX 150</v>
+        <v>SLX XT 150</v>
       </c>
       <c r="D8" t="str">
         <v>6.3</v>
@@ -2279,13 +2438,13 @@
       <c r="V8" t="str">
         <v/>
       </c>
-      <c r="W8" t="str" s="1">
+      <c r="W8" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X8" t="str">
         <v/>
       </c>
-      <c r="Y8" t="str" s="1">
+      <c r="Y8" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z8" t="str">
@@ -2315,7 +2474,7 @@
       <c r="AH8" t="str">
         <v/>
       </c>
-      <c r="AI8" t="str" s="1">
+      <c r="AI8" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ8" t="str">
@@ -2348,7 +2507,7 @@
       <c r="AS8" t="str">
         <v/>
       </c>
-      <c r="AT8" t="str" s="1">
+      <c r="AT8" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU8" t="str">
@@ -2367,24 +2526,30 @@
         <v/>
       </c>
       <c r="AZ8" t="str">
-        <v/>
-      </c>
-      <c r="BA8" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA8" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB8" t="str">
+        <v/>
+      </c>
+      <c r="BC8" t="str">
         <v>M7</v>
       </c>
-      <c r="BB8" t="str">
-        <v/>
-      </c>
-      <c r="BC8" t="str">
-        <v/>
-      </c>
       <c r="BD8" t="str">
         <v/>
       </c>
-      <c r="BE8" t="str" s="1">
+      <c r="BE8" t="str">
+        <v/>
+      </c>
+      <c r="BF8" t="str">
+        <v/>
+      </c>
+      <c r="BG8" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF8" t="str">
+      <c r="BH8" t="str">
         <v/>
       </c>
     </row>
@@ -2393,10 +2558,10 @@
         <v>SRED50371</v>
       </c>
       <c r="B9" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C9" t="str">
-        <v>SLX 151</v>
+        <v>SLX XT 151</v>
       </c>
       <c r="D9" t="str">
         <v>6.3</v>
@@ -2455,13 +2620,13 @@
       <c r="V9" t="str">
         <v/>
       </c>
-      <c r="W9" t="str" s="1">
+      <c r="W9" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X9" t="str">
         <v/>
       </c>
-      <c r="Y9" t="str" s="1">
+      <c r="Y9" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z9" t="str">
@@ -2491,7 +2656,7 @@
       <c r="AH9" t="str">
         <v/>
       </c>
-      <c r="AI9" t="str" s="1">
+      <c r="AI9" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ9" t="str">
@@ -2524,7 +2689,7 @@
       <c r="AS9" t="str">
         <v/>
       </c>
-      <c r="AT9" t="str" s="1">
+      <c r="AT9" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU9" t="str">
@@ -2543,24 +2708,30 @@
         <v/>
       </c>
       <c r="AZ9" t="str">
-        <v/>
-      </c>
-      <c r="BA9" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA9" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB9" t="str">
+        <v/>
+      </c>
+      <c r="BC9" t="str">
         <v>M7</v>
       </c>
-      <c r="BB9" t="str">
-        <v/>
-      </c>
-      <c r="BC9" t="str">
-        <v/>
-      </c>
       <c r="BD9" t="str">
         <v/>
       </c>
-      <c r="BE9" t="str" s="1">
+      <c r="BE9" t="str">
+        <v/>
+      </c>
+      <c r="BF9" t="str">
+        <v/>
+      </c>
+      <c r="BG9" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF9" t="str">
+      <c r="BH9" t="str">
         <v/>
       </c>
     </row>
@@ -2569,10 +2740,10 @@
         <v>SRED50372</v>
       </c>
       <c r="B10" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C10" t="str">
-        <v>SLX 150HG</v>
+        <v>SLX XT 150HG</v>
       </c>
       <c r="D10" t="str">
         <v>7.2</v>
@@ -2631,13 +2802,13 @@
       <c r="V10" t="str">
         <v/>
       </c>
-      <c r="W10" t="str" s="1">
+      <c r="W10" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X10" t="str">
         <v/>
       </c>
-      <c r="Y10" t="str" s="1">
+      <c r="Y10" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z10" t="str">
@@ -2667,7 +2838,7 @@
       <c r="AH10" t="str">
         <v/>
       </c>
-      <c r="AI10" t="str" s="1">
+      <c r="AI10" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ10" t="str">
@@ -2700,7 +2871,7 @@
       <c r="AS10" t="str">
         <v/>
       </c>
-      <c r="AT10" t="str" s="1">
+      <c r="AT10" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU10" t="str">
@@ -2719,24 +2890,30 @@
         <v/>
       </c>
       <c r="AZ10" t="str">
-        <v/>
-      </c>
-      <c r="BA10" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA10" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB10" t="str">
+        <v/>
+      </c>
+      <c r="BC10" t="str">
         <v>M7</v>
       </c>
-      <c r="BB10" t="str">
-        <v/>
-      </c>
-      <c r="BC10" t="str">
-        <v/>
-      </c>
       <c r="BD10" t="str">
         <v/>
       </c>
-      <c r="BE10" t="str" s="1">
+      <c r="BE10" t="str">
+        <v/>
+      </c>
+      <c r="BF10" t="str">
+        <v/>
+      </c>
+      <c r="BG10" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF10" t="str">
+      <c r="BH10" t="str">
         <v/>
       </c>
     </row>
@@ -2745,10 +2922,10 @@
         <v>SRED50373</v>
       </c>
       <c r="B11" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C11" t="str">
-        <v>SLX 151HG</v>
+        <v>SLX XT 151HG</v>
       </c>
       <c r="D11" t="str">
         <v>7.2</v>
@@ -2807,13 +2984,13 @@
       <c r="V11" t="str">
         <v/>
       </c>
-      <c r="W11" t="str" s="1">
+      <c r="W11" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X11" t="str">
         <v/>
       </c>
-      <c r="Y11" t="str" s="1">
+      <c r="Y11" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z11" t="str">
@@ -2843,7 +3020,7 @@
       <c r="AH11" t="str">
         <v/>
       </c>
-      <c r="AI11" t="str" s="1">
+      <c r="AI11" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ11" t="str">
@@ -2876,7 +3053,7 @@
       <c r="AS11" t="str">
         <v/>
       </c>
-      <c r="AT11" t="str" s="1">
+      <c r="AT11" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU11" t="str">
@@ -2895,24 +3072,30 @@
         <v/>
       </c>
       <c r="AZ11" t="str">
-        <v/>
-      </c>
-      <c r="BA11" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA11" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB11" t="str">
+        <v/>
+      </c>
+      <c r="BC11" t="str">
         <v>M7</v>
       </c>
-      <c r="BB11" t="str">
-        <v/>
-      </c>
-      <c r="BC11" t="str">
-        <v/>
-      </c>
       <c r="BD11" t="str">
         <v/>
       </c>
-      <c r="BE11" t="str" s="1">
+      <c r="BE11" t="str">
+        <v/>
+      </c>
+      <c r="BF11" t="str">
+        <v/>
+      </c>
+      <c r="BG11" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF11" t="str">
+      <c r="BH11" t="str">
         <v/>
       </c>
     </row>
@@ -2921,10 +3104,10 @@
         <v>SRED50374</v>
       </c>
       <c r="B12" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C12" t="str">
-        <v>SLX 150XG</v>
+        <v>SLX XT 150XG</v>
       </c>
       <c r="D12" t="str">
         <v>8.2</v>
@@ -2983,13 +3166,13 @@
       <c r="V12" t="str">
         <v/>
       </c>
-      <c r="W12" t="str" s="1">
+      <c r="W12" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X12" t="str">
         <v/>
       </c>
-      <c r="Y12" t="str" s="1">
+      <c r="Y12" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z12" t="str">
@@ -3019,7 +3202,7 @@
       <c r="AH12" t="str">
         <v/>
       </c>
-      <c r="AI12" t="str" s="1">
+      <c r="AI12" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ12" t="str">
@@ -3052,7 +3235,7 @@
       <c r="AS12" t="str">
         <v/>
       </c>
-      <c r="AT12" t="str" s="1">
+      <c r="AT12" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU12" t="str">
@@ -3071,24 +3254,30 @@
         <v/>
       </c>
       <c r="AZ12" t="str">
-        <v/>
-      </c>
-      <c r="BA12" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA12" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB12" t="str">
+        <v/>
+      </c>
+      <c r="BC12" t="str">
         <v>M7</v>
       </c>
-      <c r="BB12" t="str">
-        <v/>
-      </c>
-      <c r="BC12" t="str">
-        <v/>
-      </c>
       <c r="BD12" t="str">
         <v/>
       </c>
-      <c r="BE12" t="str" s="1">
+      <c r="BE12" t="str">
+        <v/>
+      </c>
+      <c r="BF12" t="str">
+        <v/>
+      </c>
+      <c r="BG12" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF12" t="str">
+      <c r="BH12" t="str">
         <v/>
       </c>
     </row>
@@ -3097,10 +3286,10 @@
         <v>SRED50375</v>
       </c>
       <c r="B13" t="str">
-        <v>SRE5058</v>
+        <v>SRE5058_150</v>
       </c>
       <c r="C13" t="str">
-        <v>SLX 151XG</v>
+        <v>SLX XT 151XG</v>
       </c>
       <c r="D13" t="str">
         <v>8.2</v>
@@ -3159,13 +3348,13 @@
       <c r="V13" t="str">
         <v/>
       </c>
-      <c r="W13" t="str" s="1">
+      <c r="W13" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X13" t="str">
         <v/>
       </c>
-      <c r="Y13" t="str" s="1">
+      <c r="Y13" t="str">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z13" t="str">
@@ -3195,7 +3384,7 @@
       <c r="AH13" t="str">
         <v/>
       </c>
-      <c r="AI13" t="str" s="1">
+      <c r="AI13" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ13" t="str">
@@ -3228,7 +3417,7 @@
       <c r="AS13" t="str">
         <v/>
       </c>
-      <c r="AT13" t="str" s="1">
+      <c r="AT13" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU13" t="str">
@@ -3247,24 +3436,30 @@
         <v/>
       </c>
       <c r="AZ13" t="str">
-        <v/>
-      </c>
-      <c r="BA13" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+      </c>
+      <c r="BA13" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+      </c>
+      <c r="BB13" t="str">
+        <v/>
+      </c>
+      <c r="BC13" t="str">
         <v>M7</v>
       </c>
-      <c r="BB13" t="str">
-        <v/>
-      </c>
-      <c r="BC13" t="str">
-        <v/>
-      </c>
       <c r="BD13" t="str">
         <v/>
       </c>
-      <c r="BE13" t="str" s="1">
+      <c r="BE13" t="str">
+        <v/>
+      </c>
+      <c r="BF13" t="str">
+        <v/>
+      </c>
+      <c r="BG13" t="str">
         <v>淡水泛用</v>
       </c>
-      <c r="BF13" t="str">
+      <c r="BH13" t="str">
         <v/>
       </c>
     </row>
@@ -3326,22 +3521,22 @@
       <c r="S14" t="str">
         <v>19</v>
       </c>
-      <c r="T14" t="str" s="1">
+      <c r="T14" t="str">
         <v>6.7</v>
       </c>
       <c r="U14" t="str">
         <v/>
       </c>
-      <c r="V14" t="str" s="1">
+      <c r="V14" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W14" t="str" s="1">
+      <c r="W14" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X14" t="str" s="1">
+      <c r="X14" t="str">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y14" t="str" s="1">
+      <c r="Y14" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z14" t="str">
@@ -3350,16 +3545,16 @@
       <c r="AA14" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB14" t="str" s="1">
+      <c r="AB14" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC14" t="str" s="1">
+      <c r="AC14" t="str">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD14" t="str" s="1">
+      <c r="AD14" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE14" t="str" s="1">
+      <c r="AE14" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF14" t="str">
@@ -3371,7 +3566,7 @@
       <c r="AH14" t="str">
         <v/>
       </c>
-      <c r="AI14" t="str" s="1">
+      <c r="AI14" t="str">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ14" t="str">
@@ -3383,7 +3578,7 @@
       <c r="AL14" t="str">
         <v/>
       </c>
-      <c r="AM14" t="str" s="1">
+      <c r="AM14" t="str">
         <v>1</v>
       </c>
       <c r="AN14" t="str">
@@ -3404,7 +3599,7 @@
       <c r="AS14" t="str">
         <v/>
       </c>
-      <c r="AT14" t="str" s="1">
+      <c r="AT14" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU14" t="str">
@@ -3423,24 +3618,30 @@
         <v/>
       </c>
       <c r="AZ14" t="str">
-        <v/>
-      </c>
-      <c r="BA14" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043986</v>
+      </c>
+      <c r="BA14" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_aldebaran_bfs.pdf</v>
+      </c>
+      <c r="BB14" t="str">
+        <v/>
+      </c>
+      <c r="BC14" t="str">
         <v>M7</v>
       </c>
-      <c r="BB14" t="str">
-        <v/>
-      </c>
-      <c r="BC14" t="str">
-        <v/>
-      </c>
       <c r="BD14" t="str">
         <v/>
       </c>
-      <c r="BE14" t="str" s="1">
+      <c r="BE14" t="str">
+        <v/>
+      </c>
+      <c r="BF14" t="str">
+        <v/>
+      </c>
+      <c r="BG14" t="str">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
-      <c r="BF14" t="str">
+      <c r="BH14" t="str">
         <v/>
       </c>
     </row>
@@ -3502,22 +3703,22 @@
       <c r="S15" t="str">
         <v>19</v>
       </c>
-      <c r="T15" t="str" s="1">
+      <c r="T15" t="str">
         <v>6.7</v>
       </c>
       <c r="U15" t="str">
         <v/>
       </c>
-      <c r="V15" t="str" s="1">
+      <c r="V15" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W15" t="str" s="1">
+      <c r="W15" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X15" t="str" s="1">
+      <c r="X15" t="str">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y15" t="str" s="1">
+      <c r="Y15" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z15" t="str">
@@ -3526,16 +3727,16 @@
       <c r="AA15" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB15" t="str" s="1">
+      <c r="AB15" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC15" t="str" s="1">
+      <c r="AC15" t="str">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD15" t="str" s="1">
+      <c r="AD15" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE15" t="str" s="1">
+      <c r="AE15" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF15" t="str">
@@ -3547,7 +3748,7 @@
       <c r="AH15" t="str">
         <v/>
       </c>
-      <c r="AI15" t="str" s="1">
+      <c r="AI15" t="str">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ15" t="str">
@@ -3559,7 +3760,7 @@
       <c r="AL15" t="str">
         <v/>
       </c>
-      <c r="AM15" t="str" s="1">
+      <c r="AM15" t="str">
         <v>1</v>
       </c>
       <c r="AN15" t="str">
@@ -3580,7 +3781,7 @@
       <c r="AS15" t="str">
         <v/>
       </c>
-      <c r="AT15" t="str" s="1">
+      <c r="AT15" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU15" t="str">
@@ -3599,24 +3800,30 @@
         <v/>
       </c>
       <c r="AZ15" t="str">
-        <v/>
-      </c>
-      <c r="BA15" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043993</v>
+      </c>
+      <c r="BA15" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_aldebaran_bfs.pdf</v>
+      </c>
+      <c r="BB15" t="str">
+        <v/>
+      </c>
+      <c r="BC15" t="str">
         <v>M7</v>
       </c>
-      <c r="BB15" t="str">
-        <v/>
-      </c>
-      <c r="BC15" t="str">
-        <v/>
-      </c>
       <c r="BD15" t="str">
         <v/>
       </c>
-      <c r="BE15" t="str" s="1">
+      <c r="BE15" t="str">
+        <v/>
+      </c>
+      <c r="BF15" t="str">
+        <v/>
+      </c>
+      <c r="BG15" t="str">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
-      <c r="BF15" t="str">
+      <c r="BH15" t="str">
         <v/>
       </c>
     </row>
@@ -3678,22 +3885,22 @@
       <c r="S16" t="str">
         <v>19</v>
       </c>
-      <c r="T16" t="str" s="1">
+      <c r="T16" t="str">
         <v>6.7</v>
       </c>
       <c r="U16" t="str">
         <v/>
       </c>
-      <c r="V16" t="str" s="1">
+      <c r="V16" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W16" t="str" s="1">
+      <c r="W16" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X16" t="str" s="1">
+      <c r="X16" t="str">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y16" t="str" s="1">
+      <c r="Y16" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z16" t="str">
@@ -3702,16 +3909,16 @@
       <c r="AA16" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB16" t="str" s="1">
+      <c r="AB16" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC16" t="str" s="1">
+      <c r="AC16" t="str">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD16" t="str" s="1">
+      <c r="AD16" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE16" t="str" s="1">
+      <c r="AE16" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF16" t="str">
@@ -3723,7 +3930,7 @@
       <c r="AH16" t="str">
         <v/>
       </c>
-      <c r="AI16" t="str" s="1">
+      <c r="AI16" t="str">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ16" t="str">
@@ -3735,7 +3942,7 @@
       <c r="AL16" t="str">
         <v/>
       </c>
-      <c r="AM16" t="str" s="1">
+      <c r="AM16" t="str">
         <v>1</v>
       </c>
       <c r="AN16" t="str">
@@ -3756,7 +3963,7 @@
       <c r="AS16" t="str">
         <v/>
       </c>
-      <c r="AT16" t="str" s="1">
+      <c r="AT16" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU16" t="str">
@@ -3775,24 +3982,30 @@
         <v/>
       </c>
       <c r="AZ16" t="str">
-        <v/>
-      </c>
-      <c r="BA16" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044006</v>
+      </c>
+      <c r="BA16" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_aldebaran_bfs%20(1).pdf</v>
+      </c>
+      <c r="BB16" t="str">
+        <v/>
+      </c>
+      <c r="BC16" t="str">
         <v>M7</v>
       </c>
-      <c r="BB16" t="str">
-        <v/>
-      </c>
-      <c r="BC16" t="str">
-        <v/>
-      </c>
       <c r="BD16" t="str">
         <v/>
       </c>
-      <c r="BE16" t="str" s="1">
+      <c r="BE16" t="str">
+        <v/>
+      </c>
+      <c r="BF16" t="str">
+        <v/>
+      </c>
+      <c r="BG16" t="str">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
-      <c r="BF16" t="str">
+      <c r="BH16" t="str">
         <v/>
       </c>
     </row>
@@ -3854,22 +4067,22 @@
       <c r="S17" t="str">
         <v>19</v>
       </c>
-      <c r="T17" t="str" s="1">
+      <c r="T17" t="str">
         <v>6.7</v>
       </c>
       <c r="U17" t="str">
         <v/>
       </c>
-      <c r="V17" t="str" s="1">
+      <c r="V17" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W17" t="str" s="1">
+      <c r="W17" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X17" t="str" s="1">
+      <c r="X17" t="str">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y17" t="str" s="1">
+      <c r="Y17" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z17" t="str">
@@ -3878,16 +4091,16 @@
       <c r="AA17" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB17" t="str" s="1">
+      <c r="AB17" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC17" t="str" s="1">
+      <c r="AC17" t="str">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD17" t="str" s="1">
+      <c r="AD17" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE17" t="str" s="1">
+      <c r="AE17" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF17" t="str">
@@ -3899,7 +4112,7 @@
       <c r="AH17" t="str">
         <v/>
       </c>
-      <c r="AI17" t="str" s="1">
+      <c r="AI17" t="str">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ17" t="str">
@@ -3911,7 +4124,7 @@
       <c r="AL17" t="str">
         <v/>
       </c>
-      <c r="AM17" t="str" s="1">
+      <c r="AM17" t="str">
         <v>1</v>
       </c>
       <c r="AN17" t="str">
@@ -3932,7 +4145,7 @@
       <c r="AS17" t="str">
         <v/>
       </c>
-      <c r="AT17" t="str" s="1">
+      <c r="AT17" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU17" t="str">
@@ -3951,24 +4164,30 @@
         <v/>
       </c>
       <c r="AZ17" t="str">
-        <v/>
-      </c>
-      <c r="BA17" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044013</v>
+      </c>
+      <c r="BA17" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_aldebaran_bfs.pdf</v>
+      </c>
+      <c r="BB17" t="str">
+        <v/>
+      </c>
+      <c r="BC17" t="str">
         <v>M7</v>
       </c>
-      <c r="BB17" t="str">
-        <v/>
-      </c>
-      <c r="BC17" t="str">
-        <v/>
-      </c>
       <c r="BD17" t="str">
         <v/>
       </c>
-      <c r="BE17" t="str" s="1">
+      <c r="BE17" t="str">
+        <v/>
+      </c>
+      <c r="BF17" t="str">
+        <v/>
+      </c>
+      <c r="BG17" t="str">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
-      <c r="BF17" t="str">
+      <c r="BH17" t="str">
         <v/>
       </c>
     </row>
@@ -4030,22 +4249,22 @@
       <c r="S18" t="str">
         <v>22</v>
       </c>
-      <c r="T18" t="str" s="1">
+      <c r="T18" t="str">
         <v>10.5</v>
       </c>
       <c r="U18" t="str">
         <v/>
       </c>
-      <c r="V18" t="str" s="1">
+      <c r="V18" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W18" t="str" s="1">
+      <c r="W18" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X18" t="str" s="1">
+      <c r="X18" t="str">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y18" t="str" s="1">
+      <c r="Y18" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z18" t="str">
@@ -4054,16 +4273,16 @@
       <c r="AA18" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB18" t="str" s="1">
+      <c r="AB18" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC18" t="str" s="1">
+      <c r="AC18" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD18" t="str" s="1">
+      <c r="AD18" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE18" t="str" s="1">
+      <c r="AE18" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF18" t="str">
@@ -4075,7 +4294,7 @@
       <c r="AH18" t="str">
         <v/>
       </c>
-      <c r="AI18" t="str" s="1">
+      <c r="AI18" t="str">
         <v>淡水技巧</v>
       </c>
       <c r="AJ18" t="str">
@@ -4108,7 +4327,7 @@
       <c r="AS18" t="str">
         <v/>
       </c>
-      <c r="AT18" t="str" s="1">
+      <c r="AT18" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU18" t="str">
@@ -4127,24 +4346,30 @@
         <v/>
       </c>
       <c r="AZ18" t="str">
-        <v/>
-      </c>
-      <c r="BA18" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038777</v>
+      </c>
+      <c r="BA18" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_aldebaran_mgl.pdf</v>
+      </c>
+      <c r="BB18" t="str">
+        <v/>
+      </c>
+      <c r="BC18" t="str">
         <v>M7</v>
       </c>
-      <c r="BB18" t="str">
-        <v/>
-      </c>
-      <c r="BC18" t="str">
-        <v/>
-      </c>
       <c r="BD18" t="str">
         <v/>
       </c>
-      <c r="BE18" t="str" s="1">
+      <c r="BE18" t="str">
+        <v/>
+      </c>
+      <c r="BF18" t="str">
+        <v/>
+      </c>
+      <c r="BG18" t="str">
         <v>轻量泛用 / 技巧</v>
       </c>
-      <c r="BF18" t="str">
+      <c r="BH18" t="str">
         <v/>
       </c>
     </row>
@@ -4206,22 +4431,22 @@
       <c r="S19" t="str">
         <v>22</v>
       </c>
-      <c r="T19" t="str" s="1">
+      <c r="T19" t="str">
         <v>10.5</v>
       </c>
       <c r="U19" t="str">
         <v/>
       </c>
-      <c r="V19" t="str" s="1">
+      <c r="V19" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W19" t="str" s="1">
+      <c r="W19" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X19" t="str" s="1">
+      <c r="X19" t="str">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y19" t="str" s="1">
+      <c r="Y19" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z19" t="str">
@@ -4230,16 +4455,16 @@
       <c r="AA19" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB19" t="str" s="1">
+      <c r="AB19" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC19" t="str" s="1">
+      <c r="AC19" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD19" t="str" s="1">
+      <c r="AD19" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE19" t="str" s="1">
+      <c r="AE19" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF19" t="str">
@@ -4251,7 +4476,7 @@
       <c r="AH19" t="str">
         <v/>
       </c>
-      <c r="AI19" t="str" s="1">
+      <c r="AI19" t="str">
         <v>淡水技巧</v>
       </c>
       <c r="AJ19" t="str">
@@ -4284,7 +4509,7 @@
       <c r="AS19" t="str">
         <v/>
       </c>
-      <c r="AT19" t="str" s="1">
+      <c r="AT19" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU19" t="str">
@@ -4303,24 +4528,30 @@
         <v/>
       </c>
       <c r="AZ19" t="str">
-        <v/>
-      </c>
-      <c r="BA19" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038784</v>
+      </c>
+      <c r="BA19" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_aldebaran_mgl.pdf</v>
+      </c>
+      <c r="BB19" t="str">
+        <v/>
+      </c>
+      <c r="BC19" t="str">
         <v>M7</v>
       </c>
-      <c r="BB19" t="str">
-        <v/>
-      </c>
-      <c r="BC19" t="str">
-        <v/>
-      </c>
       <c r="BD19" t="str">
         <v/>
       </c>
-      <c r="BE19" t="str" s="1">
+      <c r="BE19" t="str">
+        <v/>
+      </c>
+      <c r="BF19" t="str">
+        <v/>
+      </c>
+      <c r="BG19" t="str">
         <v>轻量泛用 / 技巧</v>
       </c>
-      <c r="BF19" t="str">
+      <c r="BH19" t="str">
         <v/>
       </c>
     </row>
@@ -4382,22 +4613,22 @@
       <c r="S20" t="str">
         <v>22</v>
       </c>
-      <c r="T20" t="str" s="1">
+      <c r="T20" t="str">
         <v>10.5</v>
       </c>
       <c r="U20" t="str">
         <v/>
       </c>
-      <c r="V20" t="str" s="1">
+      <c r="V20" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W20" t="str" s="1">
+      <c r="W20" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X20" t="str" s="1">
+      <c r="X20" t="str">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y20" t="str" s="1">
+      <c r="Y20" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z20" t="str">
@@ -4406,16 +4637,16 @@
       <c r="AA20" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB20" t="str" s="1">
+      <c r="AB20" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC20" t="str" s="1">
+      <c r="AC20" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD20" t="str" s="1">
+      <c r="AD20" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE20" t="str" s="1">
+      <c r="AE20" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF20" t="str">
@@ -4427,7 +4658,7 @@
       <c r="AH20" t="str">
         <v/>
       </c>
-      <c r="AI20" t="str" s="1">
+      <c r="AI20" t="str">
         <v>淡水技巧</v>
       </c>
       <c r="AJ20" t="str">
@@ -4460,7 +4691,7 @@
       <c r="AS20" t="str">
         <v/>
       </c>
-      <c r="AT20" t="str" s="1">
+      <c r="AT20" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU20" t="str">
@@ -4479,24 +4710,30 @@
         <v/>
       </c>
       <c r="AZ20" t="str">
-        <v/>
-      </c>
-      <c r="BA20" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038791</v>
+      </c>
+      <c r="BA20" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_aldebaran_mgl.pdf</v>
+      </c>
+      <c r="BB20" t="str">
+        <v/>
+      </c>
+      <c r="BC20" t="str">
         <v>M7</v>
       </c>
-      <c r="BB20" t="str">
-        <v/>
-      </c>
-      <c r="BC20" t="str">
-        <v/>
-      </c>
       <c r="BD20" t="str">
         <v/>
       </c>
-      <c r="BE20" t="str" s="1">
+      <c r="BE20" t="str">
+        <v/>
+      </c>
+      <c r="BF20" t="str">
+        <v/>
+      </c>
+      <c r="BG20" t="str">
         <v>轻量泛用 / 技巧</v>
       </c>
-      <c r="BF20" t="str">
+      <c r="BH20" t="str">
         <v/>
       </c>
     </row>
@@ -4558,22 +4795,22 @@
       <c r="S21" t="str">
         <v>22</v>
       </c>
-      <c r="T21" t="str" s="1">
+      <c r="T21" t="str">
         <v>10.5</v>
       </c>
       <c r="U21" t="str">
         <v/>
       </c>
-      <c r="V21" t="str" s="1">
+      <c r="V21" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W21" t="str" s="1">
+      <c r="W21" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X21" t="str" s="1">
+      <c r="X21" t="str">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y21" t="str" s="1">
+      <c r="Y21" t="str">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z21" t="str">
@@ -4582,16 +4819,16 @@
       <c r="AA21" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB21" t="str" s="1">
+      <c r="AB21" t="str">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC21" t="str" s="1">
+      <c r="AC21" t="str">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD21" t="str" s="1">
+      <c r="AD21" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE21" t="str" s="1">
+      <c r="AE21" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF21" t="str">
@@ -4603,7 +4840,7 @@
       <c r="AH21" t="str">
         <v/>
       </c>
-      <c r="AI21" t="str" s="1">
+      <c r="AI21" t="str">
         <v>淡水技巧</v>
       </c>
       <c r="AJ21" t="str">
@@ -4636,7 +4873,7 @@
       <c r="AS21" t="str">
         <v/>
       </c>
-      <c r="AT21" t="str" s="1">
+      <c r="AT21" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU21" t="str">
@@ -4655,24 +4892,30 @@
         <v/>
       </c>
       <c r="AZ21" t="str">
-        <v/>
-      </c>
-      <c r="BA21" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038807</v>
+      </c>
+      <c r="BA21" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_aldebaran_mgl.pdf</v>
+      </c>
+      <c r="BB21" t="str">
+        <v/>
+      </c>
+      <c r="BC21" t="str">
         <v>M7</v>
       </c>
-      <c r="BB21" t="str">
-        <v/>
-      </c>
-      <c r="BC21" t="str">
-        <v/>
-      </c>
       <c r="BD21" t="str">
         <v/>
       </c>
-      <c r="BE21" t="str" s="1">
+      <c r="BE21" t="str">
+        <v/>
+      </c>
+      <c r="BF21" t="str">
+        <v/>
+      </c>
+      <c r="BG21" t="str">
         <v>轻量泛用 / 技巧</v>
       </c>
-      <c r="BF21" t="str">
+      <c r="BH21" t="str">
         <v/>
       </c>
     </row>
@@ -4681,7 +4924,7 @@
         <v>SRED50304</v>
       </c>
       <c r="B22" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C22" t="str">
         <v>CURADO 200</v>
@@ -4743,13 +4986,13 @@
       <c r="V22" t="str">
         <v/>
       </c>
-      <c r="W22" t="str" s="1">
+      <c r="W22" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X22" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y22" t="str" s="1">
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z22" t="str">
@@ -4758,16 +5001,16 @@
       <c r="AA22" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB22" t="str" s="1">
+      <c r="AB22" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC22" t="str">
         <v/>
       </c>
-      <c r="AD22" t="str" s="1">
+      <c r="AD22" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE22" t="str" s="1">
+      <c r="AE22" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF22" t="str">
@@ -4779,7 +5022,7 @@
       <c r="AH22" t="str">
         <v/>
       </c>
-      <c r="AI22" t="str" s="1">
+      <c r="AI22" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ22" t="str">
@@ -4812,7 +5055,7 @@
       <c r="AS22" t="str">
         <v/>
       </c>
-      <c r="AT22" t="str" s="1">
+      <c r="AT22" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU22" t="str">
@@ -4833,22 +5076,28 @@
       <c r="AZ22" t="str">
         <v/>
       </c>
-      <c r="BA22" t="str" s="1">
+      <c r="BA22" t="str">
+        <v/>
+      </c>
+      <c r="BB22" t="str">
+        <v/>
+      </c>
+      <c r="BC22" t="str">
         <v>M7</v>
       </c>
-      <c r="BB22" t="str" s="1">
+      <c r="BD22" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC22" t="str">
-        <v/>
-      </c>
-      <c r="BD22" t="str">
-        <v/>
-      </c>
-      <c r="BE22" t="str" s="1">
+      <c r="BE22" t="str">
+        <v/>
+      </c>
+      <c r="BF22" t="str">
+        <v/>
+      </c>
+      <c r="BG22" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF22" t="str">
+      <c r="BH22" t="str">
         <v/>
       </c>
     </row>
@@ -4857,7 +5106,7 @@
         <v>SRED50305</v>
       </c>
       <c r="B23" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C23" t="str">
         <v>CURADO 201</v>
@@ -4919,13 +5168,13 @@
       <c r="V23" t="str">
         <v/>
       </c>
-      <c r="W23" t="str" s="1">
+      <c r="W23" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X23" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y23" t="str" s="1">
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z23" t="str">
@@ -4934,16 +5183,16 @@
       <c r="AA23" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB23" t="str" s="1">
+      <c r="AB23" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC23" t="str">
         <v/>
       </c>
-      <c r="AD23" t="str" s="1">
+      <c r="AD23" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE23" t="str" s="1">
+      <c r="AE23" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF23" t="str">
@@ -4955,7 +5204,7 @@
       <c r="AH23" t="str">
         <v/>
       </c>
-      <c r="AI23" t="str" s="1">
+      <c r="AI23" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ23" t="str">
@@ -4988,7 +5237,7 @@
       <c r="AS23" t="str">
         <v/>
       </c>
-      <c r="AT23" t="str" s="1">
+      <c r="AT23" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU23" t="str">
@@ -5009,22 +5258,28 @@
       <c r="AZ23" t="str">
         <v/>
       </c>
-      <c r="BA23" t="str" s="1">
+      <c r="BA23" t="str">
+        <v/>
+      </c>
+      <c r="BB23" t="str">
+        <v/>
+      </c>
+      <c r="BC23" t="str">
         <v>M7</v>
       </c>
-      <c r="BB23" t="str" s="1">
+      <c r="BD23" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC23" t="str">
-        <v/>
-      </c>
-      <c r="BD23" t="str">
-        <v/>
-      </c>
-      <c r="BE23" t="str" s="1">
+      <c r="BE23" t="str">
+        <v/>
+      </c>
+      <c r="BF23" t="str">
+        <v/>
+      </c>
+      <c r="BG23" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF23" t="str">
+      <c r="BH23" t="str">
         <v/>
       </c>
     </row>
@@ -5033,7 +5288,7 @@
         <v>SRED50306</v>
       </c>
       <c r="B24" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C24" t="str">
         <v>CURADO 200HG</v>
@@ -5095,13 +5350,13 @@
       <c r="V24" t="str">
         <v/>
       </c>
-      <c r="W24" t="str" s="1">
+      <c r="W24" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X24" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y24" t="str" s="1">
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z24" t="str">
@@ -5110,16 +5365,16 @@
       <c r="AA24" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB24" t="str" s="1">
+      <c r="AB24" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC24" t="str">
         <v/>
       </c>
-      <c r="AD24" t="str" s="1">
+      <c r="AD24" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE24" t="str" s="1">
+      <c r="AE24" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF24" t="str">
@@ -5131,7 +5386,7 @@
       <c r="AH24" t="str">
         <v/>
       </c>
-      <c r="AI24" t="str" s="1">
+      <c r="AI24" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ24" t="str">
@@ -5164,7 +5419,7 @@
       <c r="AS24" t="str">
         <v/>
       </c>
-      <c r="AT24" t="str" s="1">
+      <c r="AT24" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU24" t="str">
@@ -5185,22 +5440,28 @@
       <c r="AZ24" t="str">
         <v/>
       </c>
-      <c r="BA24" t="str" s="1">
+      <c r="BA24" t="str">
+        <v/>
+      </c>
+      <c r="BB24" t="str">
+        <v/>
+      </c>
+      <c r="BC24" t="str">
         <v>M7</v>
       </c>
-      <c r="BB24" t="str" s="1">
+      <c r="BD24" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC24" t="str">
-        <v/>
-      </c>
-      <c r="BD24" t="str">
-        <v/>
-      </c>
-      <c r="BE24" t="str" s="1">
+      <c r="BE24" t="str">
+        <v/>
+      </c>
+      <c r="BF24" t="str">
+        <v/>
+      </c>
+      <c r="BG24" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF24" t="str">
+      <c r="BH24" t="str">
         <v/>
       </c>
     </row>
@@ -5209,7 +5470,7 @@
         <v>SRED50307</v>
       </c>
       <c r="B25" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C25" t="str">
         <v>CURADO 201HG</v>
@@ -5271,13 +5532,13 @@
       <c r="V25" t="str">
         <v/>
       </c>
-      <c r="W25" t="str" s="1">
+      <c r="W25" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X25" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y25" t="str" s="1">
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z25" t="str">
@@ -5286,16 +5547,16 @@
       <c r="AA25" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB25" t="str" s="1">
+      <c r="AB25" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC25" t="str">
         <v/>
       </c>
-      <c r="AD25" t="str" s="1">
+      <c r="AD25" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE25" t="str" s="1">
+      <c r="AE25" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF25" t="str">
@@ -5307,7 +5568,7 @@
       <c r="AH25" t="str">
         <v/>
       </c>
-      <c r="AI25" t="str" s="1">
+      <c r="AI25" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ25" t="str">
@@ -5340,7 +5601,7 @@
       <c r="AS25" t="str">
         <v/>
       </c>
-      <c r="AT25" t="str" s="1">
+      <c r="AT25" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU25" t="str">
@@ -5361,22 +5622,28 @@
       <c r="AZ25" t="str">
         <v/>
       </c>
-      <c r="BA25" t="str" s="1">
+      <c r="BA25" t="str">
+        <v/>
+      </c>
+      <c r="BB25" t="str">
+        <v/>
+      </c>
+      <c r="BC25" t="str">
         <v>M7</v>
       </c>
-      <c r="BB25" t="str" s="1">
+      <c r="BD25" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC25" t="str">
-        <v/>
-      </c>
-      <c r="BD25" t="str">
-        <v/>
-      </c>
-      <c r="BE25" t="str" s="1">
+      <c r="BE25" t="str">
+        <v/>
+      </c>
+      <c r="BF25" t="str">
+        <v/>
+      </c>
+      <c r="BG25" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF25" t="str">
+      <c r="BH25" t="str">
         <v/>
       </c>
     </row>
@@ -5385,7 +5652,7 @@
         <v>SRED50308</v>
       </c>
       <c r="B26" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C26" t="str">
         <v>CURADO 200XG</v>
@@ -5447,13 +5714,13 @@
       <c r="V26" t="str">
         <v/>
       </c>
-      <c r="W26" t="str" s="1">
+      <c r="W26" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X26" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y26" t="str" s="1">
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z26" t="str">
@@ -5462,16 +5729,16 @@
       <c r="AA26" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB26" t="str" s="1">
+      <c r="AB26" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC26" t="str">
         <v/>
       </c>
-      <c r="AD26" t="str" s="1">
+      <c r="AD26" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE26" t="str" s="1">
+      <c r="AE26" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF26" t="str">
@@ -5483,7 +5750,7 @@
       <c r="AH26" t="str">
         <v/>
       </c>
-      <c r="AI26" t="str" s="1">
+      <c r="AI26" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ26" t="str">
@@ -5516,7 +5783,7 @@
       <c r="AS26" t="str">
         <v/>
       </c>
-      <c r="AT26" t="str" s="1">
+      <c r="AT26" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU26" t="str">
@@ -5537,22 +5804,28 @@
       <c r="AZ26" t="str">
         <v/>
       </c>
-      <c r="BA26" t="str" s="1">
+      <c r="BA26" t="str">
+        <v/>
+      </c>
+      <c r="BB26" t="str">
+        <v/>
+      </c>
+      <c r="BC26" t="str">
         <v>M7</v>
       </c>
-      <c r="BB26" t="str" s="1">
+      <c r="BD26" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC26" t="str">
-        <v/>
-      </c>
-      <c r="BD26" t="str">
-        <v/>
-      </c>
-      <c r="BE26" t="str" s="1">
+      <c r="BE26" t="str">
+        <v/>
+      </c>
+      <c r="BF26" t="str">
+        <v/>
+      </c>
+      <c r="BG26" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF26" t="str">
+      <c r="BH26" t="str">
         <v/>
       </c>
     </row>
@@ -5561,7 +5834,7 @@
         <v>SRED50309</v>
       </c>
       <c r="B27" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_200</v>
       </c>
       <c r="C27" t="str">
         <v>CURADO 201XG</v>
@@ -5623,13 +5896,13 @@
       <c r="V27" t="str">
         <v/>
       </c>
-      <c r="W27" t="str" s="1">
+      <c r="W27" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X27" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y27" t="str" s="1">
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z27" t="str">
@@ -5638,16 +5911,16 @@
       <c r="AA27" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB27" t="str" s="1">
+      <c r="AB27" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC27" t="str">
         <v/>
       </c>
-      <c r="AD27" t="str" s="1">
+      <c r="AD27" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE27" t="str" s="1">
+      <c r="AE27" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF27" t="str">
@@ -5659,7 +5932,7 @@
       <c r="AH27" t="str">
         <v/>
       </c>
-      <c r="AI27" t="str" s="1">
+      <c r="AI27" t="str">
         <v>淡水重饵</v>
       </c>
       <c r="AJ27" t="str">
@@ -5692,7 +5965,7 @@
       <c r="AS27" t="str">
         <v/>
       </c>
-      <c r="AT27" t="str" s="1">
+      <c r="AT27" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU27" t="str">
@@ -5713,22 +5986,28 @@
       <c r="AZ27" t="str">
         <v/>
       </c>
-      <c r="BA27" t="str" s="1">
+      <c r="BA27" t="str">
+        <v/>
+      </c>
+      <c r="BB27" t="str">
+        <v/>
+      </c>
+      <c r="BC27" t="str">
         <v>M7</v>
       </c>
-      <c r="BB27" t="str" s="1">
+      <c r="BD27" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC27" t="str">
-        <v/>
-      </c>
-      <c r="BD27" t="str">
-        <v/>
-      </c>
-      <c r="BE27" t="str" s="1">
+      <c r="BE27" t="str">
+        <v/>
+      </c>
+      <c r="BF27" t="str">
+        <v/>
+      </c>
+      <c r="BG27" t="str">
         <v>重饵 / 泛用</v>
       </c>
-      <c r="BF27" t="str">
+      <c r="BH27" t="str">
         <v/>
       </c>
     </row>
@@ -5737,7 +6016,7 @@
         <v>SRED50316</v>
       </c>
       <c r="B28" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_300</v>
       </c>
       <c r="C28" t="str">
         <v>CURADO 300</v>
@@ -5799,13 +6078,13 @@
       <c r="V28" t="str">
         <v/>
       </c>
-      <c r="W28" t="str" s="1">
+      <c r="W28" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X28" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y28" t="str" s="1">
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z28" t="str">
@@ -5814,16 +6093,16 @@
       <c r="AA28" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB28" t="str" s="1">
+      <c r="AB28" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC28" t="str">
         <v/>
       </c>
-      <c r="AD28" t="str" s="1">
+      <c r="AD28" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE28" t="str" s="1">
+      <c r="AE28" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF28" t="str">
@@ -5835,8 +6114,8 @@
       <c r="AH28" t="str">
         <v/>
       </c>
-      <c r="AI28" t="str" s="1">
-        <v>淡水重饵</v>
+      <c r="AI28" t="str">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ28" t="str">
         <v/>
@@ -5868,7 +6147,7 @@
       <c r="AS28" t="str">
         <v/>
       </c>
-      <c r="AT28" t="str" s="1">
+      <c r="AT28" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU28" t="str">
@@ -5889,22 +6168,28 @@
       <c r="AZ28" t="str">
         <v/>
       </c>
-      <c r="BA28" t="str" s="1">
+      <c r="BA28" t="str">
+        <v/>
+      </c>
+      <c r="BB28" t="str">
+        <v/>
+      </c>
+      <c r="BC28" t="str">
         <v>M7</v>
       </c>
-      <c r="BB28" t="str" s="1">
+      <c r="BD28" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC28" t="str">
-        <v/>
-      </c>
-      <c r="BD28" t="str">
-        <v/>
-      </c>
-      <c r="BE28" t="str" s="1">
-        <v>重饵 / 泛用</v>
+      <c r="BE28" t="str">
+        <v/>
       </c>
       <c r="BF28" t="str">
+        <v/>
+      </c>
+      <c r="BG28" t="str">
+        <v>重饵 / 巨物</v>
+      </c>
+      <c r="BH28" t="str">
         <v/>
       </c>
     </row>
@@ -5913,7 +6198,7 @@
         <v>SRED50317</v>
       </c>
       <c r="B29" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_300</v>
       </c>
       <c r="C29" t="str">
         <v>CURADO 301</v>
@@ -5975,13 +6260,13 @@
       <c r="V29" t="str">
         <v/>
       </c>
-      <c r="W29" t="str" s="1">
+      <c r="W29" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X29" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y29" t="str" s="1">
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z29" t="str">
@@ -5990,16 +6275,16 @@
       <c r="AA29" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB29" t="str" s="1">
+      <c r="AB29" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC29" t="str">
         <v/>
       </c>
-      <c r="AD29" t="str" s="1">
+      <c r="AD29" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE29" t="str" s="1">
+      <c r="AE29" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF29" t="str">
@@ -6011,8 +6296,8 @@
       <c r="AH29" t="str">
         <v/>
       </c>
-      <c r="AI29" t="str" s="1">
-        <v>淡水重饵</v>
+      <c r="AI29" t="str">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ29" t="str">
         <v/>
@@ -6044,7 +6329,7 @@
       <c r="AS29" t="str">
         <v/>
       </c>
-      <c r="AT29" t="str" s="1">
+      <c r="AT29" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU29" t="str">
@@ -6065,22 +6350,28 @@
       <c r="AZ29" t="str">
         <v/>
       </c>
-      <c r="BA29" t="str" s="1">
+      <c r="BA29" t="str">
+        <v/>
+      </c>
+      <c r="BB29" t="str">
+        <v/>
+      </c>
+      <c r="BC29" t="str">
         <v>M7</v>
       </c>
-      <c r="BB29" t="str" s="1">
+      <c r="BD29" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC29" t="str">
-        <v/>
-      </c>
-      <c r="BD29" t="str">
-        <v/>
-      </c>
-      <c r="BE29" t="str" s="1">
-        <v>重饵 / 泛用</v>
+      <c r="BE29" t="str">
+        <v/>
       </c>
       <c r="BF29" t="str">
+        <v/>
+      </c>
+      <c r="BG29" t="str">
+        <v>重饵 / 巨物</v>
+      </c>
+      <c r="BH29" t="str">
         <v/>
       </c>
     </row>
@@ -6089,7 +6380,7 @@
         <v>SRED50318</v>
       </c>
       <c r="B30" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_300</v>
       </c>
       <c r="C30" t="str">
         <v>CURADO 300HG</v>
@@ -6151,13 +6442,13 @@
       <c r="V30" t="str">
         <v/>
       </c>
-      <c r="W30" t="str" s="1">
+      <c r="W30" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X30" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y30" t="str" s="1">
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z30" t="str">
@@ -6166,16 +6457,16 @@
       <c r="AA30" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB30" t="str" s="1">
+      <c r="AB30" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC30" t="str">
         <v/>
       </c>
-      <c r="AD30" t="str" s="1">
+      <c r="AD30" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE30" t="str" s="1">
+      <c r="AE30" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF30" t="str">
@@ -6187,8 +6478,8 @@
       <c r="AH30" t="str">
         <v/>
       </c>
-      <c r="AI30" t="str" s="1">
-        <v>淡水重饵</v>
+      <c r="AI30" t="str">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ30" t="str">
         <v/>
@@ -6220,7 +6511,7 @@
       <c r="AS30" t="str">
         <v/>
       </c>
-      <c r="AT30" t="str" s="1">
+      <c r="AT30" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU30" t="str">
@@ -6241,22 +6532,28 @@
       <c r="AZ30" t="str">
         <v/>
       </c>
-      <c r="BA30" t="str" s="1">
+      <c r="BA30" t="str">
+        <v/>
+      </c>
+      <c r="BB30" t="str">
+        <v/>
+      </c>
+      <c r="BC30" t="str">
         <v>M7</v>
       </c>
-      <c r="BB30" t="str" s="1">
+      <c r="BD30" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC30" t="str">
-        <v/>
-      </c>
-      <c r="BD30" t="str">
-        <v/>
-      </c>
-      <c r="BE30" t="str" s="1">
-        <v>重饵 / 泛用</v>
+      <c r="BE30" t="str">
+        <v/>
       </c>
       <c r="BF30" t="str">
+        <v/>
+      </c>
+      <c r="BG30" t="str">
+        <v>重饵 / 巨物</v>
+      </c>
+      <c r="BH30" t="str">
         <v/>
       </c>
     </row>
@@ -6265,7 +6562,7 @@
         <v>SRED50319</v>
       </c>
       <c r="B31" t="str">
-        <v>SRE5054</v>
+        <v>SRE5054_300</v>
       </c>
       <c r="C31" t="str">
         <v>CURADO 301HG</v>
@@ -6327,13 +6624,13 @@
       <c r="V31" t="str">
         <v/>
       </c>
-      <c r="W31" t="str" s="1">
+      <c r="W31" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X31" t="str" s="1">
-        <v>Genuine Spool 22 CURADO DC</v>
-      </c>
-      <c r="Y31" t="str" s="1">
+      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z31" t="str">
@@ -6342,16 +6639,16 @@
       <c r="AA31" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB31" t="str" s="1">
+      <c r="AB31" t="str">
         <v>Paddle</v>
       </c>
       <c r="AC31" t="str">
         <v/>
       </c>
-      <c r="AD31" t="str" s="1">
+      <c r="AD31" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE31" t="str" s="1">
+      <c r="AE31" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF31" t="str">
@@ -6363,8 +6660,8 @@
       <c r="AH31" t="str">
         <v/>
       </c>
-      <c r="AI31" t="str" s="1">
-        <v>淡水重饵</v>
+      <c r="AI31" t="str">
+        <v>重饵 / 巨物</v>
       </c>
       <c r="AJ31" t="str">
         <v/>
@@ -6396,7 +6693,7 @@
       <c r="AS31" t="str">
         <v/>
       </c>
-      <c r="AT31" t="str" s="1">
+      <c r="AT31" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU31" t="str">
@@ -6417,22 +6714,28 @@
       <c r="AZ31" t="str">
         <v/>
       </c>
-      <c r="BA31" t="str" s="1">
+      <c r="BA31" t="str">
+        <v/>
+      </c>
+      <c r="BB31" t="str">
+        <v/>
+      </c>
+      <c r="BC31" t="str">
         <v>M7</v>
       </c>
-      <c r="BB31" t="str" s="1">
+      <c r="BD31" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC31" t="str">
-        <v/>
-      </c>
-      <c r="BD31" t="str">
-        <v/>
-      </c>
-      <c r="BE31" t="str" s="1">
-        <v>重饵 / 泛用</v>
+      <c r="BE31" t="str">
+        <v/>
       </c>
       <c r="BF31" t="str">
+        <v/>
+      </c>
+      <c r="BG31" t="str">
+        <v>重饵 / 巨物</v>
+      </c>
+      <c r="BH31" t="str">
         <v/>
       </c>
     </row>
@@ -6494,7 +6797,7 @@
       <c r="S32" t="str">
         <v>19</v>
       </c>
-      <c r="T32" t="str" s="1">
+      <c r="T32" t="str">
         <v>11.32</v>
       </c>
       <c r="U32" t="str">
@@ -6503,13 +6806,13 @@
       <c r="V32" t="str">
         <v/>
       </c>
-      <c r="W32" t="str" s="1">
+      <c r="W32" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X32" t="str" s="1">
+      <c r="X32" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y32" t="str" s="1">
+      <c r="Y32" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z32" t="str">
@@ -6521,13 +6824,13 @@
       <c r="AB32" t="str">
         <v/>
       </c>
-      <c r="AC32" t="str" s="1">
+      <c r="AC32" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD32" t="str" s="1">
+      <c r="AD32" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE32" t="str" s="1">
+      <c r="AE32" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF32" t="str">
@@ -6539,7 +6842,7 @@
       <c r="AH32" t="str">
         <v/>
       </c>
-      <c r="AI32" t="str" s="1">
+      <c r="AI32" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ32" t="str">
@@ -6572,7 +6875,7 @@
       <c r="AS32" t="str">
         <v/>
       </c>
-      <c r="AT32" t="str" s="1">
+      <c r="AT32" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU32" t="str">
@@ -6593,22 +6896,28 @@
       <c r="AZ32" t="str">
         <v/>
       </c>
-      <c r="BA32" t="str" s="1">
+      <c r="BA32" t="str">
+        <v/>
+      </c>
+      <c r="BB32" t="str">
+        <v/>
+      </c>
+      <c r="BC32" t="str">
         <v>M7</v>
       </c>
-      <c r="BB32" t="str">
+      <c r="BD32" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC32" t="str">
-        <v/>
-      </c>
-      <c r="BD32" t="str">
-        <v/>
-      </c>
-      <c r="BE32" t="str" s="1">
+      <c r="BE32" t="str">
+        <v/>
+      </c>
+      <c r="BF32" t="str">
+        <v/>
+      </c>
+      <c r="BG32" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF32" t="str">
+      <c r="BH32" t="str">
         <v/>
       </c>
     </row>
@@ -6670,7 +6979,7 @@
       <c r="S33" t="str">
         <v>19</v>
       </c>
-      <c r="T33" t="str" s="1">
+      <c r="T33" t="str">
         <v>11.32</v>
       </c>
       <c r="U33" t="str">
@@ -6679,13 +6988,13 @@
       <c r="V33" t="str">
         <v/>
       </c>
-      <c r="W33" t="str" s="1">
+      <c r="W33" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X33" t="str" s="1">
+      <c r="X33" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y33" t="str" s="1">
+      <c r="Y33" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z33" t="str">
@@ -6697,13 +7006,13 @@
       <c r="AB33" t="str">
         <v/>
       </c>
-      <c r="AC33" t="str" s="1">
+      <c r="AC33" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD33" t="str" s="1">
+      <c r="AD33" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE33" t="str" s="1">
+      <c r="AE33" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF33" t="str">
@@ -6715,7 +7024,7 @@
       <c r="AH33" t="str">
         <v/>
       </c>
-      <c r="AI33" t="str" s="1">
+      <c r="AI33" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ33" t="str">
@@ -6748,7 +7057,7 @@
       <c r="AS33" t="str">
         <v/>
       </c>
-      <c r="AT33" t="str" s="1">
+      <c r="AT33" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU33" t="str">
@@ -6769,22 +7078,28 @@
       <c r="AZ33" t="str">
         <v/>
       </c>
-      <c r="BA33" t="str" s="1">
+      <c r="BA33" t="str">
+        <v/>
+      </c>
+      <c r="BB33" t="str">
+        <v/>
+      </c>
+      <c r="BC33" t="str">
         <v>M7</v>
       </c>
-      <c r="BB33" t="str">
+      <c r="BD33" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC33" t="str">
-        <v/>
-      </c>
-      <c r="BD33" t="str">
-        <v/>
-      </c>
-      <c r="BE33" t="str" s="1">
+      <c r="BE33" t="str">
+        <v/>
+      </c>
+      <c r="BF33" t="str">
+        <v/>
+      </c>
+      <c r="BG33" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF33" t="str">
+      <c r="BH33" t="str">
         <v/>
       </c>
     </row>
@@ -6846,7 +7161,7 @@
       <c r="S34" t="str">
         <v>19</v>
       </c>
-      <c r="T34" t="str" s="1">
+      <c r="T34" t="str">
         <v>11.32</v>
       </c>
       <c r="U34" t="str">
@@ -6855,13 +7170,13 @@
       <c r="V34" t="str">
         <v/>
       </c>
-      <c r="W34" t="str" s="1">
+      <c r="W34" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X34" t="str" s="1">
+      <c r="X34" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y34" t="str" s="1">
+      <c r="Y34" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z34" t="str">
@@ -6873,13 +7188,13 @@
       <c r="AB34" t="str">
         <v/>
       </c>
-      <c r="AC34" t="str" s="1">
+      <c r="AC34" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD34" t="str" s="1">
+      <c r="AD34" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE34" t="str" s="1">
+      <c r="AE34" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF34" t="str">
@@ -6891,7 +7206,7 @@
       <c r="AH34" t="str">
         <v/>
       </c>
-      <c r="AI34" t="str" s="1">
+      <c r="AI34" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ34" t="str">
@@ -6924,7 +7239,7 @@
       <c r="AS34" t="str">
         <v/>
       </c>
-      <c r="AT34" t="str" s="1">
+      <c r="AT34" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU34" t="str">
@@ -6945,22 +7260,28 @@
       <c r="AZ34" t="str">
         <v/>
       </c>
-      <c r="BA34" t="str" s="1">
+      <c r="BA34" t="str">
+        <v/>
+      </c>
+      <c r="BB34" t="str">
+        <v/>
+      </c>
+      <c r="BC34" t="str">
         <v>M7</v>
       </c>
-      <c r="BB34" t="str">
+      <c r="BD34" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC34" t="str">
-        <v/>
-      </c>
-      <c r="BD34" t="str">
-        <v/>
-      </c>
-      <c r="BE34" t="str" s="1">
+      <c r="BE34" t="str">
+        <v/>
+      </c>
+      <c r="BF34" t="str">
+        <v/>
+      </c>
+      <c r="BG34" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF34" t="str">
+      <c r="BH34" t="str">
         <v/>
       </c>
     </row>
@@ -7022,7 +7343,7 @@
       <c r="S35" t="str">
         <v>19</v>
       </c>
-      <c r="T35" t="str" s="1">
+      <c r="T35" t="str">
         <v>11.32</v>
       </c>
       <c r="U35" t="str">
@@ -7031,13 +7352,13 @@
       <c r="V35" t="str">
         <v/>
       </c>
-      <c r="W35" t="str" s="1">
+      <c r="W35" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X35" t="str" s="1">
+      <c r="X35" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y35" t="str" s="1">
+      <c r="Y35" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z35" t="str">
@@ -7049,13 +7370,13 @@
       <c r="AB35" t="str">
         <v/>
       </c>
-      <c r="AC35" t="str" s="1">
+      <c r="AC35" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD35" t="str" s="1">
+      <c r="AD35" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE35" t="str" s="1">
+      <c r="AE35" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF35" t="str">
@@ -7067,7 +7388,7 @@
       <c r="AH35" t="str">
         <v/>
       </c>
-      <c r="AI35" t="str" s="1">
+      <c r="AI35" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ35" t="str">
@@ -7100,7 +7421,7 @@
       <c r="AS35" t="str">
         <v/>
       </c>
-      <c r="AT35" t="str" s="1">
+      <c r="AT35" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU35" t="str">
@@ -7121,22 +7442,28 @@
       <c r="AZ35" t="str">
         <v/>
       </c>
-      <c r="BA35" t="str" s="1">
+      <c r="BA35" t="str">
+        <v/>
+      </c>
+      <c r="BB35" t="str">
+        <v/>
+      </c>
+      <c r="BC35" t="str">
         <v>M7</v>
       </c>
-      <c r="BB35" t="str">
+      <c r="BD35" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC35" t="str">
-        <v/>
-      </c>
-      <c r="BD35" t="str">
-        <v/>
-      </c>
-      <c r="BE35" t="str" s="1">
+      <c r="BE35" t="str">
+        <v/>
+      </c>
+      <c r="BF35" t="str">
+        <v/>
+      </c>
+      <c r="BG35" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF35" t="str">
+      <c r="BH35" t="str">
         <v/>
       </c>
     </row>
@@ -7198,7 +7525,7 @@
       <c r="S36" t="str">
         <v>19</v>
       </c>
-      <c r="T36" t="str" s="1">
+      <c r="T36" t="str">
         <v>11.32</v>
       </c>
       <c r="U36" t="str">
@@ -7207,13 +7534,13 @@
       <c r="V36" t="str">
         <v/>
       </c>
-      <c r="W36" t="str" s="1">
+      <c r="W36" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X36" t="str" s="1">
+      <c r="X36" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y36" t="str" s="1">
+      <c r="Y36" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z36" t="str">
@@ -7225,13 +7552,13 @@
       <c r="AB36" t="str">
         <v/>
       </c>
-      <c r="AC36" t="str" s="1">
+      <c r="AC36" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD36" t="str" s="1">
+      <c r="AD36" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE36" t="str" s="1">
+      <c r="AE36" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF36" t="str">
@@ -7243,7 +7570,7 @@
       <c r="AH36" t="str">
         <v/>
       </c>
-      <c r="AI36" t="str" s="1">
+      <c r="AI36" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ36" t="str">
@@ -7276,7 +7603,7 @@
       <c r="AS36" t="str">
         <v/>
       </c>
-      <c r="AT36" t="str" s="1">
+      <c r="AT36" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU36" t="str">
@@ -7297,22 +7624,28 @@
       <c r="AZ36" t="str">
         <v/>
       </c>
-      <c r="BA36" t="str" s="1">
+      <c r="BA36" t="str">
+        <v/>
+      </c>
+      <c r="BB36" t="str">
+        <v/>
+      </c>
+      <c r="BC36" t="str">
         <v>M7</v>
       </c>
-      <c r="BB36" t="str">
+      <c r="BD36" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC36" t="str">
-        <v/>
-      </c>
-      <c r="BD36" t="str">
-        <v/>
-      </c>
-      <c r="BE36" t="str" s="1">
+      <c r="BE36" t="str">
+        <v/>
+      </c>
+      <c r="BF36" t="str">
+        <v/>
+      </c>
+      <c r="BG36" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF36" t="str">
+      <c r="BH36" t="str">
         <v/>
       </c>
     </row>
@@ -7374,7 +7707,7 @@
       <c r="S37" t="str">
         <v>19</v>
       </c>
-      <c r="T37" t="str" s="1">
+      <c r="T37" t="str">
         <v>11.32</v>
       </c>
       <c r="U37" t="str">
@@ -7383,13 +7716,13 @@
       <c r="V37" t="str">
         <v/>
       </c>
-      <c r="W37" t="str" s="1">
+      <c r="W37" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X37" t="str" s="1">
+      <c r="X37" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y37" t="str" s="1">
+      <c r="Y37" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z37" t="str">
@@ -7401,13 +7734,13 @@
       <c r="AB37" t="str">
         <v/>
       </c>
-      <c r="AC37" t="str" s="1">
+      <c r="AC37" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD37" t="str" s="1">
+      <c r="AD37" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE37" t="str" s="1">
+      <c r="AE37" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF37" t="str">
@@ -7419,7 +7752,7 @@
       <c r="AH37" t="str">
         <v/>
       </c>
-      <c r="AI37" t="str" s="1">
+      <c r="AI37" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ37" t="str">
@@ -7452,7 +7785,7 @@
       <c r="AS37" t="str">
         <v/>
       </c>
-      <c r="AT37" t="str" s="1">
+      <c r="AT37" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU37" t="str">
@@ -7473,22 +7806,28 @@
       <c r="AZ37" t="str">
         <v/>
       </c>
-      <c r="BA37" t="str" s="1">
+      <c r="BA37" t="str">
+        <v/>
+      </c>
+      <c r="BB37" t="str">
+        <v/>
+      </c>
+      <c r="BC37" t="str">
         <v>M7</v>
       </c>
-      <c r="BB37" t="str">
+      <c r="BD37" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC37" t="str">
-        <v/>
-      </c>
-      <c r="BD37" t="str">
-        <v/>
-      </c>
-      <c r="BE37" t="str" s="1">
+      <c r="BE37" t="str">
+        <v/>
+      </c>
+      <c r="BF37" t="str">
+        <v/>
+      </c>
+      <c r="BG37" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF37" t="str">
+      <c r="BH37" t="str">
         <v/>
       </c>
     </row>
@@ -7550,7 +7889,7 @@
       <c r="S38" t="str">
         <v>19</v>
       </c>
-      <c r="T38" t="str" s="1">
+      <c r="T38" t="str">
         <v>11.32</v>
       </c>
       <c r="U38" t="str">
@@ -7559,13 +7898,13 @@
       <c r="V38" t="str">
         <v/>
       </c>
-      <c r="W38" t="str" s="1">
+      <c r="W38" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X38" t="str" s="1">
+      <c r="X38" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y38" t="str" s="1">
+      <c r="Y38" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z38" t="str">
@@ -7577,13 +7916,13 @@
       <c r="AB38" t="str">
         <v/>
       </c>
-      <c r="AC38" t="str" s="1">
+      <c r="AC38" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD38" t="str" s="1">
+      <c r="AD38" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE38" t="str" s="1">
+      <c r="AE38" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF38" t="str">
@@ -7595,7 +7934,7 @@
       <c r="AH38" t="str">
         <v/>
       </c>
-      <c r="AI38" t="str" s="1">
+      <c r="AI38" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ38" t="str">
@@ -7628,7 +7967,7 @@
       <c r="AS38" t="str">
         <v/>
       </c>
-      <c r="AT38" t="str" s="1">
+      <c r="AT38" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU38" t="str">
@@ -7647,24 +7986,30 @@
         <v/>
       </c>
       <c r="AZ38" t="str">
-        <v/>
-      </c>
-      <c r="BA38" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041128</v>
+      </c>
+      <c r="BA38" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB38" t="str">
+        <v/>
+      </c>
+      <c r="BC38" t="str">
         <v>M7</v>
       </c>
-      <c r="BB38" t="str">
+      <c r="BD38" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC38" t="str">
-        <v/>
-      </c>
-      <c r="BD38" t="str">
-        <v/>
-      </c>
-      <c r="BE38" t="str" s="1">
+      <c r="BE38" t="str">
+        <v/>
+      </c>
+      <c r="BF38" t="str">
+        <v/>
+      </c>
+      <c r="BG38" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF38" t="str">
+      <c r="BH38" t="str">
         <v/>
       </c>
     </row>
@@ -7726,7 +8071,7 @@
       <c r="S39" t="str">
         <v>19</v>
       </c>
-      <c r="T39" t="str" s="1">
+      <c r="T39" t="str">
         <v>11.32</v>
       </c>
       <c r="U39" t="str">
@@ -7735,13 +8080,13 @@
       <c r="V39" t="str">
         <v/>
       </c>
-      <c r="W39" t="str" s="1">
+      <c r="W39" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X39" t="str" s="1">
+      <c r="X39" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y39" t="str" s="1">
+      <c r="Y39" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z39" t="str">
@@ -7753,13 +8098,13 @@
       <c r="AB39" t="str">
         <v/>
       </c>
-      <c r="AC39" t="str" s="1">
+      <c r="AC39" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD39" t="str" s="1">
+      <c r="AD39" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE39" t="str" s="1">
+      <c r="AE39" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF39" t="str">
@@ -7771,7 +8116,7 @@
       <c r="AH39" t="str">
         <v/>
       </c>
-      <c r="AI39" t="str" s="1">
+      <c r="AI39" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ39" t="str">
@@ -7804,7 +8149,7 @@
       <c r="AS39" t="str">
         <v/>
       </c>
-      <c r="AT39" t="str" s="1">
+      <c r="AT39" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU39" t="str">
@@ -7823,24 +8168,30 @@
         <v/>
       </c>
       <c r="AZ39" t="str">
-        <v/>
-      </c>
-      <c r="BA39" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041135</v>
+      </c>
+      <c r="BA39" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB39" t="str">
+        <v/>
+      </c>
+      <c r="BC39" t="str">
         <v>M7</v>
       </c>
-      <c r="BB39" t="str">
+      <c r="BD39" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC39" t="str">
-        <v/>
-      </c>
-      <c r="BD39" t="str">
-        <v/>
-      </c>
-      <c r="BE39" t="str" s="1">
+      <c r="BE39" t="str">
+        <v/>
+      </c>
+      <c r="BF39" t="str">
+        <v/>
+      </c>
+      <c r="BG39" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF39" t="str">
+      <c r="BH39" t="str">
         <v/>
       </c>
     </row>
@@ -7902,7 +8253,7 @@
       <c r="S40" t="str">
         <v>19</v>
       </c>
-      <c r="T40" t="str" s="1">
+      <c r="T40" t="str">
         <v>11.32</v>
       </c>
       <c r="U40" t="str">
@@ -7911,13 +8262,13 @@
       <c r="V40" t="str">
         <v/>
       </c>
-      <c r="W40" t="str" s="1">
+      <c r="W40" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X40" t="str" s="1">
+      <c r="X40" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y40" t="str" s="1">
+      <c r="Y40" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z40" t="str">
@@ -7929,13 +8280,13 @@
       <c r="AB40" t="str">
         <v/>
       </c>
-      <c r="AC40" t="str" s="1">
+      <c r="AC40" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD40" t="str" s="1">
+      <c r="AD40" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE40" t="str" s="1">
+      <c r="AE40" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF40" t="str">
@@ -7947,7 +8298,7 @@
       <c r="AH40" t="str">
         <v/>
       </c>
-      <c r="AI40" t="str" s="1">
+      <c r="AI40" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ40" t="str">
@@ -7980,7 +8331,7 @@
       <c r="AS40" t="str">
         <v/>
       </c>
-      <c r="AT40" t="str" s="1">
+      <c r="AT40" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU40" t="str">
@@ -7999,24 +8350,30 @@
         <v/>
       </c>
       <c r="AZ40" t="str">
-        <v/>
-      </c>
-      <c r="BA40" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041142</v>
+      </c>
+      <c r="BA40" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB40" t="str">
+        <v/>
+      </c>
+      <c r="BC40" t="str">
         <v>M7</v>
       </c>
-      <c r="BB40" t="str">
+      <c r="BD40" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC40" t="str">
-        <v/>
-      </c>
-      <c r="BD40" t="str">
-        <v/>
-      </c>
-      <c r="BE40" t="str" s="1">
+      <c r="BE40" t="str">
+        <v/>
+      </c>
+      <c r="BF40" t="str">
+        <v/>
+      </c>
+      <c r="BG40" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF40" t="str">
+      <c r="BH40" t="str">
         <v/>
       </c>
     </row>
@@ -8078,7 +8435,7 @@
       <c r="S41" t="str">
         <v>19</v>
       </c>
-      <c r="T41" t="str" s="1">
+      <c r="T41" t="str">
         <v>11.32</v>
       </c>
       <c r="U41" t="str">
@@ -8087,13 +8444,13 @@
       <c r="V41" t="str">
         <v/>
       </c>
-      <c r="W41" t="str" s="1">
+      <c r="W41" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X41" t="str" s="1">
+      <c r="X41" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y41" t="str" s="1">
+      <c r="Y41" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z41" t="str">
@@ -8105,13 +8462,13 @@
       <c r="AB41" t="str">
         <v/>
       </c>
-      <c r="AC41" t="str" s="1">
+      <c r="AC41" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD41" t="str" s="1">
+      <c r="AD41" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE41" t="str" s="1">
+      <c r="AE41" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF41" t="str">
@@ -8123,7 +8480,7 @@
       <c r="AH41" t="str">
         <v/>
       </c>
-      <c r="AI41" t="str" s="1">
+      <c r="AI41" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ41" t="str">
@@ -8156,7 +8513,7 @@
       <c r="AS41" t="str">
         <v/>
       </c>
-      <c r="AT41" t="str" s="1">
+      <c r="AT41" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU41" t="str">
@@ -8175,24 +8532,30 @@
         <v/>
       </c>
       <c r="AZ41" t="str">
-        <v/>
-      </c>
-      <c r="BA41" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041159</v>
+      </c>
+      <c r="BA41" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB41" t="str">
+        <v/>
+      </c>
+      <c r="BC41" t="str">
         <v>M7</v>
       </c>
-      <c r="BB41" t="str">
+      <c r="BD41" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC41" t="str">
-        <v/>
-      </c>
-      <c r="BD41" t="str">
-        <v/>
-      </c>
-      <c r="BE41" t="str" s="1">
+      <c r="BE41" t="str">
+        <v/>
+      </c>
+      <c r="BF41" t="str">
+        <v/>
+      </c>
+      <c r="BG41" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF41" t="str">
+      <c r="BH41" t="str">
         <v/>
       </c>
     </row>
@@ -8254,7 +8617,7 @@
       <c r="S42" t="str">
         <v>19</v>
       </c>
-      <c r="T42" t="str" s="1">
+      <c r="T42" t="str">
         <v>11.32</v>
       </c>
       <c r="U42" t="str">
@@ -8263,13 +8626,13 @@
       <c r="V42" t="str">
         <v/>
       </c>
-      <c r="W42" t="str" s="1">
+      <c r="W42" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X42" t="str" s="1">
+      <c r="X42" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y42" t="str" s="1">
+      <c r="Y42" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z42" t="str">
@@ -8281,13 +8644,13 @@
       <c r="AB42" t="str">
         <v/>
       </c>
-      <c r="AC42" t="str" s="1">
+      <c r="AC42" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD42" t="str" s="1">
+      <c r="AD42" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE42" t="str" s="1">
+      <c r="AE42" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF42" t="str">
@@ -8299,7 +8662,7 @@
       <c r="AH42" t="str">
         <v/>
       </c>
-      <c r="AI42" t="str" s="1">
+      <c r="AI42" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ42" t="str">
@@ -8332,7 +8695,7 @@
       <c r="AS42" t="str">
         <v/>
       </c>
-      <c r="AT42" t="str" s="1">
+      <c r="AT42" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU42" t="str">
@@ -8351,24 +8714,30 @@
         <v/>
       </c>
       <c r="AZ42" t="str">
-        <v/>
-      </c>
-      <c r="BA42" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041166</v>
+      </c>
+      <c r="BA42" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB42" t="str">
+        <v/>
+      </c>
+      <c r="BC42" t="str">
         <v>M7</v>
       </c>
-      <c r="BB42" t="str">
+      <c r="BD42" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC42" t="str">
-        <v/>
-      </c>
-      <c r="BD42" t="str">
-        <v/>
-      </c>
-      <c r="BE42" t="str" s="1">
+      <c r="BE42" t="str">
+        <v/>
+      </c>
+      <c r="BF42" t="str">
+        <v/>
+      </c>
+      <c r="BG42" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF42" t="str">
+      <c r="BH42" t="str">
         <v/>
       </c>
     </row>
@@ -8430,7 +8799,7 @@
       <c r="S43" t="str">
         <v>19</v>
       </c>
-      <c r="T43" t="str" s="1">
+      <c r="T43" t="str">
         <v>11.32</v>
       </c>
       <c r="U43" t="str">
@@ -8439,13 +8808,13 @@
       <c r="V43" t="str">
         <v/>
       </c>
-      <c r="W43" t="str" s="1">
+      <c r="W43" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X43" t="str" s="1">
+      <c r="X43" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y43" t="str" s="1">
+      <c r="Y43" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z43" t="str">
@@ -8457,13 +8826,13 @@
       <c r="AB43" t="str">
         <v/>
       </c>
-      <c r="AC43" t="str" s="1">
+      <c r="AC43" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD43" t="str" s="1">
+      <c r="AD43" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE43" t="str" s="1">
+      <c r="AE43" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF43" t="str">
@@ -8475,7 +8844,7 @@
       <c r="AH43" t="str">
         <v/>
       </c>
-      <c r="AI43" t="str" s="1">
+      <c r="AI43" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ43" t="str">
@@ -8508,7 +8877,7 @@
       <c r="AS43" t="str">
         <v/>
       </c>
-      <c r="AT43" t="str" s="1">
+      <c r="AT43" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU43" t="str">
@@ -8527,24 +8896,30 @@
         <v/>
       </c>
       <c r="AZ43" t="str">
-        <v/>
-      </c>
-      <c r="BA43" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041173</v>
+      </c>
+      <c r="BA43" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_metanium.pdf</v>
+      </c>
+      <c r="BB43" t="str">
+        <v/>
+      </c>
+      <c r="BC43" t="str">
         <v>M7</v>
       </c>
-      <c r="BB43" t="str">
+      <c r="BD43" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC43" t="str">
-        <v/>
-      </c>
-      <c r="BD43" t="str">
-        <v/>
-      </c>
-      <c r="BE43" t="str" s="1">
+      <c r="BE43" t="str">
+        <v/>
+      </c>
+      <c r="BF43" t="str">
+        <v/>
+      </c>
+      <c r="BG43" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF43" t="str">
+      <c r="BH43" t="str">
         <v/>
       </c>
     </row>
@@ -8606,7 +8981,7 @@
       <c r="S44" t="str">
         <v>19</v>
       </c>
-      <c r="T44" t="str" s="1">
+      <c r="T44" t="str">
         <v>11.32</v>
       </c>
       <c r="U44" t="str">
@@ -8615,13 +8990,13 @@
       <c r="V44" t="str">
         <v/>
       </c>
-      <c r="W44" t="str" s="1">
+      <c r="W44" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X44" t="str" s="1">
+      <c r="X44" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y44" t="str" s="1">
+      <c r="Y44" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z44" t="str">
@@ -8633,13 +9008,13 @@
       <c r="AB44" t="str">
         <v/>
       </c>
-      <c r="AC44" t="str" s="1">
+      <c r="AC44" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD44" t="str" s="1">
+      <c r="AD44" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE44" t="str" s="1">
+      <c r="AE44" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF44" t="str">
@@ -8651,7 +9026,7 @@
       <c r="AH44" t="str">
         <v/>
       </c>
-      <c r="AI44" t="str" s="1">
+      <c r="AI44" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ44" t="str">
@@ -8684,7 +9059,7 @@
       <c r="AS44" t="str">
         <v/>
       </c>
-      <c r="AT44" t="str" s="1">
+      <c r="AT44" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU44" t="str">
@@ -8703,24 +9078,30 @@
         <v/>
       </c>
       <c r="AZ44" t="str">
-        <v/>
-      </c>
-      <c r="BA44" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046116</v>
+      </c>
+      <c r="BA44" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23Metanium%20100.pdf</v>
+      </c>
+      <c r="BB44" t="str">
+        <v/>
+      </c>
+      <c r="BC44" t="str">
         <v>M7</v>
       </c>
-      <c r="BB44" t="str">
+      <c r="BD44" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC44" t="str">
-        <v/>
-      </c>
-      <c r="BD44" t="str">
-        <v/>
-      </c>
-      <c r="BE44" t="str" s="1">
+      <c r="BE44" t="str">
+        <v/>
+      </c>
+      <c r="BF44" t="str">
+        <v/>
+      </c>
+      <c r="BG44" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF44" t="str">
+      <c r="BH44" t="str">
         <v/>
       </c>
     </row>
@@ -8782,7 +9163,7 @@
       <c r="S45" t="str">
         <v>19</v>
       </c>
-      <c r="T45" t="str" s="1">
+      <c r="T45" t="str">
         <v>11.32</v>
       </c>
       <c r="U45" t="str">
@@ -8791,13 +9172,13 @@
       <c r="V45" t="str">
         <v/>
       </c>
-      <c r="W45" t="str" s="1">
+      <c r="W45" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X45" t="str" s="1">
+      <c r="X45" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y45" t="str" s="1">
+      <c r="Y45" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z45" t="str">
@@ -8809,13 +9190,13 @@
       <c r="AB45" t="str">
         <v/>
       </c>
-      <c r="AC45" t="str" s="1">
+      <c r="AC45" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD45" t="str" s="1">
+      <c r="AD45" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE45" t="str" s="1">
+      <c r="AE45" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF45" t="str">
@@ -8827,7 +9208,7 @@
       <c r="AH45" t="str">
         <v/>
       </c>
-      <c r="AI45" t="str" s="1">
+      <c r="AI45" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ45" t="str">
@@ -8860,7 +9241,7 @@
       <c r="AS45" t="str">
         <v/>
       </c>
-      <c r="AT45" t="str" s="1">
+      <c r="AT45" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU45" t="str">
@@ -8879,24 +9260,30 @@
         <v/>
       </c>
       <c r="AZ45" t="str">
-        <v/>
-      </c>
-      <c r="BA45" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046123</v>
+      </c>
+      <c r="BA45" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23Metanium%20100.pdf</v>
+      </c>
+      <c r="BB45" t="str">
+        <v/>
+      </c>
+      <c r="BC45" t="str">
         <v>M7</v>
       </c>
-      <c r="BB45" t="str">
+      <c r="BD45" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC45" t="str">
-        <v/>
-      </c>
-      <c r="BD45" t="str">
-        <v/>
-      </c>
-      <c r="BE45" t="str" s="1">
+      <c r="BE45" t="str">
+        <v/>
+      </c>
+      <c r="BF45" t="str">
+        <v/>
+      </c>
+      <c r="BG45" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF45" t="str">
+      <c r="BH45" t="str">
         <v/>
       </c>
     </row>
@@ -8958,7 +9345,7 @@
       <c r="S46" t="str">
         <v>19</v>
       </c>
-      <c r="T46" t="str" s="1">
+      <c r="T46" t="str">
         <v>11.32</v>
       </c>
       <c r="U46" t="str">
@@ -8967,13 +9354,13 @@
       <c r="V46" t="str">
         <v/>
       </c>
-      <c r="W46" t="str" s="1">
+      <c r="W46" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X46" t="str" s="1">
+      <c r="X46" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y46" t="str" s="1">
+      <c r="Y46" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z46" t="str">
@@ -8985,13 +9372,13 @@
       <c r="AB46" t="str">
         <v/>
       </c>
-      <c r="AC46" t="str" s="1">
+      <c r="AC46" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD46" t="str" s="1">
+      <c r="AD46" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE46" t="str" s="1">
+      <c r="AE46" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF46" t="str">
@@ -9003,7 +9390,7 @@
       <c r="AH46" t="str">
         <v/>
       </c>
-      <c r="AI46" t="str" s="1">
+      <c r="AI46" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ46" t="str">
@@ -9036,7 +9423,7 @@
       <c r="AS46" t="str">
         <v/>
       </c>
-      <c r="AT46" t="str" s="1">
+      <c r="AT46" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU46" t="str">
@@ -9055,24 +9442,30 @@
         <v/>
       </c>
       <c r="AZ46" t="str">
-        <v/>
-      </c>
-      <c r="BA46" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046130</v>
+      </c>
+      <c r="BA46" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23Metanium%20100.pdf</v>
+      </c>
+      <c r="BB46" t="str">
+        <v/>
+      </c>
+      <c r="BC46" t="str">
         <v>M7</v>
       </c>
-      <c r="BB46" t="str">
+      <c r="BD46" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC46" t="str">
-        <v/>
-      </c>
-      <c r="BD46" t="str">
-        <v/>
-      </c>
-      <c r="BE46" t="str" s="1">
+      <c r="BE46" t="str">
+        <v/>
+      </c>
+      <c r="BF46" t="str">
+        <v/>
+      </c>
+      <c r="BG46" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF46" t="str">
+      <c r="BH46" t="str">
         <v/>
       </c>
     </row>
@@ -9134,7 +9527,7 @@
       <c r="S47" t="str">
         <v>19</v>
       </c>
-      <c r="T47" t="str" s="1">
+      <c r="T47" t="str">
         <v>11.32</v>
       </c>
       <c r="U47" t="str">
@@ -9143,13 +9536,13 @@
       <c r="V47" t="str">
         <v/>
       </c>
-      <c r="W47" t="str" s="1">
+      <c r="W47" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X47" t="str" s="1">
+      <c r="X47" t="str">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y47" t="str" s="1">
+      <c r="Y47" t="str">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z47" t="str">
@@ -9161,13 +9554,13 @@
       <c r="AB47" t="str">
         <v/>
       </c>
-      <c r="AC47" t="str" s="1">
+      <c r="AC47" t="str">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD47" t="str" s="1">
+      <c r="AD47" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE47" t="str" s="1">
+      <c r="AE47" t="str">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF47" t="str">
@@ -9179,7 +9572,7 @@
       <c r="AH47" t="str">
         <v/>
       </c>
-      <c r="AI47" t="str" s="1">
+      <c r="AI47" t="str">
         <v>淡水泛用</v>
       </c>
       <c r="AJ47" t="str">
@@ -9212,7 +9605,7 @@
       <c r="AS47" t="str">
         <v/>
       </c>
-      <c r="AT47" t="str" s="1">
+      <c r="AT47" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU47" t="str">
@@ -9231,24 +9624,30 @@
         <v/>
       </c>
       <c r="AZ47" t="str">
-        <v/>
-      </c>
-      <c r="BA47" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046147</v>
+      </c>
+      <c r="BA47" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23Metanium%20100.pdf</v>
+      </c>
+      <c r="BB47" t="str">
+        <v/>
+      </c>
+      <c r="BC47" t="str">
         <v>M7</v>
       </c>
-      <c r="BB47" t="str">
+      <c r="BD47" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC47" t="str">
-        <v/>
-      </c>
-      <c r="BD47" t="str">
-        <v/>
-      </c>
-      <c r="BE47" t="str" s="1">
+      <c r="BE47" t="str">
+        <v/>
+      </c>
+      <c r="BF47" t="str">
+        <v/>
+      </c>
+      <c r="BG47" t="str">
         <v>淡水泛用 / 技巧</v>
       </c>
-      <c r="BF47" t="str">
+      <c r="BH47" t="str">
         <v/>
       </c>
     </row>
@@ -9310,7 +9709,7 @@
       <c r="S48" t="str">
         <v>19</v>
       </c>
-      <c r="T48" t="str" s="1">
+      <c r="T48" t="str">
         <v>12.09</v>
       </c>
       <c r="U48" t="str">
@@ -9319,13 +9718,13 @@
       <c r="V48" t="str">
         <v/>
       </c>
-      <c r="W48" t="str" s="1">
+      <c r="W48" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X48" t="str" s="1">
+      <c r="X48" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y48" t="str" s="1">
+      <c r="Y48" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z48" t="str">
@@ -9340,10 +9739,10 @@
       <c r="AC48" t="str">
         <v/>
       </c>
-      <c r="AD48" t="str" s="1">
+      <c r="AD48" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE48" t="str" s="1">
+      <c r="AE48" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF48" t="str">
@@ -9355,7 +9754,7 @@
       <c r="AH48" t="str">
         <v/>
       </c>
-      <c r="AI48" t="str" s="1">
+      <c r="AI48" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ48" t="str">
@@ -9388,7 +9787,7 @@
       <c r="AS48" t="str">
         <v>是</v>
       </c>
-      <c r="AT48" t="str" s="1">
+      <c r="AT48" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU48" t="str">
@@ -9407,24 +9806,30 @@
         <v/>
       </c>
       <c r="AZ48" t="str">
-        <v/>
-      </c>
-      <c r="BA48" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044617</v>
+      </c>
+      <c r="BA48" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB48" t="str">
+        <v/>
+      </c>
+      <c r="BC48" t="str">
         <v>M7</v>
       </c>
-      <c r="BB48" t="str" s="1">
+      <c r="BD48" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC48" t="str">
-        <v/>
-      </c>
-      <c r="BD48" t="str">
-        <v/>
-      </c>
-      <c r="BE48" t="str" s="1">
+      <c r="BE48" t="str">
+        <v/>
+      </c>
+      <c r="BF48" t="str">
+        <v/>
+      </c>
+      <c r="BG48" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF48" t="str">
+      <c r="BH48" t="str">
         <v/>
       </c>
     </row>
@@ -9486,7 +9891,7 @@
       <c r="S49" t="str">
         <v>19</v>
       </c>
-      <c r="T49" t="str" s="1">
+      <c r="T49" t="str">
         <v>12.09</v>
       </c>
       <c r="U49" t="str">
@@ -9495,13 +9900,13 @@
       <c r="V49" t="str">
         <v/>
       </c>
-      <c r="W49" t="str" s="1">
+      <c r="W49" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X49" t="str" s="1">
+      <c r="X49" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y49" t="str" s="1">
+      <c r="Y49" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z49" t="str">
@@ -9516,10 +9921,10 @@
       <c r="AC49" t="str">
         <v/>
       </c>
-      <c r="AD49" t="str" s="1">
+      <c r="AD49" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE49" t="str" s="1">
+      <c r="AE49" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF49" t="str">
@@ -9531,7 +9936,7 @@
       <c r="AH49" t="str">
         <v/>
       </c>
-      <c r="AI49" t="str" s="1">
+      <c r="AI49" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ49" t="str">
@@ -9564,7 +9969,7 @@
       <c r="AS49" t="str">
         <v>是</v>
       </c>
-      <c r="AT49" t="str" s="1">
+      <c r="AT49" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU49" t="str">
@@ -9583,24 +9988,30 @@
         <v/>
       </c>
       <c r="AZ49" t="str">
-        <v/>
-      </c>
-      <c r="BA49" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044624</v>
+      </c>
+      <c r="BA49" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB49" t="str">
+        <v/>
+      </c>
+      <c r="BC49" t="str">
         <v>M7</v>
       </c>
-      <c r="BB49" t="str" s="1">
+      <c r="BD49" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC49" t="str">
-        <v/>
-      </c>
-      <c r="BD49" t="str">
-        <v/>
-      </c>
-      <c r="BE49" t="str" s="1">
+      <c r="BE49" t="str">
+        <v/>
+      </c>
+      <c r="BF49" t="str">
+        <v/>
+      </c>
+      <c r="BG49" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF49" t="str">
+      <c r="BH49" t="str">
         <v/>
       </c>
     </row>
@@ -9662,7 +10073,7 @@
       <c r="S50" t="str">
         <v>19</v>
       </c>
-      <c r="T50" t="str" s="1">
+      <c r="T50" t="str">
         <v>12.09</v>
       </c>
       <c r="U50" t="str">
@@ -9671,13 +10082,13 @@
       <c r="V50" t="str">
         <v/>
       </c>
-      <c r="W50" t="str" s="1">
+      <c r="W50" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X50" t="str" s="1">
+      <c r="X50" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y50" t="str" s="1">
+      <c r="Y50" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z50" t="str">
@@ -9692,10 +10103,10 @@
       <c r="AC50" t="str">
         <v/>
       </c>
-      <c r="AD50" t="str" s="1">
+      <c r="AD50" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE50" t="str" s="1">
+      <c r="AE50" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF50" t="str">
@@ -9707,7 +10118,7 @@
       <c r="AH50" t="str">
         <v/>
       </c>
-      <c r="AI50" t="str" s="1">
+      <c r="AI50" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ50" t="str">
@@ -9740,7 +10151,7 @@
       <c r="AS50" t="str">
         <v>是</v>
       </c>
-      <c r="AT50" t="str" s="1">
+      <c r="AT50" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU50" t="str">
@@ -9759,24 +10170,30 @@
         <v/>
       </c>
       <c r="AZ50" t="str">
-        <v/>
-      </c>
-      <c r="BA50" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044631</v>
+      </c>
+      <c r="BA50" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB50" t="str">
+        <v/>
+      </c>
+      <c r="BC50" t="str">
         <v>M7</v>
       </c>
-      <c r="BB50" t="str" s="1">
+      <c r="BD50" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC50" t="str">
-        <v/>
-      </c>
-      <c r="BD50" t="str">
-        <v/>
-      </c>
-      <c r="BE50" t="str" s="1">
+      <c r="BE50" t="str">
+        <v/>
+      </c>
+      <c r="BF50" t="str">
+        <v/>
+      </c>
+      <c r="BG50" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF50" t="str">
+      <c r="BH50" t="str">
         <v/>
       </c>
     </row>
@@ -9838,7 +10255,7 @@
       <c r="S51" t="str">
         <v>19</v>
       </c>
-      <c r="T51" t="str" s="1">
+      <c r="T51" t="str">
         <v>12.09</v>
       </c>
       <c r="U51" t="str">
@@ -9847,13 +10264,13 @@
       <c r="V51" t="str">
         <v/>
       </c>
-      <c r="W51" t="str" s="1">
+      <c r="W51" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X51" t="str" s="1">
+      <c r="X51" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y51" t="str" s="1">
+      <c r="Y51" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z51" t="str">
@@ -9868,10 +10285,10 @@
       <c r="AC51" t="str">
         <v/>
       </c>
-      <c r="AD51" t="str" s="1">
+      <c r="AD51" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE51" t="str" s="1">
+      <c r="AE51" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF51" t="str">
@@ -9883,7 +10300,7 @@
       <c r="AH51" t="str">
         <v/>
       </c>
-      <c r="AI51" t="str" s="1">
+      <c r="AI51" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ51" t="str">
@@ -9916,7 +10333,7 @@
       <c r="AS51" t="str">
         <v>是</v>
       </c>
-      <c r="AT51" t="str" s="1">
+      <c r="AT51" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU51" t="str">
@@ -9935,24 +10352,30 @@
         <v/>
       </c>
       <c r="AZ51" t="str">
-        <v/>
-      </c>
-      <c r="BA51" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044648</v>
+      </c>
+      <c r="BA51" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB51" t="str">
+        <v/>
+      </c>
+      <c r="BC51" t="str">
         <v>M7</v>
       </c>
-      <c r="BB51" t="str" s="1">
+      <c r="BD51" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC51" t="str">
-        <v/>
-      </c>
-      <c r="BD51" t="str">
-        <v/>
-      </c>
-      <c r="BE51" t="str" s="1">
+      <c r="BE51" t="str">
+        <v/>
+      </c>
+      <c r="BF51" t="str">
+        <v/>
+      </c>
+      <c r="BG51" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF51" t="str">
+      <c r="BH51" t="str">
         <v/>
       </c>
     </row>
@@ -10014,7 +10437,7 @@
       <c r="S52" t="str">
         <v>19</v>
       </c>
-      <c r="T52" t="str" s="1">
+      <c r="T52" t="str">
         <v>12.09</v>
       </c>
       <c r="U52" t="str">
@@ -10023,13 +10446,13 @@
       <c r="V52" t="str">
         <v/>
       </c>
-      <c r="W52" t="str" s="1">
+      <c r="W52" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X52" t="str" s="1">
+      <c r="X52" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y52" t="str" s="1">
+      <c r="Y52" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z52" t="str">
@@ -10044,10 +10467,10 @@
       <c r="AC52" t="str">
         <v/>
       </c>
-      <c r="AD52" t="str" s="1">
+      <c r="AD52" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE52" t="str" s="1">
+      <c r="AE52" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF52" t="str">
@@ -10059,7 +10482,7 @@
       <c r="AH52" t="str">
         <v/>
       </c>
-      <c r="AI52" t="str" s="1">
+      <c r="AI52" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ52" t="str">
@@ -10092,7 +10515,7 @@
       <c r="AS52" t="str">
         <v>是</v>
       </c>
-      <c r="AT52" t="str" s="1">
+      <c r="AT52" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU52" t="str">
@@ -10111,24 +10534,30 @@
         <v/>
       </c>
       <c r="AZ52" t="str">
-        <v/>
-      </c>
-      <c r="BA52" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044655</v>
+      </c>
+      <c r="BA52" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB52" t="str">
+        <v/>
+      </c>
+      <c r="BC52" t="str">
         <v>M7</v>
       </c>
-      <c r="BB52" t="str" s="1">
+      <c r="BD52" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC52" t="str">
-        <v/>
-      </c>
-      <c r="BD52" t="str">
-        <v/>
-      </c>
-      <c r="BE52" t="str" s="1">
+      <c r="BE52" t="str">
+        <v/>
+      </c>
+      <c r="BF52" t="str">
+        <v/>
+      </c>
+      <c r="BG52" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF52" t="str">
+      <c r="BH52" t="str">
         <v/>
       </c>
     </row>
@@ -10190,7 +10619,7 @@
       <c r="S53" t="str">
         <v>19</v>
       </c>
-      <c r="T53" t="str" s="1">
+      <c r="T53" t="str">
         <v>12.09</v>
       </c>
       <c r="U53" t="str">
@@ -10199,13 +10628,13 @@
       <c r="V53" t="str">
         <v/>
       </c>
-      <c r="W53" t="str" s="1">
+      <c r="W53" t="str">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X53" t="str" s="1">
+      <c r="X53" t="str">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y53" t="str" s="1">
+      <c r="Y53" t="str">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z53" t="str">
@@ -10220,10 +10649,10 @@
       <c r="AC53" t="str">
         <v/>
       </c>
-      <c r="AD53" t="str" s="1">
+      <c r="AD53" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE53" t="str" s="1">
+      <c r="AE53" t="str">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF53" t="str">
@@ -10235,7 +10664,7 @@
       <c r="AH53" t="str">
         <v/>
       </c>
-      <c r="AI53" t="str" s="1">
+      <c r="AI53" t="str">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ53" t="str">
@@ -10268,7 +10697,7 @@
       <c r="AS53" t="str">
         <v>是</v>
       </c>
-      <c r="AT53" t="str" s="1">
+      <c r="AT53" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU53" t="str">
@@ -10287,24 +10716,30 @@
         <v/>
       </c>
       <c r="AZ53" t="str">
-        <v/>
-      </c>
-      <c r="BA53" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044662</v>
+      </c>
+      <c r="BA53" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_bantam.pdf</v>
+      </c>
+      <c r="BB53" t="str">
+        <v/>
+      </c>
+      <c r="BC53" t="str">
         <v>M7</v>
       </c>
-      <c r="BB53" t="str" s="1">
+      <c r="BD53" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC53" t="str">
-        <v/>
-      </c>
-      <c r="BD53" t="str">
-        <v/>
-      </c>
-      <c r="BE53" t="str" s="1">
+      <c r="BE53" t="str">
+        <v/>
+      </c>
+      <c r="BF53" t="str">
+        <v/>
+      </c>
+      <c r="BG53" t="str">
         <v>强力泛用</v>
       </c>
-      <c r="BF53" t="str">
+      <c r="BH53" t="str">
         <v/>
       </c>
     </row>
@@ -10375,10 +10810,10 @@
       <c r="V54" t="str">
         <v/>
       </c>
-      <c r="W54" t="str" s="1">
+      <c r="W54" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X54" t="str" s="1">
+      <c r="X54" t="str">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y54" t="str">
@@ -10396,10 +10831,10 @@
       <c r="AC54" t="str">
         <v/>
       </c>
-      <c r="AD54" t="str" s="1">
+      <c r="AD54" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE54" t="str" s="1">
+      <c r="AE54" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF54" t="str">
@@ -10411,7 +10846,7 @@
       <c r="AH54" t="str">
         <v/>
       </c>
-      <c r="AI54" t="str" s="1">
+      <c r="AI54" t="str">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ54" t="str">
@@ -10444,7 +10879,7 @@
       <c r="AS54" t="str">
         <v/>
       </c>
-      <c r="AT54" t="str" s="1">
+      <c r="AT54" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU54" t="str">
@@ -10463,24 +10898,30 @@
         <v/>
       </c>
       <c r="AZ54" t="str">
-        <v/>
-      </c>
-      <c r="BA54" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046000</v>
+      </c>
+      <c r="BA54" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23ANTARES_DC_MD%20_.pdf</v>
+      </c>
+      <c r="BB54" t="str">
+        <v/>
+      </c>
+      <c r="BC54" t="str">
         <v>M7</v>
       </c>
-      <c r="BB54" t="str" s="1">
+      <c r="BD54" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC54" t="str">
-        <v/>
-      </c>
-      <c r="BD54" t="str">
-        <v/>
-      </c>
-      <c r="BE54" t="str" s="1">
+      <c r="BE54" t="str">
+        <v/>
+      </c>
+      <c r="BF54" t="str">
+        <v/>
+      </c>
+      <c r="BG54" t="str">
         <v>重饵 / 巨物</v>
       </c>
-      <c r="BF54" t="str">
+      <c r="BH54" t="str">
         <v/>
       </c>
     </row>
@@ -10551,10 +10992,10 @@
       <c r="V55" t="str">
         <v/>
       </c>
-      <c r="W55" t="str" s="1">
+      <c r="W55" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X55" t="str" s="1">
+      <c r="X55" t="str">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y55" t="str">
@@ -10572,10 +11013,10 @@
       <c r="AC55" t="str">
         <v/>
       </c>
-      <c r="AD55" t="str" s="1">
+      <c r="AD55" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE55" t="str" s="1">
+      <c r="AE55" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF55" t="str">
@@ -10587,7 +11028,7 @@
       <c r="AH55" t="str">
         <v/>
       </c>
-      <c r="AI55" t="str" s="1">
+      <c r="AI55" t="str">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ55" t="str">
@@ -10620,7 +11061,7 @@
       <c r="AS55" t="str">
         <v/>
       </c>
-      <c r="AT55" t="str" s="1">
+      <c r="AT55" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU55" t="str">
@@ -10639,24 +11080,30 @@
         <v/>
       </c>
       <c r="AZ55" t="str">
-        <v/>
-      </c>
-      <c r="BA55" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046017</v>
+      </c>
+      <c r="BA55" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23ANTARES_DC_MD%20_.pdf</v>
+      </c>
+      <c r="BB55" t="str">
+        <v/>
+      </c>
+      <c r="BC55" t="str">
         <v>M7</v>
       </c>
-      <c r="BB55" t="str" s="1">
+      <c r="BD55" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC55" t="str">
-        <v/>
-      </c>
-      <c r="BD55" t="str">
-        <v/>
-      </c>
-      <c r="BE55" t="str" s="1">
+      <c r="BE55" t="str">
+        <v/>
+      </c>
+      <c r="BF55" t="str">
+        <v/>
+      </c>
+      <c r="BG55" t="str">
         <v>重饵 / 巨物</v>
       </c>
-      <c r="BF55" t="str">
+      <c r="BH55" t="str">
         <v/>
       </c>
     </row>
@@ -10727,10 +11174,10 @@
       <c r="V56" t="str">
         <v/>
       </c>
-      <c r="W56" t="str" s="1">
+      <c r="W56" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X56" t="str" s="1">
+      <c r="X56" t="str">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y56" t="str">
@@ -10748,10 +11195,10 @@
       <c r="AC56" t="str">
         <v/>
       </c>
-      <c r="AD56" t="str" s="1">
+      <c r="AD56" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE56" t="str" s="1">
+      <c r="AE56" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF56" t="str">
@@ -10763,7 +11210,7 @@
       <c r="AH56" t="str">
         <v/>
       </c>
-      <c r="AI56" t="str" s="1">
+      <c r="AI56" t="str">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ56" t="str">
@@ -10796,7 +11243,7 @@
       <c r="AS56" t="str">
         <v/>
       </c>
-      <c r="AT56" t="str" s="1">
+      <c r="AT56" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU56" t="str">
@@ -10815,24 +11262,30 @@
         <v/>
       </c>
       <c r="AZ56" t="str">
-        <v/>
-      </c>
-      <c r="BA56" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046024</v>
+      </c>
+      <c r="BA56" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23ANTARES_DC_MD%20_.pdf</v>
+      </c>
+      <c r="BB56" t="str">
+        <v/>
+      </c>
+      <c r="BC56" t="str">
         <v>M7</v>
       </c>
-      <c r="BB56" t="str" s="1">
+      <c r="BD56" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC56" t="str">
-        <v/>
-      </c>
-      <c r="BD56" t="str">
-        <v/>
-      </c>
-      <c r="BE56" t="str" s="1">
+      <c r="BE56" t="str">
+        <v/>
+      </c>
+      <c r="BF56" t="str">
+        <v/>
+      </c>
+      <c r="BG56" t="str">
         <v>重饵 / 巨物</v>
       </c>
-      <c r="BF56" t="str">
+      <c r="BH56" t="str">
         <v/>
       </c>
     </row>
@@ -10903,10 +11356,10 @@
       <c r="V57" t="str">
         <v/>
       </c>
-      <c r="W57" t="str" s="1">
+      <c r="W57" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X57" t="str" s="1">
+      <c r="X57" t="str">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y57" t="str">
@@ -10924,10 +11377,10 @@
       <c r="AC57" t="str">
         <v/>
       </c>
-      <c r="AD57" t="str" s="1">
+      <c r="AD57" t="str">
         <v>Magnesium</v>
       </c>
-      <c r="AE57" t="str" s="1">
+      <c r="AE57" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF57" t="str">
@@ -10939,7 +11392,7 @@
       <c r="AH57" t="str">
         <v/>
       </c>
-      <c r="AI57" t="str" s="1">
+      <c r="AI57" t="str">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ57" t="str">
@@ -10972,7 +11425,7 @@
       <c r="AS57" t="str">
         <v/>
       </c>
-      <c r="AT57" t="str" s="1">
+      <c r="AT57" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU57" t="str">
@@ -10991,24 +11444,30 @@
         <v/>
       </c>
       <c r="AZ57" t="str">
-        <v/>
-      </c>
-      <c r="BA57" t="str" s="1">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046031</v>
+      </c>
+      <c r="BA57" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23ANTARES_DC_MD%20_.pdf</v>
+      </c>
+      <c r="BB57" t="str">
+        <v/>
+      </c>
+      <c r="BC57" t="str">
         <v>M7</v>
       </c>
-      <c r="BB57" t="str" s="1">
+      <c r="BD57" t="str">
         <v>Brass</v>
       </c>
-      <c r="BC57" t="str">
-        <v/>
-      </c>
-      <c r="BD57" t="str">
-        <v/>
-      </c>
-      <c r="BE57" t="str" s="1">
+      <c r="BE57" t="str">
+        <v/>
+      </c>
+      <c r="BF57" t="str">
+        <v/>
+      </c>
+      <c r="BG57" t="str">
         <v>重饵 / 巨物</v>
       </c>
-      <c r="BF57" t="str">
+      <c r="BH57" t="str">
         <v/>
       </c>
     </row>
@@ -11079,10 +11538,10 @@
       <c r="V58" t="str">
         <v/>
       </c>
-      <c r="W58" t="str" s="1">
+      <c r="W58" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X58" t="str" s="1">
+      <c r="X58" t="str">
         <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y58" t="str">
@@ -11094,16 +11553,16 @@
       <c r="AA58" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
       </c>
-      <c r="AB58" t="str" s="1">
+      <c r="AB58" t="str">
         <v>EVA</v>
       </c>
       <c r="AC58" t="str">
         <v/>
       </c>
-      <c r="AD58" t="str" s="1">
+      <c r="AD58" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE58" t="str" s="1">
+      <c r="AE58" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF58" t="str">
@@ -11115,7 +11574,7 @@
       <c r="AH58" t="str">
         <v/>
       </c>
-      <c r="AI58" t="str" s="1">
+      <c r="AI58" t="str">
         <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ58" t="str">
@@ -11127,7 +11586,7 @@
       <c r="AL58" t="str">
         <v/>
       </c>
-      <c r="AM58" t="str" s="1">
+      <c r="AM58" t="str">
         <v>1</v>
       </c>
       <c r="AN58" t="str">
@@ -11148,7 +11607,7 @@
       <c r="AS58" t="str">
         <v/>
       </c>
-      <c r="AT58" t="str" s="1">
+      <c r="AT58" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU58" t="str">
@@ -11166,25 +11625,31 @@
       <c r="AY58" t="str">
         <v/>
       </c>
-      <c r="AZ58" t="str" s="1">
+      <c r="AZ58" t="str">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044969</v>
+      </c>
+      <c r="BA58" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_exsence_dc_2022_v2.pdf</v>
+      </c>
+      <c r="BB58" t="str">
         <v>EVA</v>
       </c>
-      <c r="BA58" t="str" s="1">
+      <c r="BC58" t="str">
         <v>M7</v>
       </c>
-      <c r="BB58" t="str">
-        <v/>
-      </c>
-      <c r="BC58" t="str">
-        <v/>
-      </c>
       <c r="BD58" t="str">
         <v/>
       </c>
-      <c r="BE58" t="str" s="1">
+      <c r="BE58" t="str">
+        <v/>
+      </c>
+      <c r="BF58" t="str">
+        <v/>
+      </c>
+      <c r="BG58" t="str">
         <v>海鲈</v>
       </c>
-      <c r="BF58" t="str">
+      <c r="BH58" t="str">
         <v/>
       </c>
     </row>
@@ -11255,10 +11720,10 @@
       <c r="V59" t="str">
         <v/>
       </c>
-      <c r="W59" t="str" s="1">
+      <c r="W59" t="str">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X59" t="str" s="1">
+      <c r="X59" t="str">
         <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y59" t="str">
@@ -11270,16 +11735,16 @@
       <c r="AA59" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
       </c>
-      <c r="AB59" t="str" s="1">
+      <c r="AB59" t="str">
         <v>EVA</v>
       </c>
       <c r="AC59" t="str">
         <v/>
       </c>
-      <c r="AD59" t="str" s="1">
+      <c r="AD59" t="str">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE59" t="str" s="1">
+      <c r="AE59" t="str">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF59" t="str">
@@ -11291,7 +11756,7 @@
       <c r="AH59" t="str">
         <v/>
       </c>
-      <c r="AI59" t="str" s="1">
+      <c r="AI59" t="str">
         <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ59" t="str">
@@ -11303,7 +11768,7 @@
       <c r="AL59" t="str">
         <v/>
       </c>
-      <c r="AM59" t="str" s="1">
+      <c r="AM59" t="str">
         <v>1</v>
       </c>
       <c r="AN59" t="str">
@@ -11324,7 +11789,7 @@
       <c r="AS59" t="str">
         <v/>
       </c>
-      <c r="AT59" t="str" s="1">
+      <c r="AT59" t="str">
         <v>单摇臂</v>
       </c>
       <c r="AU59" t="str">
@@ -11342,31 +11807,37 @@
       <c r="AY59" t="str">
         <v/>
       </c>
-      <c r="AZ59" t="str" s="1">
+      <c r="AZ59" t="str">
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044976</v>
+      </c>
+      <c r="BA59" t="str">
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_exsence_dc_2022_v2.pdf</v>
+      </c>
+      <c r="BB59" t="str">
         <v>EVA</v>
       </c>
-      <c r="BA59" t="str" s="1">
+      <c r="BC59" t="str">
         <v>M7</v>
       </c>
-      <c r="BB59" t="str">
-        <v/>
-      </c>
-      <c r="BC59" t="str">
-        <v/>
-      </c>
       <c r="BD59" t="str">
         <v/>
       </c>
-      <c r="BE59" t="str" s="1">
+      <c r="BE59" t="str">
+        <v/>
+      </c>
+      <c r="BF59" t="str">
+        <v/>
+      </c>
+      <c r="BG59" t="str">
         <v>海鲈</v>
       </c>
-      <c r="BF59" t="str">
+      <c r="BH59" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BF59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BH59"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -49,12 +49,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF59D"/>
+        <bgColor rgb="FFF59D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,8 +75,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +408,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:T11"/>
   <sheetData>
     <row r="1">
@@ -482,10 +489,10 @@
       <c r="E2" t="str">
         <v/>
       </c>
-      <c r="F2" t="str">
+      <c r="F2" t="str" s="1">
         <v>2024</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="1">
         <v>24 SLX 70</v>
       </c>
       <c r="H2" t="str">
@@ -503,10 +510,10 @@
       <c r="L2" t="str">
         <v>2026-04-15 02:14:15</v>
       </c>
-      <c r="M2" t="str">
+      <c r="M2" t="str" s="1">
         <v>泛用入门</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N2" t="str" s="1">
         <v>MGL III / 紧凑机身 / 入门泛用</v>
       </c>
       <c r="O2" t="str">
@@ -521,10 +528,10 @@
       <c r="R2" t="str">
         <v/>
       </c>
-      <c r="S2" t="str">
+      <c r="S2" t="str" s="1">
         <v>泛用入门水滴轮</v>
       </c>
-      <c r="T2" t="str">
+      <c r="T2" t="str" s="1">
         <v>性价比高 / MGL III / 泛用覆盖</v>
       </c>
     </row>
@@ -544,10 +551,10 @@
       <c r="E3" t="str">
         <v/>
       </c>
-      <c r="F3" t="str">
+      <c r="F3" t="str" s="1">
         <v>2024</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="1">
         <v>24 SLX XT 150</v>
       </c>
       <c r="H3" t="str">
@@ -565,10 +572,10 @@
       <c r="L3" t="str">
         <v>2026-04-15 02:14:15</v>
       </c>
-      <c r="M3" t="str">
+      <c r="M3" t="str" s="1">
         <v>泛用入门</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N3" t="str" s="1">
         <v>HAGANE机身 / SILENTTUNE / 高性价比</v>
       </c>
       <c r="O3" t="str">
@@ -583,10 +590,10 @@
       <c r="R3" t="str">
         <v/>
       </c>
-      <c r="S3" t="str">
+      <c r="S3" t="str" s="1">
         <v>泛用入门水滴轮</v>
       </c>
-      <c r="T3" t="str">
+      <c r="T3" t="str" s="1">
         <v>入门友好 / 更强容线量 / 泛用覆盖</v>
       </c>
     </row>
@@ -603,13 +610,13 @@
       <c r="D4" t="str">
         <v>ALDEBARAN BFS</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" t="str" s="1">
         <v>阿德巴兰 BFS</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F4" t="str" s="1">
         <v>2022</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="1">
         <v>22 Aldebaran BFS</v>
       </c>
       <c r="H4" t="str">
@@ -627,10 +634,10 @@
       <c r="L4" t="str">
         <v>2026-04-15 02:13:31</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4" t="str" s="1">
         <v>极致BFS</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N4" t="str" s="1">
         <v>FTB / 超轻量线杯 / 轻饵特化</v>
       </c>
       <c r="O4" t="str">
@@ -642,13 +649,13 @@
       <c r="Q4" t="str">
         <v>ALDEBARAN BFS搭载了第一次在SHIMANO BFS渔轮上运用的MGLⅢ技术。专门为BFS设计的低惯性线杯将在轻钓组的世界里掀起一场风暴。采用不易炸线的FTB磁刹系统。不在线杯上配置刹车单位配件，使其低惯性化，相比过去刹车单位配件行程拉长，使刹车更易调节。此外，新配置的磁环在最小刹车力时能够吸收磁力的影响，即使抖动抛投假饵弹道也不易上浮，彷如在水面上爬行般达到结构钓点的深处。此外，其重量仅130g，满载了MICROMODULE GEAR和EXCITING DRAG SOUND等先进技术。于是高性价比的ALDEBARAN诞生了。</v>
       </c>
-      <c r="R4" t="str">
+      <c r="R4" t="str" s="1">
         <v>49900JPY</v>
       </c>
-      <c r="S4" t="str">
+      <c r="S4" t="str" s="1">
         <v>BFS轻饵特化旗舰</v>
       </c>
-      <c r="T4" t="str">
+      <c r="T4" t="str" s="1">
         <v>超轻线杯 / FTB / 轻饵上限高</v>
       </c>
     </row>
@@ -665,13 +672,13 @@
       <c r="D5" t="str">
         <v>ALDEBARAN MGL</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" t="str" s="1">
         <v>阿德巴兰 MGL</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F5" t="str" s="1">
         <v>2018</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5" t="str" s="1">
         <v>18 Aldebaran MGL</v>
       </c>
       <c r="H5" t="str">
@@ -689,10 +696,10 @@
       <c r="L5" t="str">
         <v>2026-04-15 02:13:33</v>
       </c>
-      <c r="M5" t="str">
+      <c r="M5" t="str" s="1">
         <v>轻量泛用技巧</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N5" t="str" s="1">
         <v>浅溝轻量线杯 / 轻饵泛用 / 低姿态机身</v>
       </c>
       <c r="O5" t="str">
@@ -704,13 +711,13 @@
       <c r="Q5" t="str">
         <v>轻假饵专用的ALDEBARAN，浅杯化并搭载新设计的MagnumLITE线杯。通过在线杯侧面打孔减轻了惯性及重量，这样减少了需要控制的刹车力。轻量假饵的适应性进一步提升，提升了远投性能。轻量假饵那轻微的重量能够瞬间加速，提升抛投的距离，覆盖至微物钓的领域。</v>
       </c>
-      <c r="R5" t="str">
+      <c r="R5" t="str" s="1">
         <v>49500JPY</v>
       </c>
-      <c r="S5" t="str">
+      <c r="S5" t="str" s="1">
         <v>轻量技巧泛用</v>
       </c>
-      <c r="T5" t="str">
+      <c r="T5" t="str" s="1">
         <v>低姿态轻量 / MGL线杯 / 技巧泛用</v>
       </c>
     </row>
@@ -727,13 +734,13 @@
       <c r="D6" t="str">
         <v>CURADO</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" t="str" s="1">
         <v>库拉多</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F6" t="str" s="1">
         <v>2022</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G6" t="str" s="1">
         <v>22 CURADO 200</v>
       </c>
       <c r="H6" t="str">
@@ -751,10 +758,10 @@
       <c r="L6" t="str">
         <v>2026-04-15 02:14:08</v>
       </c>
-      <c r="M6" t="str">
+      <c r="M6" t="str" s="1">
         <v>重饵泛用</v>
       </c>
-      <c r="N6" t="str">
+      <c r="N6" t="str" s="1">
         <v>MGL III线杯 / MICROMODULE GEAR / SILENTTUNE</v>
       </c>
       <c r="O6" t="str">
@@ -766,13 +773,13 @@
       <c r="Q6" t="str">
         <v>搭载第三代MGL线杯后，CURADO朝着更远的抛投距离前进，加持MICROMODULE GEAR和SILENTTUNE技术后，手感也有所提升，适合大饵的200型也是你攻略巨物的好伙伴。</v>
       </c>
-      <c r="R6" t="str">
+      <c r="R6" t="str" s="1">
         <v>33300JPY</v>
       </c>
-      <c r="S6" t="str">
+      <c r="S6" t="str" s="1">
         <v>重饵泛用</v>
       </c>
-      <c r="T6" t="str">
+      <c r="T6" t="str" s="1">
         <v>200尺寸 / 卷感顺滑 / 重饵覆盖</v>
       </c>
     </row>
@@ -789,13 +796,13 @@
       <c r="D7" t="str">
         <v>CURADO</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" t="str" s="1">
         <v>库拉多</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F7" t="str" s="1">
         <v>2022</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G7" t="str" s="1">
         <v>22 CURADO 300</v>
       </c>
       <c r="H7" t="str">
@@ -813,10 +820,10 @@
       <c r="L7" t="str">
         <v>2026-04-15 02:14:08</v>
       </c>
-      <c r="M7" t="str">
+      <c r="M7" t="str" s="1">
         <v>巨物泛用</v>
       </c>
-      <c r="N7" t="str">
+      <c r="N7" t="str" s="1">
         <v>300尺寸 / 巨物覆盖 / 高端技术下放</v>
       </c>
       <c r="O7" t="str">
@@ -828,13 +835,13 @@
       <c r="Q7" t="str">
         <v>汇聚SHIMANO高端技术的CURADO推出300规格。</v>
       </c>
-      <c r="R7" t="str">
+      <c r="R7" t="str" s="1">
         <v>33300JPY</v>
       </c>
-      <c r="S7" t="str">
+      <c r="S7" t="str" s="1">
         <v>重饵巨物泛用</v>
       </c>
-      <c r="T7" t="str">
+      <c r="T7" t="str" s="1">
         <v>300尺寸 / 巨物覆盖 / 容线量更大</v>
       </c>
     </row>
@@ -854,10 +861,10 @@
       <c r="E8" t="str">
         <v/>
       </c>
-      <c r="F8" t="str">
+      <c r="F8" t="str" s="1">
         <v>2020</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8" t="str" s="1">
         <v>20 Metanium</v>
       </c>
       <c r="H8" t="str">
@@ -875,10 +882,10 @@
       <c r="L8" t="str">
         <v>2026-04-15 02:13:35</v>
       </c>
-      <c r="M8" t="str">
+      <c r="M8" t="str" s="1">
         <v>泛用技巧</v>
       </c>
-      <c r="N8" t="str">
+      <c r="N8" t="str" s="1">
         <v>CORESOLID / MGL III / 轻量泛用</v>
       </c>
       <c r="O8" t="str">
@@ -890,13 +897,13 @@
       <c r="Q8" t="str">
         <v>覆盖范围广泛的技巧款泛用规格，操作性优秀且轻量，采用镁金属一体成型的CORESOLID机身并搭载了第三代MGL线杯。轻快的操作性和坚韧的适应力，经过提升后，都能更技巧地收线打点和操控轻量假饵。另外在保证轻量的同时，采用超高强度黄铜素材的驱动齿轮，让渔轮更耐用。</v>
       </c>
-      <c r="R8" t="str">
+      <c r="R8" t="str" s="1">
         <v>48200JPY</v>
       </c>
-      <c r="S8" t="str">
+      <c r="S8" t="str" s="1">
         <v>轻量泛用旗舰</v>
       </c>
-      <c r="T8" t="str">
+      <c r="T8" t="str" s="1">
         <v>CORESOLID / 轻量机身 / 泛用上限高</v>
       </c>
     </row>
@@ -913,13 +920,13 @@
       <c r="D9" t="str">
         <v>Bantam</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" t="str" s="1">
         <v>班塔姆</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F9" t="str" s="1">
         <v>2022</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G9" t="str" s="1">
         <v>22 Bantam</v>
       </c>
       <c r="H9" t="str">
@@ -937,10 +944,10 @@
       <c r="L9" t="str">
         <v>2026-04-15 02:13:42</v>
       </c>
-      <c r="M9" t="str">
+      <c r="M9" t="str" s="1">
         <v>强力泛用</v>
       </c>
-      <c r="N9" t="str">
+      <c r="N9" t="str" s="1">
         <v>35mm线杯 / CORESOLID / 黄铜齿轮</v>
       </c>
       <c r="O9" t="str">
@@ -952,13 +959,13 @@
       <c r="Q9" t="str">
         <v>开拓了强力泛用轮的新世界的Bantam再次进化。新Bantam搭载了150号尺寸MGLⅢ线杯。抛竿时的轻便和舒适感彷如19 ANTARES。兼具高刚性和紧凑握感的CORE SOLID机身中，蕴藏SHIMANO第一次在水滴轮上运用的INFINITYDRIVE。减少转动阻力使其可以在全力状态下收线。将强力泛用轮带向新台阶的一款渔轮。</v>
       </c>
-      <c r="R9" t="str">
+      <c r="R9" t="str" s="1">
         <v>42600JPY</v>
       </c>
-      <c r="S9" t="str">
+      <c r="S9" t="str" s="1">
         <v>刚性强力泛用</v>
       </c>
-      <c r="T9" t="str">
+      <c r="T9" t="str" s="1">
         <v>高刚性机身 / 黄铜主齿 / 卷感扎实</v>
       </c>
     </row>
@@ -975,13 +982,13 @@
       <c r="D10" t="str">
         <v>ANTARES DC MD</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" t="str" s="1">
         <v>安塔列斯 DC MD</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F10" t="str" s="1">
         <v>2023</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G10" t="str" s="1">
         <v>23 Antares DC MD</v>
       </c>
       <c r="H10" t="str">
@@ -999,10 +1006,10 @@
       <c r="L10" t="str">
         <v>2026-04-15 02:13:04</v>
       </c>
-      <c r="M10" t="str">
+      <c r="M10" t="str" s="1">
         <v>巨物旗舰</v>
       </c>
-      <c r="N10" t="str">
+      <c r="N10" t="str" s="1">
         <v>MGL III / 4x8 DC MD Tune / 巨物强化</v>
       </c>
       <c r="O10" t="str">
@@ -1014,13 +1021,13 @@
       <c r="Q10" t="str">
         <v>SHIMANO FREESTYLE的巅峰，ANTARES DC MD，作为奋斗在世界舞台的旗舰产品，搭载了MGL SPOOL Ⅲ和新4X8DC MD TUNE刹车系统后，进化成了更具战斗力的规格。第三代MGL线杯带来了抛投时更轻量的手感和更优秀的抛投距离，新4X8DC MD TUNE则在刹车介入时有着更好的精度，和以往抛投时相比抛投得更远且更不易发生缠线问题。另外，搭载精密齿轮后也带来了顺滑的转动性能，在驱动齿轮轴增加支撑培林让构造更强大坚固，转动手把时也能有效降低卡顿问题，带来更顺滑的收线手感。流线美丽的机身传达出的跃动感和信赖感，不断积累厚重的历史步伐，带着更高目标并带着钓手向着高处进发，SHIMANO FREESTYLE的顶点。</v>
       </c>
-      <c r="R10" t="str">
+      <c r="R10" t="str" s="1">
         <v>62000JPY</v>
       </c>
-      <c r="S10" t="str">
+      <c r="S10" t="str" s="1">
         <v>巨物远投旗舰</v>
       </c>
-      <c r="T10" t="str">
+      <c r="T10" t="str" s="1">
         <v>4x8 DC MD Tune / 巨物向 / 宽线杯</v>
       </c>
     </row>
@@ -1040,10 +1047,10 @@
       <c r="E11" t="str">
         <v/>
       </c>
-      <c r="F11" t="str">
+      <c r="F11" t="str" s="1">
         <v>2022</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G11" t="str" s="1">
         <v>22 Exsence DC</v>
       </c>
       <c r="H11" t="str">
@@ -1061,10 +1068,10 @@
       <c r="L11" t="str">
         <v>2026-04-15 02:13:02</v>
       </c>
-      <c r="M11" t="str">
+      <c r="M11" t="str" s="1">
         <v>海鲈远投特化</v>
       </c>
-      <c r="N11" t="str">
+      <c r="N11" t="str" s="1">
         <v>4x8 DC Exsence Tune / 海鲈远投 / PE 线路亚</v>
       </c>
       <c r="O11" t="str">
@@ -1076,13 +1083,13 @@
       <c r="Q11" t="str">
         <v>技术进化而重生的NEW 4x8 DC EXSENCE TUNE，实现了SHIMANO至今未有的精密刹车力。MGL SPOOLⅢ，SILENTUNE，S3D线杯效果相辅相成，使得抛投距离大幅进化。特别是解决了使用PE线时的缠线问题，瞬间的刹车控制能力大幅减少了切线的可能性。另外增加了最大卸力和收线量，使其泛用性更强。具备可以和海水鱼对抗潜力的两轴轮诞生。</v>
       </c>
-      <c r="R11" t="str">
+      <c r="R11" t="str" s="1">
         <v>83400JPY</v>
       </c>
-      <c r="S11" t="str">
+      <c r="S11" t="str" s="1">
         <v>海鲈DC远投特化</v>
       </c>
-      <c r="T11" t="str">
+      <c r="T11" t="str" s="1">
         <v>海鲈PE适配 / DC调校 / 远投性能</v>
       </c>
     </row>
@@ -1094,7 +1101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:BH59"/>
   <sheetData>
     <row r="1">
@@ -1346,13 +1353,13 @@
       <c r="V2" t="str">
         <v/>
       </c>
-      <c r="W2" t="str">
+      <c r="W2" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X2" t="str">
         <v/>
       </c>
-      <c r="Y2" t="str">
+      <c r="Y2" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z2" t="str">
@@ -1382,7 +1389,7 @@
       <c r="AH2" t="str">
         <v/>
       </c>
-      <c r="AI2" t="str">
+      <c r="AI2" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ2" t="str">
@@ -1415,7 +1422,7 @@
       <c r="AS2" t="str">
         <v/>
       </c>
-      <c r="AT2" t="str">
+      <c r="AT2" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU2" t="str">
@@ -1442,7 +1449,7 @@
       <c r="BB2" t="str">
         <v/>
       </c>
-      <c r="BC2" t="str">
+      <c r="BC2" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD2" t="str">
@@ -1454,7 +1461,7 @@
       <c r="BF2" t="str">
         <v/>
       </c>
-      <c r="BG2" t="str">
+      <c r="BG2" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH2" t="str">
@@ -1528,13 +1535,13 @@
       <c r="V3" t="str">
         <v/>
       </c>
-      <c r="W3" t="str">
+      <c r="W3" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X3" t="str">
         <v/>
       </c>
-      <c r="Y3" t="str">
+      <c r="Y3" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z3" t="str">
@@ -1564,7 +1571,7 @@
       <c r="AH3" t="str">
         <v/>
       </c>
-      <c r="AI3" t="str">
+      <c r="AI3" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ3" t="str">
@@ -1597,7 +1604,7 @@
       <c r="AS3" t="str">
         <v/>
       </c>
-      <c r="AT3" t="str">
+      <c r="AT3" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU3" t="str">
@@ -1624,7 +1631,7 @@
       <c r="BB3" t="str">
         <v/>
       </c>
-      <c r="BC3" t="str">
+      <c r="BC3" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD3" t="str">
@@ -1636,7 +1643,7 @@
       <c r="BF3" t="str">
         <v/>
       </c>
-      <c r="BG3" t="str">
+      <c r="BG3" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH3" t="str">
@@ -1710,13 +1717,13 @@
       <c r="V4" t="str">
         <v/>
       </c>
-      <c r="W4" t="str">
+      <c r="W4" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X4" t="str">
         <v/>
       </c>
-      <c r="Y4" t="str">
+      <c r="Y4" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z4" t="str">
@@ -1746,7 +1753,7 @@
       <c r="AH4" t="str">
         <v/>
       </c>
-      <c r="AI4" t="str">
+      <c r="AI4" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ4" t="str">
@@ -1779,7 +1786,7 @@
       <c r="AS4" t="str">
         <v/>
       </c>
-      <c r="AT4" t="str">
+      <c r="AT4" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU4" t="str">
@@ -1806,7 +1813,7 @@
       <c r="BB4" t="str">
         <v/>
       </c>
-      <c r="BC4" t="str">
+      <c r="BC4" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD4" t="str">
@@ -1818,7 +1825,7 @@
       <c r="BF4" t="str">
         <v/>
       </c>
-      <c r="BG4" t="str">
+      <c r="BG4" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH4" t="str">
@@ -1892,13 +1899,13 @@
       <c r="V5" t="str">
         <v/>
       </c>
-      <c r="W5" t="str">
+      <c r="W5" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X5" t="str">
         <v/>
       </c>
-      <c r="Y5" t="str">
+      <c r="Y5" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z5" t="str">
@@ -1928,7 +1935,7 @@
       <c r="AH5" t="str">
         <v/>
       </c>
-      <c r="AI5" t="str">
+      <c r="AI5" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ5" t="str">
@@ -1961,7 +1968,7 @@
       <c r="AS5" t="str">
         <v/>
       </c>
-      <c r="AT5" t="str">
+      <c r="AT5" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU5" t="str">
@@ -1988,7 +1995,7 @@
       <c r="BB5" t="str">
         <v/>
       </c>
-      <c r="BC5" t="str">
+      <c r="BC5" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD5" t="str">
@@ -2000,7 +2007,7 @@
       <c r="BF5" t="str">
         <v/>
       </c>
-      <c r="BG5" t="str">
+      <c r="BG5" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH5" t="str">
@@ -2074,13 +2081,13 @@
       <c r="V6" t="str">
         <v/>
       </c>
-      <c r="W6" t="str">
+      <c r="W6" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X6" t="str">
         <v/>
       </c>
-      <c r="Y6" t="str">
+      <c r="Y6" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z6" t="str">
@@ -2110,7 +2117,7 @@
       <c r="AH6" t="str">
         <v/>
       </c>
-      <c r="AI6" t="str">
+      <c r="AI6" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ6" t="str">
@@ -2143,7 +2150,7 @@
       <c r="AS6" t="str">
         <v/>
       </c>
-      <c r="AT6" t="str">
+      <c r="AT6" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU6" t="str">
@@ -2170,7 +2177,7 @@
       <c r="BB6" t="str">
         <v/>
       </c>
-      <c r="BC6" t="str">
+      <c r="BC6" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD6" t="str">
@@ -2182,7 +2189,7 @@
       <c r="BF6" t="str">
         <v/>
       </c>
-      <c r="BG6" t="str">
+      <c r="BG6" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH6" t="str">
@@ -2256,13 +2263,13 @@
       <c r="V7" t="str">
         <v/>
       </c>
-      <c r="W7" t="str">
+      <c r="W7" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X7" t="str">
         <v/>
       </c>
-      <c r="Y7" t="str">
+      <c r="Y7" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z7" t="str">
@@ -2292,7 +2299,7 @@
       <c r="AH7" t="str">
         <v/>
       </c>
-      <c r="AI7" t="str">
+      <c r="AI7" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ7" t="str">
@@ -2325,7 +2332,7 @@
       <c r="AS7" t="str">
         <v/>
       </c>
-      <c r="AT7" t="str">
+      <c r="AT7" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU7" t="str">
@@ -2352,7 +2359,7 @@
       <c r="BB7" t="str">
         <v/>
       </c>
-      <c r="BC7" t="str">
+      <c r="BC7" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD7" t="str">
@@ -2364,7 +2371,7 @@
       <c r="BF7" t="str">
         <v/>
       </c>
-      <c r="BG7" t="str">
+      <c r="BG7" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH7" t="str">
@@ -2438,13 +2445,13 @@
       <c r="V8" t="str">
         <v/>
       </c>
-      <c r="W8" t="str">
+      <c r="W8" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X8" t="str">
         <v/>
       </c>
-      <c r="Y8" t="str">
+      <c r="Y8" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z8" t="str">
@@ -2474,7 +2481,7 @@
       <c r="AH8" t="str">
         <v/>
       </c>
-      <c r="AI8" t="str">
+      <c r="AI8" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ8" t="str">
@@ -2507,7 +2514,7 @@
       <c r="AS8" t="str">
         <v/>
       </c>
-      <c r="AT8" t="str">
+      <c r="AT8" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU8" t="str">
@@ -2534,7 +2541,7 @@
       <c r="BB8" t="str">
         <v/>
       </c>
-      <c r="BC8" t="str">
+      <c r="BC8" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD8" t="str">
@@ -2546,7 +2553,7 @@
       <c r="BF8" t="str">
         <v/>
       </c>
-      <c r="BG8" t="str">
+      <c r="BG8" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH8" t="str">
@@ -2620,13 +2627,13 @@
       <c r="V9" t="str">
         <v/>
       </c>
-      <c r="W9" t="str">
+      <c r="W9" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X9" t="str">
         <v/>
       </c>
-      <c r="Y9" t="str">
+      <c r="Y9" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z9" t="str">
@@ -2656,7 +2663,7 @@
       <c r="AH9" t="str">
         <v/>
       </c>
-      <c r="AI9" t="str">
+      <c r="AI9" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ9" t="str">
@@ -2689,7 +2696,7 @@
       <c r="AS9" t="str">
         <v/>
       </c>
-      <c r="AT9" t="str">
+      <c r="AT9" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU9" t="str">
@@ -2716,7 +2723,7 @@
       <c r="BB9" t="str">
         <v/>
       </c>
-      <c r="BC9" t="str">
+      <c r="BC9" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD9" t="str">
@@ -2728,7 +2735,7 @@
       <c r="BF9" t="str">
         <v/>
       </c>
-      <c r="BG9" t="str">
+      <c r="BG9" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH9" t="str">
@@ -2802,13 +2809,13 @@
       <c r="V10" t="str">
         <v/>
       </c>
-      <c r="W10" t="str">
+      <c r="W10" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X10" t="str">
         <v/>
       </c>
-      <c r="Y10" t="str">
+      <c r="Y10" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z10" t="str">
@@ -2838,7 +2845,7 @@
       <c r="AH10" t="str">
         <v/>
       </c>
-      <c r="AI10" t="str">
+      <c r="AI10" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ10" t="str">
@@ -2871,7 +2878,7 @@
       <c r="AS10" t="str">
         <v/>
       </c>
-      <c r="AT10" t="str">
+      <c r="AT10" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU10" t="str">
@@ -2898,7 +2905,7 @@
       <c r="BB10" t="str">
         <v/>
       </c>
-      <c r="BC10" t="str">
+      <c r="BC10" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD10" t="str">
@@ -2910,7 +2917,7 @@
       <c r="BF10" t="str">
         <v/>
       </c>
-      <c r="BG10" t="str">
+      <c r="BG10" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH10" t="str">
@@ -2984,13 +2991,13 @@
       <c r="V11" t="str">
         <v/>
       </c>
-      <c r="W11" t="str">
+      <c r="W11" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X11" t="str">
         <v/>
       </c>
-      <c r="Y11" t="str">
+      <c r="Y11" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z11" t="str">
@@ -3020,7 +3027,7 @@
       <c r="AH11" t="str">
         <v/>
       </c>
-      <c r="AI11" t="str">
+      <c r="AI11" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ11" t="str">
@@ -3053,7 +3060,7 @@
       <c r="AS11" t="str">
         <v/>
       </c>
-      <c r="AT11" t="str">
+      <c r="AT11" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU11" t="str">
@@ -3080,7 +3087,7 @@
       <c r="BB11" t="str">
         <v/>
       </c>
-      <c r="BC11" t="str">
+      <c r="BC11" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD11" t="str">
@@ -3092,7 +3099,7 @@
       <c r="BF11" t="str">
         <v/>
       </c>
-      <c r="BG11" t="str">
+      <c r="BG11" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH11" t="str">
@@ -3166,13 +3173,13 @@
       <c r="V12" t="str">
         <v/>
       </c>
-      <c r="W12" t="str">
+      <c r="W12" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X12" t="str">
         <v/>
       </c>
-      <c r="Y12" t="str">
+      <c r="Y12" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z12" t="str">
@@ -3202,7 +3209,7 @@
       <c r="AH12" t="str">
         <v/>
       </c>
-      <c r="AI12" t="str">
+      <c r="AI12" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ12" t="str">
@@ -3235,7 +3242,7 @@
       <c r="AS12" t="str">
         <v/>
       </c>
-      <c r="AT12" t="str">
+      <c r="AT12" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU12" t="str">
@@ -3262,7 +3269,7 @@
       <c r="BB12" t="str">
         <v/>
       </c>
-      <c r="BC12" t="str">
+      <c r="BC12" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD12" t="str">
@@ -3274,7 +3281,7 @@
       <c r="BF12" t="str">
         <v/>
       </c>
-      <c r="BG12" t="str">
+      <c r="BG12" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH12" t="str">
@@ -3348,13 +3355,13 @@
       <c r="V13" t="str">
         <v/>
       </c>
-      <c r="W13" t="str">
+      <c r="W13" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X13" t="str">
         <v/>
       </c>
-      <c r="Y13" t="str">
+      <c r="Y13" t="str" s="1">
         <v>24 SLX Custom Handle Knob / Handle Knob Bearing upgrade</v>
       </c>
       <c r="Z13" t="str">
@@ -3384,7 +3391,7 @@
       <c r="AH13" t="str">
         <v/>
       </c>
-      <c r="AI13" t="str">
+      <c r="AI13" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ13" t="str">
@@ -3417,7 +3424,7 @@
       <c r="AS13" t="str">
         <v/>
       </c>
-      <c r="AT13" t="str">
+      <c r="AT13" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU13" t="str">
@@ -3444,7 +3451,7 @@
       <c r="BB13" t="str">
         <v/>
       </c>
-      <c r="BC13" t="str">
+      <c r="BC13" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD13" t="str">
@@ -3456,7 +3463,7 @@
       <c r="BF13" t="str">
         <v/>
       </c>
-      <c r="BG13" t="str">
+      <c r="BG13" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="BH13" t="str">
@@ -3521,22 +3528,22 @@
       <c r="S14" t="str">
         <v>19</v>
       </c>
-      <c r="T14" t="str">
+      <c r="T14" t="str" s="1">
         <v>6.7</v>
       </c>
       <c r="U14" t="str">
         <v/>
       </c>
-      <c r="V14" t="str">
+      <c r="V14" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W14" t="str">
+      <c r="W14" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X14" t="str">
+      <c r="X14" t="str" s="1">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y14" t="str">
+      <c r="Y14" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z14" t="str">
@@ -3545,16 +3552,16 @@
       <c r="AA14" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB14" t="str">
+      <c r="AB14" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC14" t="str">
+      <c r="AC14" t="str" s="1">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD14" t="str">
+      <c r="AD14" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE14" t="str">
+      <c r="AE14" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF14" t="str">
@@ -3566,7 +3573,7 @@
       <c r="AH14" t="str">
         <v/>
       </c>
-      <c r="AI14" t="str">
+      <c r="AI14" t="str" s="1">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ14" t="str">
@@ -3578,7 +3585,7 @@
       <c r="AL14" t="str">
         <v/>
       </c>
-      <c r="AM14" t="str">
+      <c r="AM14" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN14" t="str">
@@ -3599,7 +3606,7 @@
       <c r="AS14" t="str">
         <v/>
       </c>
-      <c r="AT14" t="str">
+      <c r="AT14" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU14" t="str">
@@ -3626,7 +3633,7 @@
       <c r="BB14" t="str">
         <v/>
       </c>
-      <c r="BC14" t="str">
+      <c r="BC14" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD14" t="str">
@@ -3638,7 +3645,7 @@
       <c r="BF14" t="str">
         <v/>
       </c>
-      <c r="BG14" t="str">
+      <c r="BG14" t="str" s="1">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
       <c r="BH14" t="str">
@@ -3703,22 +3710,22 @@
       <c r="S15" t="str">
         <v>19</v>
       </c>
-      <c r="T15" t="str">
+      <c r="T15" t="str" s="1">
         <v>6.7</v>
       </c>
       <c r="U15" t="str">
         <v/>
       </c>
-      <c r="V15" t="str">
+      <c r="V15" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W15" t="str">
+      <c r="W15" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X15" t="str">
+      <c r="X15" t="str" s="1">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y15" t="str">
+      <c r="Y15" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z15" t="str">
@@ -3727,16 +3734,16 @@
       <c r="AA15" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB15" t="str">
+      <c r="AB15" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC15" t="str">
+      <c r="AC15" t="str" s="1">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD15" t="str">
+      <c r="AD15" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE15" t="str">
+      <c r="AE15" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF15" t="str">
@@ -3748,7 +3755,7 @@
       <c r="AH15" t="str">
         <v/>
       </c>
-      <c r="AI15" t="str">
+      <c r="AI15" t="str" s="1">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ15" t="str">
@@ -3760,7 +3767,7 @@
       <c r="AL15" t="str">
         <v/>
       </c>
-      <c r="AM15" t="str">
+      <c r="AM15" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN15" t="str">
@@ -3781,7 +3788,7 @@
       <c r="AS15" t="str">
         <v/>
       </c>
-      <c r="AT15" t="str">
+      <c r="AT15" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU15" t="str">
@@ -3808,7 +3815,7 @@
       <c r="BB15" t="str">
         <v/>
       </c>
-      <c r="BC15" t="str">
+      <c r="BC15" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD15" t="str">
@@ -3820,7 +3827,7 @@
       <c r="BF15" t="str">
         <v/>
       </c>
-      <c r="BG15" t="str">
+      <c r="BG15" t="str" s="1">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
       <c r="BH15" t="str">
@@ -3885,22 +3892,22 @@
       <c r="S16" t="str">
         <v>19</v>
       </c>
-      <c r="T16" t="str">
+      <c r="T16" t="str" s="1">
         <v>6.7</v>
       </c>
       <c r="U16" t="str">
         <v/>
       </c>
-      <c r="V16" t="str">
+      <c r="V16" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W16" t="str">
+      <c r="W16" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X16" t="str">
+      <c r="X16" t="str" s="1">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y16" t="str">
+      <c r="Y16" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z16" t="str">
@@ -3909,16 +3916,16 @@
       <c r="AA16" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB16" t="str">
+      <c r="AB16" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC16" t="str">
+      <c r="AC16" t="str" s="1">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD16" t="str">
+      <c r="AD16" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE16" t="str">
+      <c r="AE16" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF16" t="str">
@@ -3930,7 +3937,7 @@
       <c r="AH16" t="str">
         <v/>
       </c>
-      <c r="AI16" t="str">
+      <c r="AI16" t="str" s="1">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ16" t="str">
@@ -3942,7 +3949,7 @@
       <c r="AL16" t="str">
         <v/>
       </c>
-      <c r="AM16" t="str">
+      <c r="AM16" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN16" t="str">
@@ -3963,7 +3970,7 @@
       <c r="AS16" t="str">
         <v/>
       </c>
-      <c r="AT16" t="str">
+      <c r="AT16" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU16" t="str">
@@ -3990,7 +3997,7 @@
       <c r="BB16" t="str">
         <v/>
       </c>
-      <c r="BC16" t="str">
+      <c r="BC16" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD16" t="str">
@@ -4002,7 +4009,7 @@
       <c r="BF16" t="str">
         <v/>
       </c>
-      <c r="BG16" t="str">
+      <c r="BG16" t="str" s="1">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
       <c r="BH16" t="str">
@@ -4067,22 +4074,22 @@
       <c r="S17" t="str">
         <v>19</v>
       </c>
-      <c r="T17" t="str">
+      <c r="T17" t="str" s="1">
         <v>6.7</v>
       </c>
       <c r="U17" t="str">
         <v/>
       </c>
-      <c r="V17" t="str">
+      <c r="V17" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W17" t="str">
+      <c r="W17" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X17" t="str">
+      <c r="X17" t="str" s="1">
         <v>Genuine Spool 22 ALDEBARAN BFS / Avail Microcast Spool 22ALD22R</v>
       </c>
-      <c r="Y17" t="str">
+      <c r="Y17" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z17" t="str">
@@ -4091,16 +4098,16 @@
       <c r="AA17" t="str">
         <v>氟碳lb 6-45, 8-45</v>
       </c>
-      <c r="AB17" t="str">
+      <c r="AB17" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC17" t="str">
+      <c r="AC17" t="str" s="1">
         <v>HKC-23VAN / 轻量握丸规格</v>
       </c>
-      <c r="AD17" t="str">
+      <c r="AD17" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE17" t="str">
+      <c r="AE17" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF17" t="str">
@@ -4112,7 +4119,7 @@
       <c r="AH17" t="str">
         <v/>
       </c>
-      <c r="AI17" t="str">
+      <c r="AI17" t="str" s="1">
         <v>溪流 / 轻盐近岸</v>
       </c>
       <c r="AJ17" t="str">
@@ -4124,7 +4131,7 @@
       <c r="AL17" t="str">
         <v/>
       </c>
-      <c r="AM17" t="str">
+      <c r="AM17" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN17" t="str">
@@ -4145,7 +4152,7 @@
       <c r="AS17" t="str">
         <v/>
       </c>
-      <c r="AT17" t="str">
+      <c r="AT17" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU17" t="str">
@@ -4172,7 +4179,7 @@
       <c r="BB17" t="str">
         <v/>
       </c>
-      <c r="BC17" t="str">
+      <c r="BC17" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD17" t="str">
@@ -4184,7 +4191,7 @@
       <c r="BF17" t="str">
         <v/>
       </c>
-      <c r="BG17" t="str">
+      <c r="BG17" t="str" s="1">
         <v>BFS / 溪流 / 轻盐</v>
       </c>
       <c r="BH17" t="str">
@@ -4249,22 +4256,22 @@
       <c r="S18" t="str">
         <v>22</v>
       </c>
-      <c r="T18" t="str">
+      <c r="T18" t="str" s="1">
         <v>10.5</v>
       </c>
       <c r="U18" t="str">
         <v/>
       </c>
-      <c r="V18" t="str">
+      <c r="V18" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W18" t="str">
+      <c r="W18" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X18" t="str">
+      <c r="X18" t="str" s="1">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y18" t="str">
+      <c r="Y18" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z18" t="str">
@@ -4273,16 +4280,16 @@
       <c r="AA18" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB18" t="str">
+      <c r="AB18" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC18" t="str">
+      <c r="AC18" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD18" t="str">
+      <c r="AD18" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE18" t="str">
+      <c r="AE18" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF18" t="str">
@@ -4294,7 +4301,7 @@
       <c r="AH18" t="str">
         <v/>
       </c>
-      <c r="AI18" t="str">
+      <c r="AI18" t="str" s="1">
         <v>淡水技巧</v>
       </c>
       <c r="AJ18" t="str">
@@ -4327,7 +4334,7 @@
       <c r="AS18" t="str">
         <v/>
       </c>
-      <c r="AT18" t="str">
+      <c r="AT18" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU18" t="str">
@@ -4354,7 +4361,7 @@
       <c r="BB18" t="str">
         <v/>
       </c>
-      <c r="BC18" t="str">
+      <c r="BC18" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD18" t="str">
@@ -4366,7 +4373,7 @@
       <c r="BF18" t="str">
         <v/>
       </c>
-      <c r="BG18" t="str">
+      <c r="BG18" t="str" s="1">
         <v>轻量泛用 / 技巧</v>
       </c>
       <c r="BH18" t="str">
@@ -4431,22 +4438,22 @@
       <c r="S19" t="str">
         <v>22</v>
       </c>
-      <c r="T19" t="str">
+      <c r="T19" t="str" s="1">
         <v>10.5</v>
       </c>
       <c r="U19" t="str">
         <v/>
       </c>
-      <c r="V19" t="str">
+      <c r="V19" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W19" t="str">
+      <c r="W19" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X19" t="str">
+      <c r="X19" t="str" s="1">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y19" t="str">
+      <c r="Y19" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z19" t="str">
@@ -4455,16 +4462,16 @@
       <c r="AA19" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB19" t="str">
+      <c r="AB19" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC19" t="str">
+      <c r="AC19" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD19" t="str">
+      <c r="AD19" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE19" t="str">
+      <c r="AE19" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF19" t="str">
@@ -4476,7 +4483,7 @@
       <c r="AH19" t="str">
         <v/>
       </c>
-      <c r="AI19" t="str">
+      <c r="AI19" t="str" s="1">
         <v>淡水技巧</v>
       </c>
       <c r="AJ19" t="str">
@@ -4509,7 +4516,7 @@
       <c r="AS19" t="str">
         <v/>
       </c>
-      <c r="AT19" t="str">
+      <c r="AT19" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU19" t="str">
@@ -4536,7 +4543,7 @@
       <c r="BB19" t="str">
         <v/>
       </c>
-      <c r="BC19" t="str">
+      <c r="BC19" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD19" t="str">
@@ -4548,7 +4555,7 @@
       <c r="BF19" t="str">
         <v/>
       </c>
-      <c r="BG19" t="str">
+      <c r="BG19" t="str" s="1">
         <v>轻量泛用 / 技巧</v>
       </c>
       <c r="BH19" t="str">
@@ -4613,22 +4620,22 @@
       <c r="S20" t="str">
         <v>22</v>
       </c>
-      <c r="T20" t="str">
+      <c r="T20" t="str" s="1">
         <v>10.5</v>
       </c>
       <c r="U20" t="str">
         <v/>
       </c>
-      <c r="V20" t="str">
+      <c r="V20" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W20" t="str">
+      <c r="W20" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X20" t="str">
+      <c r="X20" t="str" s="1">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y20" t="str">
+      <c r="Y20" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z20" t="str">
@@ -4637,16 +4644,16 @@
       <c r="AA20" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB20" t="str">
+      <c r="AB20" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC20" t="str">
+      <c r="AC20" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD20" t="str">
+      <c r="AD20" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE20" t="str">
+      <c r="AE20" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF20" t="str">
@@ -4658,7 +4665,7 @@
       <c r="AH20" t="str">
         <v/>
       </c>
-      <c r="AI20" t="str">
+      <c r="AI20" t="str" s="1">
         <v>淡水技巧</v>
       </c>
       <c r="AJ20" t="str">
@@ -4691,7 +4698,7 @@
       <c r="AS20" t="str">
         <v/>
       </c>
-      <c r="AT20" t="str">
+      <c r="AT20" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU20" t="str">
@@ -4718,7 +4725,7 @@
       <c r="BB20" t="str">
         <v/>
       </c>
-      <c r="BC20" t="str">
+      <c r="BC20" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD20" t="str">
@@ -4730,7 +4737,7 @@
       <c r="BF20" t="str">
         <v/>
       </c>
-      <c r="BG20" t="str">
+      <c r="BG20" t="str" s="1">
         <v>轻量泛用 / 技巧</v>
       </c>
       <c r="BH20" t="str">
@@ -4795,22 +4802,22 @@
       <c r="S21" t="str">
         <v>22</v>
       </c>
-      <c r="T21" t="str">
+      <c r="T21" t="str" s="1">
         <v>10.5</v>
       </c>
       <c r="U21" t="str">
         <v/>
       </c>
-      <c r="V21" t="str">
+      <c r="V21" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="W21" t="str">
+      <c r="W21" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X21" t="str">
+      <c r="X21" t="str" s="1">
         <v>Genuine Spool 18 ALDEBARAN MGL</v>
       </c>
-      <c r="Y21" t="str">
+      <c r="Y21" t="str" s="1">
         <v>Handle Knob Cap Set S size / Custom Handle Knob</v>
       </c>
       <c r="Z21" t="str">
@@ -4819,16 +4826,16 @@
       <c r="AA21" t="str">
         <v>尼龙lb 8-100, 10-90, 12-65</v>
       </c>
-      <c r="AB21" t="str">
+      <c r="AB21" t="str" s="1">
         <v>lightweight slim knob</v>
       </c>
-      <c r="AC21" t="str">
+      <c r="AC21" t="str" s="1">
         <v>S size / lightweight slim knob</v>
       </c>
-      <c r="AD21" t="str">
+      <c r="AD21" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE21" t="str">
+      <c r="AE21" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF21" t="str">
@@ -4840,7 +4847,7 @@
       <c r="AH21" t="str">
         <v/>
       </c>
-      <c r="AI21" t="str">
+      <c r="AI21" t="str" s="1">
         <v>淡水技巧</v>
       </c>
       <c r="AJ21" t="str">
@@ -4873,7 +4880,7 @@
       <c r="AS21" t="str">
         <v/>
       </c>
-      <c r="AT21" t="str">
+      <c r="AT21" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU21" t="str">
@@ -4900,7 +4907,7 @@
       <c r="BB21" t="str">
         <v/>
       </c>
-      <c r="BC21" t="str">
+      <c r="BC21" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD21" t="str">
@@ -4912,7 +4919,7 @@
       <c r="BF21" t="str">
         <v/>
       </c>
-      <c r="BG21" t="str">
+      <c r="BG21" t="str" s="1">
         <v>轻量泛用 / 技巧</v>
       </c>
       <c r="BH21" t="str">
@@ -4986,13 +4993,13 @@
       <c r="V22" t="str">
         <v/>
       </c>
-      <c r="W22" t="str">
+      <c r="W22" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X22" t="str">
-        <v/>
-      </c>
-      <c r="Y22" t="str">
+      <c r="X22" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y22" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z22" t="str">
@@ -5001,16 +5008,16 @@
       <c r="AA22" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB22" t="str">
+      <c r="AB22" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC22" t="str">
         <v/>
       </c>
-      <c r="AD22" t="str">
+      <c r="AD22" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE22" t="str">
+      <c r="AE22" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF22" t="str">
@@ -5022,7 +5029,7 @@
       <c r="AH22" t="str">
         <v/>
       </c>
-      <c r="AI22" t="str">
+      <c r="AI22" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ22" t="str">
@@ -5055,7 +5062,7 @@
       <c r="AS22" t="str">
         <v/>
       </c>
-      <c r="AT22" t="str">
+      <c r="AT22" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU22" t="str">
@@ -5082,10 +5089,10 @@
       <c r="BB22" t="str">
         <v/>
       </c>
-      <c r="BC22" t="str">
+      <c r="BC22" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD22" t="str">
+      <c r="BD22" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE22" t="str">
@@ -5094,7 +5101,7 @@
       <c r="BF22" t="str">
         <v/>
       </c>
-      <c r="BG22" t="str">
+      <c r="BG22" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH22" t="str">
@@ -5168,13 +5175,13 @@
       <c r="V23" t="str">
         <v/>
       </c>
-      <c r="W23" t="str">
+      <c r="W23" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
-      <c r="Y23" t="str">
+      <c r="X23" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y23" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z23" t="str">
@@ -5183,16 +5190,16 @@
       <c r="AA23" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB23" t="str">
+      <c r="AB23" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC23" t="str">
         <v/>
       </c>
-      <c r="AD23" t="str">
+      <c r="AD23" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE23" t="str">
+      <c r="AE23" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF23" t="str">
@@ -5204,7 +5211,7 @@
       <c r="AH23" t="str">
         <v/>
       </c>
-      <c r="AI23" t="str">
+      <c r="AI23" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ23" t="str">
@@ -5237,7 +5244,7 @@
       <c r="AS23" t="str">
         <v/>
       </c>
-      <c r="AT23" t="str">
+      <c r="AT23" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU23" t="str">
@@ -5264,10 +5271,10 @@
       <c r="BB23" t="str">
         <v/>
       </c>
-      <c r="BC23" t="str">
+      <c r="BC23" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD23" t="str">
+      <c r="BD23" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE23" t="str">
@@ -5276,7 +5283,7 @@
       <c r="BF23" t="str">
         <v/>
       </c>
-      <c r="BG23" t="str">
+      <c r="BG23" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH23" t="str">
@@ -5350,13 +5357,13 @@
       <c r="V24" t="str">
         <v/>
       </c>
-      <c r="W24" t="str">
+      <c r="W24" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
+      <c r="X24" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y24" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z24" t="str">
@@ -5365,16 +5372,16 @@
       <c r="AA24" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB24" t="str">
+      <c r="AB24" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC24" t="str">
         <v/>
       </c>
-      <c r="AD24" t="str">
+      <c r="AD24" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE24" t="str">
+      <c r="AE24" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF24" t="str">
@@ -5386,7 +5393,7 @@
       <c r="AH24" t="str">
         <v/>
       </c>
-      <c r="AI24" t="str">
+      <c r="AI24" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ24" t="str">
@@ -5419,7 +5426,7 @@
       <c r="AS24" t="str">
         <v/>
       </c>
-      <c r="AT24" t="str">
+      <c r="AT24" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU24" t="str">
@@ -5446,10 +5453,10 @@
       <c r="BB24" t="str">
         <v/>
       </c>
-      <c r="BC24" t="str">
+      <c r="BC24" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD24" t="str">
+      <c r="BD24" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE24" t="str">
@@ -5458,7 +5465,7 @@
       <c r="BF24" t="str">
         <v/>
       </c>
-      <c r="BG24" t="str">
+      <c r="BG24" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH24" t="str">
@@ -5532,13 +5539,13 @@
       <c r="V25" t="str">
         <v/>
       </c>
-      <c r="W25" t="str">
+      <c r="W25" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
+      <c r="X25" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y25" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z25" t="str">
@@ -5547,16 +5554,16 @@
       <c r="AA25" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB25" t="str">
+      <c r="AB25" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC25" t="str">
         <v/>
       </c>
-      <c r="AD25" t="str">
+      <c r="AD25" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE25" t="str">
+      <c r="AE25" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF25" t="str">
@@ -5568,7 +5575,7 @@
       <c r="AH25" t="str">
         <v/>
       </c>
-      <c r="AI25" t="str">
+      <c r="AI25" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ25" t="str">
@@ -5601,7 +5608,7 @@
       <c r="AS25" t="str">
         <v/>
       </c>
-      <c r="AT25" t="str">
+      <c r="AT25" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU25" t="str">
@@ -5628,10 +5635,10 @@
       <c r="BB25" t="str">
         <v/>
       </c>
-      <c r="BC25" t="str">
+      <c r="BC25" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD25" t="str">
+      <c r="BD25" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE25" t="str">
@@ -5640,7 +5647,7 @@
       <c r="BF25" t="str">
         <v/>
       </c>
-      <c r="BG25" t="str">
+      <c r="BG25" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH25" t="str">
@@ -5714,13 +5721,13 @@
       <c r="V26" t="str">
         <v/>
       </c>
-      <c r="W26" t="str">
+      <c r="W26" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
+      <c r="X26" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y26" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z26" t="str">
@@ -5729,16 +5736,16 @@
       <c r="AA26" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB26" t="str">
+      <c r="AB26" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC26" t="str">
         <v/>
       </c>
-      <c r="AD26" t="str">
+      <c r="AD26" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE26" t="str">
+      <c r="AE26" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF26" t="str">
@@ -5750,7 +5757,7 @@
       <c r="AH26" t="str">
         <v/>
       </c>
-      <c r="AI26" t="str">
+      <c r="AI26" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ26" t="str">
@@ -5783,7 +5790,7 @@
       <c r="AS26" t="str">
         <v/>
       </c>
-      <c r="AT26" t="str">
+      <c r="AT26" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU26" t="str">
@@ -5810,10 +5817,10 @@
       <c r="BB26" t="str">
         <v/>
       </c>
-      <c r="BC26" t="str">
+      <c r="BC26" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD26" t="str">
+      <c r="BD26" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE26" t="str">
@@ -5822,7 +5829,7 @@
       <c r="BF26" t="str">
         <v/>
       </c>
-      <c r="BG26" t="str">
+      <c r="BG26" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH26" t="str">
@@ -5896,13 +5903,13 @@
       <c r="V27" t="str">
         <v/>
       </c>
-      <c r="W27" t="str">
+      <c r="W27" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
+      <c r="X27" t="str" s="1">
+        <v/>
+      </c>
+      <c r="Y27" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z27" t="str">
@@ -5911,16 +5918,16 @@
       <c r="AA27" t="str">
         <v>尼龙lb 12-165, 14-145, 16-120, 20-100</v>
       </c>
-      <c r="AB27" t="str">
+      <c r="AB27" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC27" t="str">
         <v/>
       </c>
-      <c r="AD27" t="str">
+      <c r="AD27" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE27" t="str">
+      <c r="AE27" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF27" t="str">
@@ -5932,7 +5939,7 @@
       <c r="AH27" t="str">
         <v/>
       </c>
-      <c r="AI27" t="str">
+      <c r="AI27" t="str" s="1">
         <v>淡水重饵</v>
       </c>
       <c r="AJ27" t="str">
@@ -5965,7 +5972,7 @@
       <c r="AS27" t="str">
         <v/>
       </c>
-      <c r="AT27" t="str">
+      <c r="AT27" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU27" t="str">
@@ -5992,10 +5999,10 @@
       <c r="BB27" t="str">
         <v/>
       </c>
-      <c r="BC27" t="str">
+      <c r="BC27" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD27" t="str">
+      <c r="BD27" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE27" t="str">
@@ -6004,7 +6011,7 @@
       <c r="BF27" t="str">
         <v/>
       </c>
-      <c r="BG27" t="str">
+      <c r="BG27" t="str" s="1">
         <v>重饵 / 泛用</v>
       </c>
       <c r="BH27" t="str">
@@ -6078,13 +6085,13 @@
       <c r="V28" t="str">
         <v/>
       </c>
-      <c r="W28" t="str">
+      <c r="W28" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X28" t="str">
         <v/>
       </c>
-      <c r="Y28" t="str">
+      <c r="Y28" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z28" t="str">
@@ -6093,16 +6100,16 @@
       <c r="AA28" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB28" t="str">
+      <c r="AB28" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC28" t="str">
         <v/>
       </c>
-      <c r="AD28" t="str">
+      <c r="AD28" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE28" t="str">
+      <c r="AE28" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF28" t="str">
@@ -6114,7 +6121,7 @@
       <c r="AH28" t="str">
         <v/>
       </c>
-      <c r="AI28" t="str">
+      <c r="AI28" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ28" t="str">
@@ -6147,7 +6154,7 @@
       <c r="AS28" t="str">
         <v/>
       </c>
-      <c r="AT28" t="str">
+      <c r="AT28" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU28" t="str">
@@ -6174,10 +6181,10 @@
       <c r="BB28" t="str">
         <v/>
       </c>
-      <c r="BC28" t="str">
+      <c r="BC28" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD28" t="str">
+      <c r="BD28" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE28" t="str">
@@ -6186,7 +6193,7 @@
       <c r="BF28" t="str">
         <v/>
       </c>
-      <c r="BG28" t="str">
+      <c r="BG28" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH28" t="str">
@@ -6260,13 +6267,13 @@
       <c r="V29" t="str">
         <v/>
       </c>
-      <c r="W29" t="str">
+      <c r="W29" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X29" t="str">
         <v/>
       </c>
-      <c r="Y29" t="str">
+      <c r="Y29" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z29" t="str">
@@ -6275,16 +6282,16 @@
       <c r="AA29" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB29" t="str">
+      <c r="AB29" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC29" t="str">
         <v/>
       </c>
-      <c r="AD29" t="str">
+      <c r="AD29" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE29" t="str">
+      <c r="AE29" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF29" t="str">
@@ -6296,7 +6303,7 @@
       <c r="AH29" t="str">
         <v/>
       </c>
-      <c r="AI29" t="str">
+      <c r="AI29" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ29" t="str">
@@ -6329,7 +6336,7 @@
       <c r="AS29" t="str">
         <v/>
       </c>
-      <c r="AT29" t="str">
+      <c r="AT29" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU29" t="str">
@@ -6356,10 +6363,10 @@
       <c r="BB29" t="str">
         <v/>
       </c>
-      <c r="BC29" t="str">
+      <c r="BC29" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD29" t="str">
+      <c r="BD29" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE29" t="str">
@@ -6368,7 +6375,7 @@
       <c r="BF29" t="str">
         <v/>
       </c>
-      <c r="BG29" t="str">
+      <c r="BG29" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH29" t="str">
@@ -6442,13 +6449,13 @@
       <c r="V30" t="str">
         <v/>
       </c>
-      <c r="W30" t="str">
+      <c r="W30" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X30" t="str">
         <v/>
       </c>
-      <c r="Y30" t="str">
+      <c r="Y30" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z30" t="str">
@@ -6457,16 +6464,16 @@
       <c r="AA30" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB30" t="str">
+      <c r="AB30" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC30" t="str">
         <v/>
       </c>
-      <c r="AD30" t="str">
+      <c r="AD30" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE30" t="str">
+      <c r="AE30" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF30" t="str">
@@ -6478,7 +6485,7 @@
       <c r="AH30" t="str">
         <v/>
       </c>
-      <c r="AI30" t="str">
+      <c r="AI30" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ30" t="str">
@@ -6511,7 +6518,7 @@
       <c r="AS30" t="str">
         <v/>
       </c>
-      <c r="AT30" t="str">
+      <c r="AT30" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU30" t="str">
@@ -6538,10 +6545,10 @@
       <c r="BB30" t="str">
         <v/>
       </c>
-      <c r="BC30" t="str">
+      <c r="BC30" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD30" t="str">
+      <c r="BD30" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE30" t="str">
@@ -6550,7 +6557,7 @@
       <c r="BF30" t="str">
         <v/>
       </c>
-      <c r="BG30" t="str">
+      <c r="BG30" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH30" t="str">
@@ -6624,13 +6631,13 @@
       <c r="V31" t="str">
         <v/>
       </c>
-      <c r="W31" t="str">
+      <c r="W31" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
       <c r="X31" t="str">
         <v/>
       </c>
-      <c r="Y31" t="str">
+      <c r="Y31" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+4BB)</v>
       </c>
       <c r="Z31" t="str">
@@ -6639,16 +6646,16 @@
       <c r="AA31" t="str">
         <v>尼龙号 4-210, 5-160, 6-135 / 尼龙lb 16-210, 20-160, 25-135 / PE 4-180, 5-140, 6-120</v>
       </c>
-      <c r="AB31" t="str">
+      <c r="AB31" t="str" s="1">
         <v>Paddle</v>
       </c>
       <c r="AC31" t="str">
         <v/>
       </c>
-      <c r="AD31" t="str">
+      <c r="AD31" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE31" t="str">
+      <c r="AE31" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF31" t="str">
@@ -6660,7 +6667,7 @@
       <c r="AH31" t="str">
         <v/>
       </c>
-      <c r="AI31" t="str">
+      <c r="AI31" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ31" t="str">
@@ -6693,7 +6700,7 @@
       <c r="AS31" t="str">
         <v/>
       </c>
-      <c r="AT31" t="str">
+      <c r="AT31" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU31" t="str">
@@ -6720,10 +6727,10 @@
       <c r="BB31" t="str">
         <v/>
       </c>
-      <c r="BC31" t="str">
+      <c r="BC31" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD31" t="str">
+      <c r="BD31" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE31" t="str">
@@ -6732,7 +6739,7 @@
       <c r="BF31" t="str">
         <v/>
       </c>
-      <c r="BG31" t="str">
+      <c r="BG31" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH31" t="str">
@@ -6797,7 +6804,7 @@
       <c r="S32" t="str">
         <v>19</v>
       </c>
-      <c r="T32" t="str">
+      <c r="T32" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U32" t="str">
@@ -6806,13 +6813,13 @@
       <c r="V32" t="str">
         <v/>
       </c>
-      <c r="W32" t="str">
+      <c r="W32" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X32" t="str">
+      <c r="X32" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y32" t="str">
+      <c r="Y32" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z32" t="str">
@@ -6824,13 +6831,13 @@
       <c r="AB32" t="str">
         <v/>
       </c>
-      <c r="AC32" t="str">
+      <c r="AC32" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD32" t="str">
+      <c r="AD32" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE32" t="str">
+      <c r="AE32" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF32" t="str">
@@ -6842,7 +6849,7 @@
       <c r="AH32" t="str">
         <v/>
       </c>
-      <c r="AI32" t="str">
+      <c r="AI32" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ32" t="str">
@@ -6875,7 +6882,7 @@
       <c r="AS32" t="str">
         <v/>
       </c>
-      <c r="AT32" t="str">
+      <c r="AT32" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU32" t="str">
@@ -6902,7 +6909,7 @@
       <c r="BB32" t="str">
         <v/>
       </c>
-      <c r="BC32" t="str">
+      <c r="BC32" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD32" t="str">
@@ -6914,7 +6921,7 @@
       <c r="BF32" t="str">
         <v/>
       </c>
-      <c r="BG32" t="str">
+      <c r="BG32" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH32" t="str">
@@ -6979,7 +6986,7 @@
       <c r="S33" t="str">
         <v>19</v>
       </c>
-      <c r="T33" t="str">
+      <c r="T33" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U33" t="str">
@@ -6988,13 +6995,13 @@
       <c r="V33" t="str">
         <v/>
       </c>
-      <c r="W33" t="str">
+      <c r="W33" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X33" t="str">
+      <c r="X33" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y33" t="str">
+      <c r="Y33" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z33" t="str">
@@ -7006,13 +7013,13 @@
       <c r="AB33" t="str">
         <v/>
       </c>
-      <c r="AC33" t="str">
+      <c r="AC33" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD33" t="str">
+      <c r="AD33" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE33" t="str">
+      <c r="AE33" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF33" t="str">
@@ -7024,7 +7031,7 @@
       <c r="AH33" t="str">
         <v/>
       </c>
-      <c r="AI33" t="str">
+      <c r="AI33" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ33" t="str">
@@ -7057,7 +7064,7 @@
       <c r="AS33" t="str">
         <v/>
       </c>
-      <c r="AT33" t="str">
+      <c r="AT33" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU33" t="str">
@@ -7084,7 +7091,7 @@
       <c r="BB33" t="str">
         <v/>
       </c>
-      <c r="BC33" t="str">
+      <c r="BC33" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD33" t="str">
@@ -7096,7 +7103,7 @@
       <c r="BF33" t="str">
         <v/>
       </c>
-      <c r="BG33" t="str">
+      <c r="BG33" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH33" t="str">
@@ -7161,7 +7168,7 @@
       <c r="S34" t="str">
         <v>19</v>
       </c>
-      <c r="T34" t="str">
+      <c r="T34" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U34" t="str">
@@ -7170,13 +7177,13 @@
       <c r="V34" t="str">
         <v/>
       </c>
-      <c r="W34" t="str">
+      <c r="W34" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X34" t="str">
+      <c r="X34" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y34" t="str">
+      <c r="Y34" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z34" t="str">
@@ -7188,13 +7195,13 @@
       <c r="AB34" t="str">
         <v/>
       </c>
-      <c r="AC34" t="str">
+      <c r="AC34" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD34" t="str">
+      <c r="AD34" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE34" t="str">
+      <c r="AE34" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF34" t="str">
@@ -7206,7 +7213,7 @@
       <c r="AH34" t="str">
         <v/>
       </c>
-      <c r="AI34" t="str">
+      <c r="AI34" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ34" t="str">
@@ -7239,7 +7246,7 @@
       <c r="AS34" t="str">
         <v/>
       </c>
-      <c r="AT34" t="str">
+      <c r="AT34" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU34" t="str">
@@ -7266,7 +7273,7 @@
       <c r="BB34" t="str">
         <v/>
       </c>
-      <c r="BC34" t="str">
+      <c r="BC34" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD34" t="str">
@@ -7278,7 +7285,7 @@
       <c r="BF34" t="str">
         <v/>
       </c>
-      <c r="BG34" t="str">
+      <c r="BG34" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH34" t="str">
@@ -7343,7 +7350,7 @@
       <c r="S35" t="str">
         <v>19</v>
       </c>
-      <c r="T35" t="str">
+      <c r="T35" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U35" t="str">
@@ -7352,13 +7359,13 @@
       <c r="V35" t="str">
         <v/>
       </c>
-      <c r="W35" t="str">
+      <c r="W35" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X35" t="str">
+      <c r="X35" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y35" t="str">
+      <c r="Y35" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z35" t="str">
@@ -7370,13 +7377,13 @@
       <c r="AB35" t="str">
         <v/>
       </c>
-      <c r="AC35" t="str">
+      <c r="AC35" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD35" t="str">
+      <c r="AD35" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE35" t="str">
+      <c r="AE35" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF35" t="str">
@@ -7388,7 +7395,7 @@
       <c r="AH35" t="str">
         <v/>
       </c>
-      <c r="AI35" t="str">
+      <c r="AI35" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ35" t="str">
@@ -7421,7 +7428,7 @@
       <c r="AS35" t="str">
         <v/>
       </c>
-      <c r="AT35" t="str">
+      <c r="AT35" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU35" t="str">
@@ -7448,7 +7455,7 @@
       <c r="BB35" t="str">
         <v/>
       </c>
-      <c r="BC35" t="str">
+      <c r="BC35" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD35" t="str">
@@ -7460,7 +7467,7 @@
       <c r="BF35" t="str">
         <v/>
       </c>
-      <c r="BG35" t="str">
+      <c r="BG35" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH35" t="str">
@@ -7525,7 +7532,7 @@
       <c r="S36" t="str">
         <v>19</v>
       </c>
-      <c r="T36" t="str">
+      <c r="T36" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U36" t="str">
@@ -7534,13 +7541,13 @@
       <c r="V36" t="str">
         <v/>
       </c>
-      <c r="W36" t="str">
+      <c r="W36" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X36" t="str">
+      <c r="X36" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y36" t="str">
+      <c r="Y36" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z36" t="str">
@@ -7552,13 +7559,13 @@
       <c r="AB36" t="str">
         <v/>
       </c>
-      <c r="AC36" t="str">
+      <c r="AC36" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD36" t="str">
+      <c r="AD36" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE36" t="str">
+      <c r="AE36" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF36" t="str">
@@ -7570,7 +7577,7 @@
       <c r="AH36" t="str">
         <v/>
       </c>
-      <c r="AI36" t="str">
+      <c r="AI36" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ36" t="str">
@@ -7603,7 +7610,7 @@
       <c r="AS36" t="str">
         <v/>
       </c>
-      <c r="AT36" t="str">
+      <c r="AT36" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU36" t="str">
@@ -7630,7 +7637,7 @@
       <c r="BB36" t="str">
         <v/>
       </c>
-      <c r="BC36" t="str">
+      <c r="BC36" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD36" t="str">
@@ -7642,7 +7649,7 @@
       <c r="BF36" t="str">
         <v/>
       </c>
-      <c r="BG36" t="str">
+      <c r="BG36" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH36" t="str">
@@ -7707,7 +7714,7 @@
       <c r="S37" t="str">
         <v>19</v>
       </c>
-      <c r="T37" t="str">
+      <c r="T37" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U37" t="str">
@@ -7716,13 +7723,13 @@
       <c r="V37" t="str">
         <v/>
       </c>
-      <c r="W37" t="str">
+      <c r="W37" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X37" t="str">
+      <c r="X37" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y37" t="str">
+      <c r="Y37" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z37" t="str">
@@ -7734,13 +7741,13 @@
       <c r="AB37" t="str">
         <v/>
       </c>
-      <c r="AC37" t="str">
+      <c r="AC37" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD37" t="str">
+      <c r="AD37" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE37" t="str">
+      <c r="AE37" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF37" t="str">
@@ -7752,7 +7759,7 @@
       <c r="AH37" t="str">
         <v/>
       </c>
-      <c r="AI37" t="str">
+      <c r="AI37" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ37" t="str">
@@ -7785,7 +7792,7 @@
       <c r="AS37" t="str">
         <v/>
       </c>
-      <c r="AT37" t="str">
+      <c r="AT37" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU37" t="str">
@@ -7812,7 +7819,7 @@
       <c r="BB37" t="str">
         <v/>
       </c>
-      <c r="BC37" t="str">
+      <c r="BC37" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD37" t="str">
@@ -7824,7 +7831,7 @@
       <c r="BF37" t="str">
         <v/>
       </c>
-      <c r="BG37" t="str">
+      <c r="BG37" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH37" t="str">
@@ -7889,7 +7896,7 @@
       <c r="S38" t="str">
         <v>19</v>
       </c>
-      <c r="T38" t="str">
+      <c r="T38" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U38" t="str">
@@ -7898,13 +7905,13 @@
       <c r="V38" t="str">
         <v/>
       </c>
-      <c r="W38" t="str">
+      <c r="W38" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X38" t="str">
+      <c r="X38" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y38" t="str">
+      <c r="Y38" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z38" t="str">
@@ -7916,13 +7923,13 @@
       <c r="AB38" t="str">
         <v/>
       </c>
-      <c r="AC38" t="str">
+      <c r="AC38" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD38" t="str">
+      <c r="AD38" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE38" t="str">
+      <c r="AE38" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF38" t="str">
@@ -7934,7 +7941,7 @@
       <c r="AH38" t="str">
         <v/>
       </c>
-      <c r="AI38" t="str">
+      <c r="AI38" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ38" t="str">
@@ -7967,7 +7974,7 @@
       <c r="AS38" t="str">
         <v/>
       </c>
-      <c r="AT38" t="str">
+      <c r="AT38" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU38" t="str">
@@ -7994,7 +8001,7 @@
       <c r="BB38" t="str">
         <v/>
       </c>
-      <c r="BC38" t="str">
+      <c r="BC38" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD38" t="str">
@@ -8006,7 +8013,7 @@
       <c r="BF38" t="str">
         <v/>
       </c>
-      <c r="BG38" t="str">
+      <c r="BG38" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH38" t="str">
@@ -8071,7 +8078,7 @@
       <c r="S39" t="str">
         <v>19</v>
       </c>
-      <c r="T39" t="str">
+      <c r="T39" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U39" t="str">
@@ -8080,13 +8087,13 @@
       <c r="V39" t="str">
         <v/>
       </c>
-      <c r="W39" t="str">
+      <c r="W39" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X39" t="str">
+      <c r="X39" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y39" t="str">
+      <c r="Y39" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z39" t="str">
@@ -8098,13 +8105,13 @@
       <c r="AB39" t="str">
         <v/>
       </c>
-      <c r="AC39" t="str">
+      <c r="AC39" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD39" t="str">
+      <c r="AD39" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE39" t="str">
+      <c r="AE39" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF39" t="str">
@@ -8116,7 +8123,7 @@
       <c r="AH39" t="str">
         <v/>
       </c>
-      <c r="AI39" t="str">
+      <c r="AI39" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ39" t="str">
@@ -8149,7 +8156,7 @@
       <c r="AS39" t="str">
         <v/>
       </c>
-      <c r="AT39" t="str">
+      <c r="AT39" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU39" t="str">
@@ -8176,7 +8183,7 @@
       <c r="BB39" t="str">
         <v/>
       </c>
-      <c r="BC39" t="str">
+      <c r="BC39" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD39" t="str">
@@ -8188,7 +8195,7 @@
       <c r="BF39" t="str">
         <v/>
       </c>
-      <c r="BG39" t="str">
+      <c r="BG39" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH39" t="str">
@@ -8253,7 +8260,7 @@
       <c r="S40" t="str">
         <v>19</v>
       </c>
-      <c r="T40" t="str">
+      <c r="T40" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U40" t="str">
@@ -8262,13 +8269,13 @@
       <c r="V40" t="str">
         <v/>
       </c>
-      <c r="W40" t="str">
+      <c r="W40" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X40" t="str">
+      <c r="X40" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y40" t="str">
+      <c r="Y40" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z40" t="str">
@@ -8280,13 +8287,13 @@
       <c r="AB40" t="str">
         <v/>
       </c>
-      <c r="AC40" t="str">
+      <c r="AC40" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD40" t="str">
+      <c r="AD40" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE40" t="str">
+      <c r="AE40" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF40" t="str">
@@ -8298,7 +8305,7 @@
       <c r="AH40" t="str">
         <v/>
       </c>
-      <c r="AI40" t="str">
+      <c r="AI40" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ40" t="str">
@@ -8331,7 +8338,7 @@
       <c r="AS40" t="str">
         <v/>
       </c>
-      <c r="AT40" t="str">
+      <c r="AT40" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU40" t="str">
@@ -8358,7 +8365,7 @@
       <c r="BB40" t="str">
         <v/>
       </c>
-      <c r="BC40" t="str">
+      <c r="BC40" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD40" t="str">
@@ -8370,7 +8377,7 @@
       <c r="BF40" t="str">
         <v/>
       </c>
-      <c r="BG40" t="str">
+      <c r="BG40" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH40" t="str">
@@ -8435,7 +8442,7 @@
       <c r="S41" t="str">
         <v>19</v>
       </c>
-      <c r="T41" t="str">
+      <c r="T41" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U41" t="str">
@@ -8444,13 +8451,13 @@
       <c r="V41" t="str">
         <v/>
       </c>
-      <c r="W41" t="str">
+      <c r="W41" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X41" t="str">
+      <c r="X41" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y41" t="str">
+      <c r="Y41" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z41" t="str">
@@ -8462,13 +8469,13 @@
       <c r="AB41" t="str">
         <v/>
       </c>
-      <c r="AC41" t="str">
+      <c r="AC41" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD41" t="str">
+      <c r="AD41" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE41" t="str">
+      <c r="AE41" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF41" t="str">
@@ -8480,7 +8487,7 @@
       <c r="AH41" t="str">
         <v/>
       </c>
-      <c r="AI41" t="str">
+      <c r="AI41" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ41" t="str">
@@ -8513,7 +8520,7 @@
       <c r="AS41" t="str">
         <v/>
       </c>
-      <c r="AT41" t="str">
+      <c r="AT41" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU41" t="str">
@@ -8540,7 +8547,7 @@
       <c r="BB41" t="str">
         <v/>
       </c>
-      <c r="BC41" t="str">
+      <c r="BC41" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD41" t="str">
@@ -8552,7 +8559,7 @@
       <c r="BF41" t="str">
         <v/>
       </c>
-      <c r="BG41" t="str">
+      <c r="BG41" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH41" t="str">
@@ -8617,7 +8624,7 @@
       <c r="S42" t="str">
         <v>19</v>
       </c>
-      <c r="T42" t="str">
+      <c r="T42" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U42" t="str">
@@ -8626,13 +8633,13 @@
       <c r="V42" t="str">
         <v/>
       </c>
-      <c r="W42" t="str">
+      <c r="W42" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X42" t="str">
+      <c r="X42" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y42" t="str">
+      <c r="Y42" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z42" t="str">
@@ -8644,13 +8651,13 @@
       <c r="AB42" t="str">
         <v/>
       </c>
-      <c r="AC42" t="str">
+      <c r="AC42" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD42" t="str">
+      <c r="AD42" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE42" t="str">
+      <c r="AE42" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF42" t="str">
@@ -8662,7 +8669,7 @@
       <c r="AH42" t="str">
         <v/>
       </c>
-      <c r="AI42" t="str">
+      <c r="AI42" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ42" t="str">
@@ -8695,7 +8702,7 @@
       <c r="AS42" t="str">
         <v/>
       </c>
-      <c r="AT42" t="str">
+      <c r="AT42" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU42" t="str">
@@ -8722,7 +8729,7 @@
       <c r="BB42" t="str">
         <v/>
       </c>
-      <c r="BC42" t="str">
+      <c r="BC42" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD42" t="str">
@@ -8734,7 +8741,7 @@
       <c r="BF42" t="str">
         <v/>
       </c>
-      <c r="BG42" t="str">
+      <c r="BG42" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH42" t="str">
@@ -8799,7 +8806,7 @@
       <c r="S43" t="str">
         <v>19</v>
       </c>
-      <c r="T43" t="str">
+      <c r="T43" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U43" t="str">
@@ -8808,13 +8815,13 @@
       <c r="V43" t="str">
         <v/>
       </c>
-      <c r="W43" t="str">
+      <c r="W43" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X43" t="str">
+      <c r="X43" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y43" t="str">
+      <c r="Y43" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z43" t="str">
@@ -8826,13 +8833,13 @@
       <c r="AB43" t="str">
         <v/>
       </c>
-      <c r="AC43" t="str">
+      <c r="AC43" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD43" t="str">
+      <c r="AD43" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE43" t="str">
+      <c r="AE43" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF43" t="str">
@@ -8844,7 +8851,7 @@
       <c r="AH43" t="str">
         <v/>
       </c>
-      <c r="AI43" t="str">
+      <c r="AI43" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ43" t="str">
@@ -8877,7 +8884,7 @@
       <c r="AS43" t="str">
         <v/>
       </c>
-      <c r="AT43" t="str">
+      <c r="AT43" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU43" t="str">
@@ -8904,7 +8911,7 @@
       <c r="BB43" t="str">
         <v/>
       </c>
-      <c r="BC43" t="str">
+      <c r="BC43" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD43" t="str">
@@ -8916,7 +8923,7 @@
       <c r="BF43" t="str">
         <v/>
       </c>
-      <c r="BG43" t="str">
+      <c r="BG43" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH43" t="str">
@@ -8981,7 +8988,7 @@
       <c r="S44" t="str">
         <v>19</v>
       </c>
-      <c r="T44" t="str">
+      <c r="T44" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U44" t="str">
@@ -8990,13 +8997,13 @@
       <c r="V44" t="str">
         <v/>
       </c>
-      <c r="W44" t="str">
+      <c r="W44" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X44" t="str">
+      <c r="X44" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y44" t="str">
+      <c r="Y44" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z44" t="str">
@@ -9008,13 +9015,13 @@
       <c r="AB44" t="str">
         <v/>
       </c>
-      <c r="AC44" t="str">
+      <c r="AC44" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD44" t="str">
+      <c r="AD44" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE44" t="str">
+      <c r="AE44" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF44" t="str">
@@ -9026,7 +9033,7 @@
       <c r="AH44" t="str">
         <v/>
       </c>
-      <c r="AI44" t="str">
+      <c r="AI44" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ44" t="str">
@@ -9059,7 +9066,7 @@
       <c r="AS44" t="str">
         <v/>
       </c>
-      <c r="AT44" t="str">
+      <c r="AT44" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU44" t="str">
@@ -9086,7 +9093,7 @@
       <c r="BB44" t="str">
         <v/>
       </c>
-      <c r="BC44" t="str">
+      <c r="BC44" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD44" t="str">
@@ -9098,7 +9105,7 @@
       <c r="BF44" t="str">
         <v/>
       </c>
-      <c r="BG44" t="str">
+      <c r="BG44" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH44" t="str">
@@ -9163,7 +9170,7 @@
       <c r="S45" t="str">
         <v>19</v>
       </c>
-      <c r="T45" t="str">
+      <c r="T45" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U45" t="str">
@@ -9172,13 +9179,13 @@
       <c r="V45" t="str">
         <v/>
       </c>
-      <c r="W45" t="str">
+      <c r="W45" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X45" t="str">
+      <c r="X45" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y45" t="str">
+      <c r="Y45" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z45" t="str">
@@ -9190,13 +9197,13 @@
       <c r="AB45" t="str">
         <v/>
       </c>
-      <c r="AC45" t="str">
+      <c r="AC45" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD45" t="str">
+      <c r="AD45" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE45" t="str">
+      <c r="AE45" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF45" t="str">
@@ -9208,7 +9215,7 @@
       <c r="AH45" t="str">
         <v/>
       </c>
-      <c r="AI45" t="str">
+      <c r="AI45" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ45" t="str">
@@ -9241,7 +9248,7 @@
       <c r="AS45" t="str">
         <v/>
       </c>
-      <c r="AT45" t="str">
+      <c r="AT45" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU45" t="str">
@@ -9268,7 +9275,7 @@
       <c r="BB45" t="str">
         <v/>
       </c>
-      <c r="BC45" t="str">
+      <c r="BC45" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD45" t="str">
@@ -9280,7 +9287,7 @@
       <c r="BF45" t="str">
         <v/>
       </c>
-      <c r="BG45" t="str">
+      <c r="BG45" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH45" t="str">
@@ -9345,7 +9352,7 @@
       <c r="S46" t="str">
         <v>19</v>
       </c>
-      <c r="T46" t="str">
+      <c r="T46" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U46" t="str">
@@ -9354,13 +9361,13 @@
       <c r="V46" t="str">
         <v/>
       </c>
-      <c r="W46" t="str">
+      <c r="W46" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X46" t="str">
+      <c r="X46" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y46" t="str">
+      <c r="Y46" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z46" t="str">
@@ -9372,13 +9379,13 @@
       <c r="AB46" t="str">
         <v/>
       </c>
-      <c r="AC46" t="str">
+      <c r="AC46" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD46" t="str">
+      <c r="AD46" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE46" t="str">
+      <c r="AE46" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF46" t="str">
@@ -9390,7 +9397,7 @@
       <c r="AH46" t="str">
         <v/>
       </c>
-      <c r="AI46" t="str">
+      <c r="AI46" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ46" t="str">
@@ -9423,7 +9430,7 @@
       <c r="AS46" t="str">
         <v/>
       </c>
-      <c r="AT46" t="str">
+      <c r="AT46" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU46" t="str">
@@ -9450,7 +9457,7 @@
       <c r="BB46" t="str">
         <v/>
       </c>
-      <c r="BC46" t="str">
+      <c r="BC46" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD46" t="str">
@@ -9462,7 +9469,7 @@
       <c r="BF46" t="str">
         <v/>
       </c>
-      <c r="BG46" t="str">
+      <c r="BG46" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH46" t="str">
@@ -9527,7 +9534,7 @@
       <c r="S47" t="str">
         <v>19</v>
       </c>
-      <c r="T47" t="str">
+      <c r="T47" t="str" s="1">
         <v>11.32</v>
       </c>
       <c r="U47" t="str">
@@ -9536,13 +9543,13 @@
       <c r="V47" t="str">
         <v/>
       </c>
-      <c r="W47" t="str">
+      <c r="W47" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X47" t="str">
+      <c r="X47" t="str" s="1">
         <v>Genuine Spool 20 Metanium / 22 Metanium SHALLOW EDITION / Avail Microcast Spool 20MT24R, 20MT42R</v>
       </c>
-      <c r="Y47" t="str">
+      <c r="Y47" t="str" s="1">
         <v>Handle Knob Cap HKC-20MT / Custom Handle Knob</v>
       </c>
       <c r="Z47" t="str">
@@ -9554,13 +9561,13 @@
       <c r="AB47" t="str">
         <v/>
       </c>
-      <c r="AC47" t="str">
+      <c r="AC47" t="str" s="1">
         <v>HKC-20MT</v>
       </c>
-      <c r="AD47" t="str">
+      <c r="AD47" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE47" t="str">
+      <c r="AE47" t="str" s="1">
         <v>CORESOLID BODY / 一体成型</v>
       </c>
       <c r="AF47" t="str">
@@ -9572,7 +9579,7 @@
       <c r="AH47" t="str">
         <v/>
       </c>
-      <c r="AI47" t="str">
+      <c r="AI47" t="str" s="1">
         <v>淡水泛用</v>
       </c>
       <c r="AJ47" t="str">
@@ -9605,7 +9612,7 @@
       <c r="AS47" t="str">
         <v/>
       </c>
-      <c r="AT47" t="str">
+      <c r="AT47" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU47" t="str">
@@ -9632,7 +9639,7 @@
       <c r="BB47" t="str">
         <v/>
       </c>
-      <c r="BC47" t="str">
+      <c r="BC47" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD47" t="str">
@@ -9644,7 +9651,7 @@
       <c r="BF47" t="str">
         <v/>
       </c>
-      <c r="BG47" t="str">
+      <c r="BG47" t="str" s="1">
         <v>淡水泛用 / 技巧</v>
       </c>
       <c r="BH47" t="str">
@@ -9709,7 +9716,7 @@
       <c r="S48" t="str">
         <v>19</v>
       </c>
-      <c r="T48" t="str">
+      <c r="T48" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U48" t="str">
@@ -9718,13 +9725,13 @@
       <c r="V48" t="str">
         <v/>
       </c>
-      <c r="W48" t="str">
+      <c r="W48" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X48" t="str">
+      <c r="X48" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y48" t="str">
+      <c r="Y48" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z48" t="str">
@@ -9739,10 +9746,10 @@
       <c r="AC48" t="str">
         <v/>
       </c>
-      <c r="AD48" t="str">
+      <c r="AD48" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE48" t="str">
+      <c r="AE48" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF48" t="str">
@@ -9754,7 +9761,7 @@
       <c r="AH48" t="str">
         <v/>
       </c>
-      <c r="AI48" t="str">
+      <c r="AI48" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ48" t="str">
@@ -9785,9 +9792,9 @@
         <v/>
       </c>
       <c r="AS48" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT48" t="str">
+        <v/>
+      </c>
+      <c r="AT48" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU48" t="str">
@@ -9814,10 +9821,10 @@
       <c r="BB48" t="str">
         <v/>
       </c>
-      <c r="BC48" t="str">
+      <c r="BC48" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD48" t="str">
+      <c r="BD48" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE48" t="str">
@@ -9826,7 +9833,7 @@
       <c r="BF48" t="str">
         <v/>
       </c>
-      <c r="BG48" t="str">
+      <c r="BG48" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH48" t="str">
@@ -9891,7 +9898,7 @@
       <c r="S49" t="str">
         <v>19</v>
       </c>
-      <c r="T49" t="str">
+      <c r="T49" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U49" t="str">
@@ -9900,13 +9907,13 @@
       <c r="V49" t="str">
         <v/>
       </c>
-      <c r="W49" t="str">
+      <c r="W49" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X49" t="str">
+      <c r="X49" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y49" t="str">
+      <c r="Y49" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z49" t="str">
@@ -9921,10 +9928,10 @@
       <c r="AC49" t="str">
         <v/>
       </c>
-      <c r="AD49" t="str">
+      <c r="AD49" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE49" t="str">
+      <c r="AE49" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF49" t="str">
@@ -9936,7 +9943,7 @@
       <c r="AH49" t="str">
         <v/>
       </c>
-      <c r="AI49" t="str">
+      <c r="AI49" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ49" t="str">
@@ -9967,9 +9974,9 @@
         <v/>
       </c>
       <c r="AS49" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT49" t="str">
+        <v/>
+      </c>
+      <c r="AT49" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU49" t="str">
@@ -9996,10 +10003,10 @@
       <c r="BB49" t="str">
         <v/>
       </c>
-      <c r="BC49" t="str">
+      <c r="BC49" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD49" t="str">
+      <c r="BD49" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE49" t="str">
@@ -10008,7 +10015,7 @@
       <c r="BF49" t="str">
         <v/>
       </c>
-      <c r="BG49" t="str">
+      <c r="BG49" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH49" t="str">
@@ -10073,7 +10080,7 @@
       <c r="S50" t="str">
         <v>19</v>
       </c>
-      <c r="T50" t="str">
+      <c r="T50" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U50" t="str">
@@ -10082,13 +10089,13 @@
       <c r="V50" t="str">
         <v/>
       </c>
-      <c r="W50" t="str">
+      <c r="W50" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X50" t="str">
+      <c r="X50" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y50" t="str">
+      <c r="Y50" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z50" t="str">
@@ -10103,10 +10110,10 @@
       <c r="AC50" t="str">
         <v/>
       </c>
-      <c r="AD50" t="str">
+      <c r="AD50" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE50" t="str">
+      <c r="AE50" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF50" t="str">
@@ -10118,7 +10125,7 @@
       <c r="AH50" t="str">
         <v/>
       </c>
-      <c r="AI50" t="str">
+      <c r="AI50" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ50" t="str">
@@ -10149,9 +10156,9 @@
         <v/>
       </c>
       <c r="AS50" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT50" t="str">
+        <v/>
+      </c>
+      <c r="AT50" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU50" t="str">
@@ -10178,10 +10185,10 @@
       <c r="BB50" t="str">
         <v/>
       </c>
-      <c r="BC50" t="str">
+      <c r="BC50" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD50" t="str">
+      <c r="BD50" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE50" t="str">
@@ -10190,7 +10197,7 @@
       <c r="BF50" t="str">
         <v/>
       </c>
-      <c r="BG50" t="str">
+      <c r="BG50" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH50" t="str">
@@ -10255,7 +10262,7 @@
       <c r="S51" t="str">
         <v>19</v>
       </c>
-      <c r="T51" t="str">
+      <c r="T51" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U51" t="str">
@@ -10264,13 +10271,13 @@
       <c r="V51" t="str">
         <v/>
       </c>
-      <c r="W51" t="str">
+      <c r="W51" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X51" t="str">
+      <c r="X51" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y51" t="str">
+      <c r="Y51" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z51" t="str">
@@ -10285,10 +10292,10 @@
       <c r="AC51" t="str">
         <v/>
       </c>
-      <c r="AD51" t="str">
+      <c r="AD51" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE51" t="str">
+      <c r="AE51" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF51" t="str">
@@ -10300,7 +10307,7 @@
       <c r="AH51" t="str">
         <v/>
       </c>
-      <c r="AI51" t="str">
+      <c r="AI51" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ51" t="str">
@@ -10331,9 +10338,9 @@
         <v/>
       </c>
       <c r="AS51" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT51" t="str">
+        <v/>
+      </c>
+      <c r="AT51" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU51" t="str">
@@ -10360,10 +10367,10 @@
       <c r="BB51" t="str">
         <v/>
       </c>
-      <c r="BC51" t="str">
+      <c r="BC51" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD51" t="str">
+      <c r="BD51" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE51" t="str">
@@ -10372,7 +10379,7 @@
       <c r="BF51" t="str">
         <v/>
       </c>
-      <c r="BG51" t="str">
+      <c r="BG51" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH51" t="str">
@@ -10437,7 +10444,7 @@
       <c r="S52" t="str">
         <v>19</v>
       </c>
-      <c r="T52" t="str">
+      <c r="T52" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U52" t="str">
@@ -10446,13 +10453,13 @@
       <c r="V52" t="str">
         <v/>
       </c>
-      <c r="W52" t="str">
+      <c r="W52" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X52" t="str">
+      <c r="X52" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y52" t="str">
+      <c r="Y52" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z52" t="str">
@@ -10467,10 +10474,10 @@
       <c r="AC52" t="str">
         <v/>
       </c>
-      <c r="AD52" t="str">
+      <c r="AD52" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE52" t="str">
+      <c r="AE52" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF52" t="str">
@@ -10482,7 +10489,7 @@
       <c r="AH52" t="str">
         <v/>
       </c>
-      <c r="AI52" t="str">
+      <c r="AI52" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ52" t="str">
@@ -10513,9 +10520,9 @@
         <v/>
       </c>
       <c r="AS52" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT52" t="str">
+        <v/>
+      </c>
+      <c r="AT52" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU52" t="str">
@@ -10542,10 +10549,10 @@
       <c r="BB52" t="str">
         <v/>
       </c>
-      <c r="BC52" t="str">
+      <c r="BC52" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD52" t="str">
+      <c r="BD52" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE52" t="str">
@@ -10554,7 +10561,7 @@
       <c r="BF52" t="str">
         <v/>
       </c>
-      <c r="BG52" t="str">
+      <c r="BG52" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH52" t="str">
@@ -10619,7 +10626,7 @@
       <c r="S53" t="str">
         <v>19</v>
       </c>
-      <c r="T53" t="str">
+      <c r="T53" t="str" s="1">
         <v>12.09</v>
       </c>
       <c r="U53" t="str">
@@ -10628,13 +10635,13 @@
       <c r="V53" t="str">
         <v/>
       </c>
-      <c r="W53" t="str">
+      <c r="W53" t="str" s="1">
         <v>SHG-740ZZ / HRCB-740ZHi</v>
       </c>
-      <c r="X53" t="str">
+      <c r="X53" t="str" s="1">
         <v>Genuine Spool 22 Bantam</v>
       </c>
-      <c r="Y53" t="str">
+      <c r="Y53" t="str" s="1">
         <v>Handle Knob Bearing upgrade (+2BB)</v>
       </c>
       <c r="Z53" t="str">
@@ -10649,10 +10656,10 @@
       <c r="AC53" t="str">
         <v/>
       </c>
-      <c r="AD53" t="str">
+      <c r="AD53" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE53" t="str">
+      <c r="AE53" t="str" s="1">
         <v>CORE SOLID / HAGANE 机身</v>
       </c>
       <c r="AF53" t="str">
@@ -10664,7 +10671,7 @@
       <c r="AH53" t="str">
         <v/>
       </c>
-      <c r="AI53" t="str">
+      <c r="AI53" t="str" s="1">
         <v>淡水强力泛用</v>
       </c>
       <c r="AJ53" t="str">
@@ -10695,9 +10702,9 @@
         <v/>
       </c>
       <c r="AS53" t="str">
-        <v>是</v>
-      </c>
-      <c r="AT53" t="str">
+        <v/>
+      </c>
+      <c r="AT53" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU53" t="str">
@@ -10724,10 +10731,10 @@
       <c r="BB53" t="str">
         <v/>
       </c>
-      <c r="BC53" t="str">
+      <c r="BC53" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD53" t="str">
+      <c r="BD53" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE53" t="str">
@@ -10736,7 +10743,7 @@
       <c r="BF53" t="str">
         <v/>
       </c>
-      <c r="BG53" t="str">
+      <c r="BG53" t="str" s="1">
         <v>强力泛用</v>
       </c>
       <c r="BH53" t="str">
@@ -10810,10 +10817,10 @@
       <c r="V54" t="str">
         <v/>
       </c>
-      <c r="W54" t="str">
+      <c r="W54" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X54" t="str">
+      <c r="X54" t="str" s="1">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y54" t="str">
@@ -10831,10 +10838,10 @@
       <c r="AC54" t="str">
         <v/>
       </c>
-      <c r="AD54" t="str">
+      <c r="AD54" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE54" t="str">
+      <c r="AE54" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF54" t="str">
@@ -10846,7 +10853,7 @@
       <c r="AH54" t="str">
         <v/>
       </c>
-      <c r="AI54" t="str">
+      <c r="AI54" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ54" t="str">
@@ -10879,7 +10886,7 @@
       <c r="AS54" t="str">
         <v/>
       </c>
-      <c r="AT54" t="str">
+      <c r="AT54" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU54" t="str">
@@ -10906,10 +10913,10 @@
       <c r="BB54" t="str">
         <v/>
       </c>
-      <c r="BC54" t="str">
+      <c r="BC54" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD54" t="str">
+      <c r="BD54" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE54" t="str">
@@ -10918,7 +10925,7 @@
       <c r="BF54" t="str">
         <v/>
       </c>
-      <c r="BG54" t="str">
+      <c r="BG54" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH54" t="str">
@@ -10992,10 +10999,10 @@
       <c r="V55" t="str">
         <v/>
       </c>
-      <c r="W55" t="str">
+      <c r="W55" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X55" t="str">
+      <c r="X55" t="str" s="1">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y55" t="str">
@@ -11013,10 +11020,10 @@
       <c r="AC55" t="str">
         <v/>
       </c>
-      <c r="AD55" t="str">
+      <c r="AD55" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE55" t="str">
+      <c r="AE55" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF55" t="str">
@@ -11028,7 +11035,7 @@
       <c r="AH55" t="str">
         <v/>
       </c>
-      <c r="AI55" t="str">
+      <c r="AI55" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ55" t="str">
@@ -11061,7 +11068,7 @@
       <c r="AS55" t="str">
         <v/>
       </c>
-      <c r="AT55" t="str">
+      <c r="AT55" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU55" t="str">
@@ -11088,10 +11095,10 @@
       <c r="BB55" t="str">
         <v/>
       </c>
-      <c r="BC55" t="str">
+      <c r="BC55" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD55" t="str">
+      <c r="BD55" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE55" t="str">
@@ -11100,7 +11107,7 @@
       <c r="BF55" t="str">
         <v/>
       </c>
-      <c r="BG55" t="str">
+      <c r="BG55" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH55" t="str">
@@ -11174,10 +11181,10 @@
       <c r="V56" t="str">
         <v/>
       </c>
-      <c r="W56" t="str">
+      <c r="W56" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X56" t="str">
+      <c r="X56" t="str" s="1">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y56" t="str">
@@ -11195,10 +11202,10 @@
       <c r="AC56" t="str">
         <v/>
       </c>
-      <c r="AD56" t="str">
+      <c r="AD56" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE56" t="str">
+      <c r="AE56" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF56" t="str">
@@ -11210,7 +11217,7 @@
       <c r="AH56" t="str">
         <v/>
       </c>
-      <c r="AI56" t="str">
+      <c r="AI56" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ56" t="str">
@@ -11243,7 +11250,7 @@
       <c r="AS56" t="str">
         <v/>
       </c>
-      <c r="AT56" t="str">
+      <c r="AT56" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU56" t="str">
@@ -11270,10 +11277,10 @@
       <c r="BB56" t="str">
         <v/>
       </c>
-      <c r="BC56" t="str">
+      <c r="BC56" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD56" t="str">
+      <c r="BD56" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE56" t="str">
@@ -11282,7 +11289,7 @@
       <c r="BF56" t="str">
         <v/>
       </c>
-      <c r="BG56" t="str">
+      <c r="BG56" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH56" t="str">
@@ -11356,10 +11363,10 @@
       <c r="V57" t="str">
         <v/>
       </c>
-      <c r="W57" t="str">
+      <c r="W57" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X57" t="str">
+      <c r="X57" t="str" s="1">
         <v>Genuine Spool 23 ANTARES DC MD</v>
       </c>
       <c r="Y57" t="str">
@@ -11377,10 +11384,10 @@
       <c r="AC57" t="str">
         <v/>
       </c>
-      <c r="AD57" t="str">
+      <c r="AD57" t="str" s="1">
         <v>Magnesium</v>
       </c>
-      <c r="AE57" t="str">
+      <c r="AE57" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF57" t="str">
@@ -11392,7 +11399,7 @@
       <c r="AH57" t="str">
         <v/>
       </c>
-      <c r="AI57" t="str">
+      <c r="AI57" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="AJ57" t="str">
@@ -11425,7 +11432,7 @@
       <c r="AS57" t="str">
         <v/>
       </c>
-      <c r="AT57" t="str">
+      <c r="AT57" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU57" t="str">
@@ -11452,10 +11459,10 @@
       <c r="BB57" t="str">
         <v/>
       </c>
-      <c r="BC57" t="str">
+      <c r="BC57" t="str" s="1">
         <v>M7</v>
       </c>
-      <c r="BD57" t="str">
+      <c r="BD57" t="str" s="1">
         <v>Brass</v>
       </c>
       <c r="BE57" t="str">
@@ -11464,7 +11471,7 @@
       <c r="BF57" t="str">
         <v/>
       </c>
-      <c r="BG57" t="str">
+      <c r="BG57" t="str" s="1">
         <v>重饵 / 巨物</v>
       </c>
       <c r="BH57" t="str">
@@ -11538,10 +11545,10 @@
       <c r="V58" t="str">
         <v/>
       </c>
-      <c r="W58" t="str">
+      <c r="W58" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X58" t="str">
+      <c r="X58" t="str" s="1">
         <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y58" t="str">
@@ -11553,16 +11560,16 @@
       <c r="AA58" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
       </c>
-      <c r="AB58" t="str">
+      <c r="AB58" t="str" s="1">
         <v>EVA</v>
       </c>
       <c r="AC58" t="str">
         <v/>
       </c>
-      <c r="AD58" t="str">
+      <c r="AD58" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE58" t="str">
+      <c r="AE58" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF58" t="str">
@@ -11574,7 +11581,7 @@
       <c r="AH58" t="str">
         <v/>
       </c>
-      <c r="AI58" t="str">
+      <c r="AI58" t="str" s="1">
         <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ58" t="str">
@@ -11586,7 +11593,7 @@
       <c r="AL58" t="str">
         <v/>
       </c>
-      <c r="AM58" t="str">
+      <c r="AM58" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN58" t="str">
@@ -11607,7 +11614,7 @@
       <c r="AS58" t="str">
         <v/>
       </c>
-      <c r="AT58" t="str">
+      <c r="AT58" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU58" t="str">
@@ -11631,10 +11638,10 @@
       <c r="BA58" t="str">
         <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_exsence_dc_2022_v2.pdf</v>
       </c>
-      <c r="BB58" t="str">
+      <c r="BB58" t="str" s="1">
         <v>EVA</v>
       </c>
-      <c r="BC58" t="str">
+      <c r="BC58" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD58" t="str">
@@ -11646,7 +11653,7 @@
       <c r="BF58" t="str">
         <v/>
       </c>
-      <c r="BG58" t="str">
+      <c r="BG58" t="str" s="1">
         <v>海鲈</v>
       </c>
       <c r="BH58" t="str">
@@ -11720,10 +11727,10 @@
       <c r="V59" t="str">
         <v/>
       </c>
-      <c r="W59" t="str">
+      <c r="W59" t="str" s="1">
         <v>4x7x2.5（stock）</v>
       </c>
-      <c r="X59" t="str">
+      <c r="X59" t="str" s="1">
         <v>Genuine Spool 22 EXSENCE DC</v>
       </c>
       <c r="Y59" t="str">
@@ -11735,16 +11742,16 @@
       <c r="AA59" t="str">
         <v>氟碳lb 12-130, 14-95, 16-85 / PE 1-365, 1.5-255, 2-180</v>
       </c>
-      <c r="AB59" t="str">
+      <c r="AB59" t="str" s="1">
         <v>EVA</v>
       </c>
       <c r="AC59" t="str">
         <v/>
       </c>
-      <c r="AD59" t="str">
+      <c r="AD59" t="str" s="1">
         <v>Aluminum alloy</v>
       </c>
-      <c r="AE59" t="str">
+      <c r="AE59" t="str" s="1">
         <v>HAGANE 机身</v>
       </c>
       <c r="AF59" t="str">
@@ -11756,7 +11763,7 @@
       <c r="AH59" t="str">
         <v/>
       </c>
-      <c r="AI59" t="str">
+      <c r="AI59" t="str" s="1">
         <v>海鲈近岸 / 港湾</v>
       </c>
       <c r="AJ59" t="str">
@@ -11768,7 +11775,7 @@
       <c r="AL59" t="str">
         <v/>
       </c>
-      <c r="AM59" t="str">
+      <c r="AM59" t="str" s="1">
         <v>1</v>
       </c>
       <c r="AN59" t="str">
@@ -11789,7 +11796,7 @@
       <c r="AS59" t="str">
         <v/>
       </c>
-      <c r="AT59" t="str">
+      <c r="AT59" t="str" s="1">
         <v>单摇臂</v>
       </c>
       <c r="AU59" t="str">
@@ -11813,10 +11820,10 @@
       <c r="BA59" t="str">
         <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_exsence_dc_2022_v2.pdf</v>
       </c>
-      <c r="BB59" t="str">
+      <c r="BB59" t="str" s="1">
         <v>EVA</v>
       </c>
-      <c r="BC59" t="str">
+      <c r="BC59" t="str" s="1">
         <v>M7</v>
       </c>
       <c r="BD59" t="str">
@@ -11828,7 +11835,7 @@
       <c r="BF59" t="str">
         <v/>
       </c>
-      <c r="BG59" t="str">
+      <c r="BG59" t="str" s="1">
         <v>海鲈</v>
       </c>
       <c r="BH59" t="str">

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import_test.xlsx
@@ -2533,10 +2533,10 @@
         <v/>
       </c>
       <c r="AZ8" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA8" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB8" t="str">
         <v/>
@@ -2715,10 +2715,10 @@
         <v/>
       </c>
       <c r="AZ9" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA9" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB9" t="str">
         <v/>
@@ -2897,10 +2897,10 @@
         <v/>
       </c>
       <c r="AZ10" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA10" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB10" t="str">
         <v/>
@@ -3079,10 +3079,10 @@
         <v/>
       </c>
       <c r="AZ11" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA11" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB11" t="str">
         <v/>
@@ -3261,10 +3261,10 @@
         <v/>
       </c>
       <c r="AZ12" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA12" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB12" t="str">
         <v/>
@@ -3443,10 +3443,10 @@
         <v/>
       </c>
       <c r="AZ13" t="str">
-        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046956</v>
+        <v/>
       </c>
       <c r="BA13" t="str">
-        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24SLX_70.pdf</v>
+        <v/>
       </c>
       <c r="BB13" t="str">
         <v/>
